--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -1,34 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Natures et techniques" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Natures et techniques" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,78 +351,100 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="44.83203125" customWidth="1"/>
+    <col min="3" max="3" width="120.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Identifiant</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Sujet</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Texte</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Modifié le</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
+      <c r="A1" t="str">
+        <v>Identifiant</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Sujet</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Modifié le</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Statut</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sc.sub.equestre</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Statue ou monument équestre</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tout commence à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen Âge, on la prenait pour Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Il s'inspire de Marc Aurèle, mais il se méfie : sous le sabot levé du cheval, il glisse une boule de bronze, un point d'appui discret. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio, à Venise, supprime la béquille. Dans le *Colleoni*, le sabot se lève dans le vide, le cheval tire sur le mors, le cavalier se dresse sur ses étriers et fixe l'horizon. Verrocchio meurt en 1488 avant la fonte, que réalise Alessandro Leopardi, qui conçoit aussi le socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Giambologne revient au calme avec *Cosme Ier* en 1594 : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. Son élève Pietro Tacca l'imite en 1608 pour *Ferdinand Ier*, d'après un projet du maître. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg/1280px-Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Mochi y met du mouvement : manteau et crinière au vent, c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin : le bronze semble s'élancer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Pour Philippe IV d'Espagne, Tacca cabre le cheval : seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Desjardins, puis Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. La statue de Lyon, détruite en 1792, a été refaite par Lemot en 1825. Même retour à l'antique à Bristol en 1733, où Rysbrack habille Guillaume III à la romaine. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg/960px-Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]Le XIXe siècle fait du monument un récit national. À Berlin, Rauch place Frédéric le Grand en costume de son temps, au-dessus d'un socle peuplé des généraux, des ministres et des penseurs de son règne. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]À Saint-Pétersbourg, en 1859, Klodt va plus loin que Tacca : le cheval de Nicolas Ier se cabre en ne touchant le socle que par ses deux pattes arrière, sans l'aide de la queue. À Ajaccio, Barye habille Napoléon en empereur romain, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]et Bartholdi offre à la France un héros dont personne ne connaît le visage, Vercingétorix. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Troubetzkoy, en 1909, choisit au contraire la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. En vingt siècles, le cavalier est passé de trois sabots à deux, puis est revenu à quatre.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21/10/2026 18:27:42</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Terminé</t>
-        </is>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>sc.sub.equestre</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Statue ou monument équestre</v>
+      </c>
+      <c r="C2" t="str" xml:space="preserve">
+        <v xml:space="preserve">[titre: Le monument équestre]
+En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc-Aurèle, 175 av JC | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Il s'inspire de Marc Aurèle, mais il se méfie : sous le sabot levé du cheval, il glisse une boule de bronze, un point d'appui discret. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio, à Venise, supprime la béquille. Dans le *Colleoni*, le sabot se lève dans le vide, le cheval tire sur le mors, le cavalier se dresse sur ses étriers et fixe l'horizon. Verrocchio meurt en 1488 avant la fonte, que réalise Alessandro Leopardi, qui conçoit aussi le socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Giambologna revient au calme avec *Cosme Ier* en 1594 : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite en 1608 pour *Ferdinand Ier*, d'après un projet du maître. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg/1280px-Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Mochi introduit plus de mouvement dans son monument dédié à Alexandre Farnèse: manteau et crinière au vent, c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin : le bronze semble s'élancer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Pour Philippe IV d'Espagne, Tacca cabre le cheval : seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère un retour à la sérénité : Desjardins, puis Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. La statue de Lyon, détruite en 1792, a été refaite par Lemot en 1825. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol en 1733, où Rysbrack habille Guillaume III à la romaine. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg/960px-Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]Le XIXe siècle fait du monument un récit national. À Berlin, Rauch place Frédéric le Grand en costume de son temps, au-dessus d'un socle peuplé des généraux, des ministres et des penseurs de son règne. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]À Saint-Pétersbourg, en 1859, Klodt va plus loin que Tacca : le cheval de Nicolas Ier se cabre en ne touchant le socle que par ses deux pattes arrière, sans l'aide de la queue. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Barye habille Napoléon en empereur romain dans une formule plus classique, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10] mais Bartholdi offre à la France un héros dont personne ne connaît le visage, Vercingétorix, sur son cheval lancé au triple galop, dont aucun sabot ne touche le sol. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Troubetzkoy, en 1909, choisit au contraire la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
+[sortie: noir]</v>
+      </c>
+      <c r="D2" t="str">
+        <v>22/10/2026 00:07:04</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Terminé</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -403,7 +403,7 @@
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
     <col min="3" max="3" width="120.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,11 +432,11 @@
       </c>
       <c r="C2" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: Le monument équestre]
-En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc-Aurèle, 175 av JC | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Il s'inspire de Marc Aurèle, mais il se méfie : sous le sabot levé du cheval, il glisse une boule de bronze, un point d'appui discret. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio, à Venise, supprime la béquille. Dans le *Colleoni*, le sabot se lève dans le vide, le cheval tire sur le mors, le cavalier se dresse sur ses étriers et fixe l'horizon. Verrocchio meurt en 1488 avant la fonte, que réalise Alessandro Leopardi, qui conçoit aussi le socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Giambologna revient au calme avec *Cosme Ier* en 1594 : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite en 1608 pour *Ferdinand Ier*, d'après un projet du maître. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg/1280px-Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Mochi introduit plus de mouvement dans son monument dédié à Alexandre Farnèse: manteau et crinière au vent, c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin : le bronze semble s'élancer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Pour Philippe IV d'Espagne, Tacca cabre le cheval : seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère un retour à la sérénité : Desjardins, puis Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. La statue de Lyon, détruite en 1792, a été refaite par Lemot en 1825. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol en 1733, où Rysbrack habille Guillaume III à la romaine. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg/960px-Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]Le XIXe siècle fait du monument un récit national. À Berlin, Rauch place Frédéric le Grand en costume de son temps, au-dessus d'un socle peuplé des généraux, des ministres et des penseurs de son règne. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]À Saint-Pétersbourg, en 1859, Klodt va plus loin que Tacca : le cheval de Nicolas Ier se cabre en ne touchant le socle que par ses deux pattes arrière, sans l'aide de la queue. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Barye habille Napoléon en empereur romain dans une formule plus classique, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10] mais Bartholdi offre à la France un héros dont personne ne connaît le visage, Vercingétorix, sur son cheval lancé au triple galop, dont aucun sabot ne touche le sol. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Troubetzkoy, en 1909, choisit au contraire la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
+En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Il s'inspire [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]de Marc Aurèle, mais il se méfie : sous le sabot levé [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]du cheval, il glisse une boule de bronze, un point d'appui discret. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio, à Venise, supprime la béquille. Dans le *Colleoni*, le sabot se lève dans le vide, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]le cheval tire sur le mors, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio meurt en 1488 avant la fonte, que réalise Alessandro Leopardi, qui conçoit aussi le socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Giambologna revient au calme avec *Cosme Ier* en 1594 : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]en 1608 pour *Ferdinand Ier*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]d'après un projet du maître. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Mochi introduit plus de mouvement dans son monument dédié à [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Alexandre Farnèse: manteau et crinière au vent, c'est l'élan du baroque, tout le [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]contraire de la sérénité du modèle florentin : le bronze semble s'élancer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Pour Philippe IV d'Espagne, Tacca réalise un cheval cabré : [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère un retour à la sérénité : Desjardins, [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]puis Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Aurèle. La statue de Lyon, détruite en 1792, a été refaite par Lemot en 1825. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol en 1733, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]où Rysbrack habille Guillaume III à la romaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, Thorvaldsen représente le prince Józef Poniatowski, mort en 1813 en combattant aux côtés de Napoléon, en général romain presque nu, ce qui déplaît à beaucoup. Surtout, après le [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Rauch place Frédéric le Grand en costume de son temps, au-dessus d'un socle peuplé des généraux, des ministres et des penseurs de son règne. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Thomas Crawford le place à cheval au sommet d'un monument, au-dessus de six autres figures de la Révolution virginienne, dont Jefferson. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Crawford meurt en 1857, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]À Saint-Pétersbourg, en 1859, Klodt va plus loin que Tacca : le cheval de Nicolas Ier se cabre en ne touchant le socle que par ses deux pattes arrière, sans l'aide de la queue. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Barye habille Napoléon en empereur romain dans une formule plus classique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait pourtant fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure : ce roi, c'est celui que Jeanne d'Arc avait fait sacrer à Reims. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Frémiet la met en selle en 1874, place des Pyramides, à Paris : une jeune paysanne devenue chef de guerre, étendard levé, en bronze doré, figure nationale d'une France meurtrie par la défaite de 1870. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]À l'échelle de la statuette, Gérôme met en scène en 1897 l'entrée de Bonaparte au Caire, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]et Troubetzkoy, en 1899, montre *Tolstoï à cheval* : un écrivain en promenade, sans uniforme ni couronne, au modelé rapide. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Bartholdi, en 1903, offre à la France un héros dont personne ne connaît le visage, Vercingétorix, sur son cheval lancé au triple galop, dont aucun sabot ne touche le sol. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Victoire, précède le cheval. L'allégorie quitte le socle pour entrer dans la scène, et le bronze est doré. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, en 1908, Dallin offre un tout autre visage de l'Amérique [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]: un cavalier amérindien, sans arme, les bras ouverts vers le ciel. Ici, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]le cheval ne sert plus à la guerre mais à la prière. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Bourdelle, enfin, reçoit en 1913 la commande du monument au général Alvear, à Buenos Aires. Il lui faut dix ans : le général, bras levé et cape au vent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. Inauguré en 1926, il retrouve le socle peuplé de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
 [sortie: noir]</v>
       </c>
       <c r="D2" t="str">
-        <v>22/10/2026 00:07:04</v>
+        <v>24/10/2026 00:15:35</v>
       </c>
       <c r="E2" t="str">
         <v>Terminé</v>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -432,11 +432,11 @@
       </c>
       <c r="C2" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: Le monument équestre]
-En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Il s'inspire [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]de Marc Aurèle, mais il se méfie : sous le sabot levé [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]du cheval, il glisse une boule de bronze, un point d'appui discret. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio, à Venise, supprime la béquille. Dans le *Colleoni*, le sabot se lève dans le vide, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]le cheval tire sur le mors, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Verrocchio meurt en 1488 avant la fonte, que réalise Alessandro Leopardi, qui conçoit aussi le socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Giambologna revient au calme avec *Cosme Ier* en 1594 : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]en 1608 pour *Ferdinand Ier*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]d'après un projet du maître. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Mochi introduit plus de mouvement dans son monument dédié à [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Alexandre Farnèse: manteau et crinière au vent, c'est l'élan du baroque, tout le [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]contraire de la sérénité du modèle florentin : le bronze semble s'élancer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Pour Philippe IV d'Espagne, Tacca réalise un cheval cabré : [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère un retour à la sérénité : Desjardins, [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]puis Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Aurèle. La statue de Lyon, détruite en 1792, a été refaite par Lemot en 1825. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol en 1733, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]où Rysbrack habille Guillaume III à la romaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, Thorvaldsen représente le prince Józef Poniatowski, mort en 1813 en combattant aux côtés de Napoléon, en général romain presque nu, ce qui déplaît à beaucoup. Surtout, après le [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Rauch place Frédéric le Grand en costume de son temps, au-dessus d'un socle peuplé des généraux, des ministres et des penseurs de son règne. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Thomas Crawford le place à cheval au sommet d'un monument, au-dessus de six autres figures de la Révolution virginienne, dont Jefferson. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Crawford meurt en 1857, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]À Saint-Pétersbourg, en 1859, Klodt va plus loin que Tacca : le cheval de Nicolas Ier se cabre en ne touchant le socle que par ses deux pattes arrière, sans l'aide de la queue. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Barye habille Napoléon en empereur romain dans une formule plus classique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait pourtant fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure : ce roi, c'est celui que Jeanne d'Arc avait fait sacrer à Reims. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Frémiet la met en selle en 1874, place des Pyramides, à Paris : une jeune paysanne devenue chef de guerre, étendard levé, en bronze doré, figure nationale d'une France meurtrie par la défaite de 1870. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]À l'échelle de la statuette, Gérôme met en scène en 1897 l'entrée de Bonaparte au Caire, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]et Troubetzkoy, en 1899, montre *Tolstoï à cheval* : un écrivain en promenade, sans uniforme ni couronne, au modelé rapide. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Bartholdi, en 1903, offre à la France un héros dont personne ne connaît le visage, Vercingétorix, sur son cheval lancé au triple galop, dont aucun sabot ne touche le sol. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Victoire, précède le cheval. L'allégorie quitte le socle pour entrer dans la scène, et le bronze est doré. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, en 1908, Dallin offre un tout autre visage de l'Amérique [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]: un cavalier amérindien, sans arme, les bras ouverts vers le ciel. Ici, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]le cheval ne sert plus à la guerre mais à la prière. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Bourdelle, enfin, reçoit en 1913 la commande du monument au général Alvear, à Buenos Aires. Il lui faut dix ans : le général, bras levé et cape au vent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. Inauguré en 1926, il retrouve le socle peuplé de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
+En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. Sa tête est au Louvre, son corps à Athènes : on ne les a réunis qu'en 1936. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Ce « chat au miel », c'est Erasmo da Narni, un condottiere, chef de mercenaires, mort en 1443 au service de Venise. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Une statue équestre était réservée aux souverains : le Sénat de Venise a fait une exception. Donatello s'inspire de Marc Aurèle, mais son cavalier est un homme d'armes, cuirassé, l'épée au côté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Il se méfie pourtant : sous le sabot levé, une boule de bronze sert de point d'appui. Fêté à Padoue, il rentre à Florence, dit Vasari, de peur que les louanges lui fassent oublier son métier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Andrea del Verrocchio, à Venise, supprime la béquille : dans le *Colleoni*, le sabot se lève dans le vide, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Bartolomeo Colleoni, condottiere et capitaine général de Venise, lègue sa fortune à la République, à condition qu'on lui dresse une statue place Saint-Marc. Or les statues y sont interdites. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Venise place donc le cavalier devant la Scuola di San Marco, une autre « Saint-Marc ». Verrocchio meurt en 1488 avant la fonte : Alessandro Leopardi coule le bronze, et la statue est dressée en 1496. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Jean de Boulogne, dit Giambologna, né à Douai, en Flandre, termine en 1594 *Cosme Ier*, premier grand-duc de Toscane : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite pour *Ferdinand Ier*, fils de Cosme, d'après un projet du maître, qui meurt en 1608, l'année de l'inauguration. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]On raconte que le bronze vient de canons pris aux Turcs par les chevaliers de Saint-Étienne, l'ordre fondé par les Médicis contre les corsaires ; Ferdinand en porte la croix. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Derrière le cheval, deux fontaines aux monstres marins, que Tacca avait d'abord conçues pour une statue de Ferdinand à Livourne : le grand-duc a droit à toute une mise en scène. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Francesco Mochi, venu de Toscane, élève en 1625 le monument d'Alexandre Farnèse, ce duc de Parme qui commanda les armées de l'Espagne en Flandre et prit Anvers en 1585. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Manteau et crinière au vent, le cheval semble sauvage : c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin, et le bronze semble s'élancer. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Mochi a sculpté cinq ans plus tôt le fils d'Alexandre, Ranuccio, et ces deux cavaliers ont donné son nom à la place : la Piazza dei Cavalli, la place des Chevaux. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Philippe IV d'Espagne veut une statue plus prestigieuse que celle de son père, et Pietro Tacca, d'après un dessin de Velázquez, réalise un cheval cabré : [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. Sur le socle, le roi décore Velázquez, l'homme dont le dessin a servi de modèle ; mais la statue ne gagne la place d'Orient qu'en 1843. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Martin Desjardins, puis François Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]À Lyon, la statue de Desjardins, coulée en 1694, voyage sept ans par la Seine, la mer et le Rhône, et n'est inaugurée qu'en 1713, deux ans avant la mort du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Détruite en 1792, elle est refaite par Lemot en 1825. Selon une légende, il se serait tué d'avoir oublié les étriers : c'est faux, le roi est monté à la romaine. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol, où le Flamand John Michael Rysbrack habille à la romaine Guillaume III d'Orange. Coulée en 1733, la statue est dressée en 1736 sur Queen Square. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]La ville pensait d'abord à George II ; ses notables, partisans du Parlement, ont préféré Guillaume III. Évacuée à Badminton pendant la guerre, elle est revenue en 1948. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, le Danois Bertel Thorvaldsen représente le prince Józef Poniatowski, noyé dans l'Elster, à Leipzig, en 1813, trois jours après avoir été nommé maréchal de France par Napoléon. Il le sculpte en général romain presque nu, ce qui déplaît à beaucoup. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Surtout, après le soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Christian Daniel Rauch place Frédéric le Grand en uniforme, au-dessus d'un socle où défilent soixante-quatorze généraux, ministres et penseurs de son règne. Démonté en 1950 par l'Allemagne de l'Est, il revient en 1980, quand Honecker se met à dire « Frédéric le Grand ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, l'Américain Thomas Crawford, installé à Rome, le place à cheval au sommet d'un monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Autour de lui, d'autres grandes figures de la Révolution virginienne, dont Jefferson et Patrick Henry. Les bronzes sont modelés à Rome, puis fondus à Munich avant de traverser l'Atlantique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Mais Crawford perd la vue en 1856 : c'est un cancer de l'œil. Il meurt à Londres en 1857, avant que la statue soit dressée, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]En 1859, à Saint-Pétersbourg, Piotr Klodt va plus loin que Tacca : le cheval de Nicolas Ier ne touche le socle que par ses deux pattes arrière. On plaisante : Nicolas veut rattraper Pierre le Grand, mais la cathédrale Saint-Isaac l'en empêche. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Antoine-Louis Barye, le sculpteur des fauves, habille Napoléon en empereur romain et ses frères en toges, pour éviter les costumes d'époque. Le monument regardait la mer ; depuis 1969, il fait face à la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure : le roi que Jeanne d'Arc a fait sacrer à Reims en 1429, et qui ne fera rien pour la sauver. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Emmanuel Frémiet la met en selle en 1874, place des Pyramides, là où Jeanne fut blessée en 1429 : une paysanne devenue chef de guerre, en bronze doré, pour une France meurtrie par 1870. Mécontent du cheval, il l'a discrètement fait remplacer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]Le peintre Jean-Léon Gérôme s'essaie aussi au bronze : son *Bonaparte entrant au Caire*, en 1798, est présenté au Salon de 1897 puis acheté par l'État pour le Luxembourg, avec une patine colorée et dorée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]En 1899, Paolo Troubetzkoy, que Tolstoï aimait beaucoup, le montre à cheval : un écrivain en promenade, sans uniforme ni couronne. Tous deux végétariens, Troubetzkoy refusait la viande en s'écriant : « Je ne mange pas de cadavre ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Auguste Bartholdi, père de la Liberté de New York et du Lion de Belfort, offre en 1903 à la France un héros dont personne ne connaît le visage : Vercingétorix, l'épée levée sur son cheval cabré, un Romain mort sous les sabots. Inauguré par Émile Combes. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Augustus Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la Victoire, précède le cheval, et le bronze est doré. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Son modèle, Hettie Anderson, une jeune femme noire, ne fut connue du public que dans les années 1980. Onze ans séparent le projet de l'inauguration, où le sculpteur, très fragile, était présent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, Cyrus Dallin, né dans l'Utah, offre en 1908 un tout autre visage de l'Amérique : enfant, il côtoyait des petits Amérindiens, et il en garde ce cavalier sans arme, les bras ouverts vers le ciel. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Le cheval ne sert plus à la guerre mais à la prière. Fondue à Paris, la statue reçoit une médaille d'or au Salon, puis est installée devant le musée des Beaux-Arts de Boston en 1912. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Quand on a restauré le bronze, Dallin a exigé qu'on lui rende sa patine verte, qu'il préférait au brun d'origine. Le musée invite aujourd'hui des auteurs amérindiens à en discuter le sens. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Paolo Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. On surnomme aussitôt le monument « l'Hippopotame » ; sous les Soviets, on y grave « l'épouvantail en fonte ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Antoine Bourdelle, enfin, reçoit en 1913 la commande du monument au général Carlos María de Alvear, l'un des héros de l'indépendance argentine, à Buenos Aires. Il lui faudra près de dix ans, et cinquante-sept études, avant de trouver la bonne forme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Le général, bras levé et cape au vent, domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Inauguré en 1926, il retrouve le socle peuplé de Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
 [sortie: noir]</v>
       </c>
       <c r="D2" t="str">
-        <v>24/10/2026 00:15:35</v>
+        <v>24/10/2026 09:39:19</v>
       </c>
       <c r="E2" t="str">
         <v>Terminé</v>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -432,11 +432,11 @@
       </c>
       <c r="C2" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: Le monument équestre]
-En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. Sa tête est au Louvre, son corps à Athènes : on ne les a réunis qu'en 1936. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Ce « chat au miel », c'est Erasmo da Narni, un condottiere, chef de mercenaires, mort en 1443 au service de Venise. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Une statue équestre était réservée aux souverains : le Sénat de Venise a fait une exception. Donatello s'inspire de Marc Aurèle, mais son cavalier est un homme d'armes, cuirassé, l'épée au côté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Il se méfie pourtant : sous le sabot levé, une boule de bronze sert de point d'appui. Fêté à Padoue, il rentre à Florence, dit Vasari, de peur que les louanges lui fassent oublier son métier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Andrea del Verrocchio, à Venise, supprime la béquille : dans le *Colleoni*, le sabot se lève dans le vide, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Bartolomeo Colleoni, condottiere et capitaine général de Venise, lègue sa fortune à la République, à condition qu'on lui dresse une statue place Saint-Marc. Or les statues y sont interdites. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Venise place donc le cavalier devant la Scuola di San Marco, une autre « Saint-Marc ». Verrocchio meurt en 1488 avant la fonte : Alessandro Leopardi coule le bronze, et la statue est dressée en 1496. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Jean de Boulogne, dit Giambologna, né à Douai, en Flandre, termine en 1594 *Cosme Ier*, premier grand-duc de Toscane : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite pour *Ferdinand Ier*, fils de Cosme, d'après un projet du maître, qui meurt en 1608, l'année de l'inauguration. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]On raconte que le bronze vient de canons pris aux Turcs par les chevaliers de Saint-Étienne, l'ordre fondé par les Médicis contre les corsaires ; Ferdinand en porte la croix. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Derrière le cheval, deux fontaines aux monstres marins, que Tacca avait d'abord conçues pour une statue de Ferdinand à Livourne : le grand-duc a droit à toute une mise en scène. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Francesco Mochi, venu de Toscane, élève en 1625 le monument d'Alexandre Farnèse, ce duc de Parme qui commanda les armées de l'Espagne en Flandre et prit Anvers en 1585. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Manteau et crinière au vent, le cheval semble sauvage : c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin, et le bronze semble s'élancer. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Mochi a sculpté cinq ans plus tôt le fils d'Alexandre, Ranuccio, et ces deux cavaliers ont donné son nom à la place : la Piazza dei Cavalli, la place des Chevaux. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Philippe IV d'Espagne veut une statue plus prestigieuse que celle de son père, et Pietro Tacca, d'après un dessin de Velázquez, réalise un cheval cabré : [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. Sur le socle, le roi décore Velázquez, l'homme dont le dessin a servi de modèle ; mais la statue ne gagne la place d'Orient qu'en 1843. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Martin Desjardins, puis François Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]À Lyon, la statue de Desjardins, coulée en 1694, voyage sept ans par la Seine, la mer et le Rhône, et n'est inaugurée qu'en 1713, deux ans avant la mort du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Détruite en 1792, elle est refaite par Lemot en 1825. Selon une légende, il se serait tué d'avoir oublié les étriers : c'est faux, le roi est monté à la romaine. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol, où le Flamand John Michael Rysbrack habille à la romaine Guillaume III d'Orange. Coulée en 1733, la statue est dressée en 1736 sur Queen Square. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]La ville pensait d'abord à George II ; ses notables, partisans du Parlement, ont préféré Guillaume III. Évacuée à Badminton pendant la guerre, elle est revenue en 1948. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, le Danois Bertel Thorvaldsen représente le prince Józef Poniatowski, noyé dans l'Elster, à Leipzig, en 1813, trois jours après avoir été nommé maréchal de France par Napoléon. Il le sculpte en général romain presque nu, ce qui déplaît à beaucoup. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Surtout, après le soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Christian Daniel Rauch place Frédéric le Grand en uniforme, au-dessus d'un socle où défilent soixante-quatorze généraux, ministres et penseurs de son règne. Démonté en 1950 par l'Allemagne de l'Est, il revient en 1980, quand Honecker se met à dire « Frédéric le Grand ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, l'Américain Thomas Crawford, installé à Rome, le place à cheval au sommet d'un monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Autour de lui, d'autres grandes figures de la Révolution virginienne, dont Jefferson et Patrick Henry. Les bronzes sont modelés à Rome, puis fondus à Munich avant de traverser l'Atlantique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Mais Crawford perd la vue en 1856 : c'est un cancer de l'œil. Il meurt à Londres en 1857, avant que la statue soit dressée, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]En 1859, à Saint-Pétersbourg, Piotr Klodt va plus loin que Tacca : le cheval de Nicolas Ier ne touche le socle que par ses deux pattes arrière. On plaisante : Nicolas veut rattraper Pierre le Grand, mais la cathédrale Saint-Isaac l'en empêche. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Antoine-Louis Barye, le sculpteur des fauves, habille Napoléon en empereur romain et ses frères en toges, pour éviter les costumes d'époque. Le monument regardait la mer ; depuis 1969, il fait face à la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure : le roi que Jeanne d'Arc a fait sacrer à Reims en 1429, et qui ne fera rien pour la sauver. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Emmanuel Frémiet la met en selle en 1874, place des Pyramides, là où Jeanne fut blessée en 1429 : une paysanne devenue chef de guerre, en bronze doré, pour une France meurtrie par 1870. Mécontent du cheval, il l'a discrètement fait remplacer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]Le peintre Jean-Léon Gérôme s'essaie aussi au bronze : son *Bonaparte entrant au Caire*, en 1798, est présenté au Salon de 1897 puis acheté par l'État pour le Luxembourg, avec une patine colorée et dorée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]En 1899, Paolo Troubetzkoy, que Tolstoï aimait beaucoup, le montre à cheval : un écrivain en promenade, sans uniforme ni couronne. Tous deux végétariens, Troubetzkoy refusait la viande en s'écriant : « Je ne mange pas de cadavre ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Auguste Bartholdi, père de la Liberté de New York et du Lion de Belfort, offre en 1903 à la France un héros dont personne ne connaît le visage : Vercingétorix, l'épée levée sur son cheval cabré, un Romain mort sous les sabots. Inauguré par Émile Combes. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Augustus Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la Victoire, précède le cheval, et le bronze est doré. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Son modèle, Hettie Anderson, une jeune femme noire, ne fut connue du public que dans les années 1980. Onze ans séparent le projet de l'inauguration, où le sculpteur, très fragile, était présent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, Cyrus Dallin, né dans l'Utah, offre en 1908 un tout autre visage de l'Amérique : enfant, il côtoyait des petits Amérindiens, et il en garde ce cavalier sans arme, les bras ouverts vers le ciel. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Le cheval ne sert plus à la guerre mais à la prière. Fondue à Paris, la statue reçoit une médaille d'or au Salon, puis est installée devant le musée des Beaux-Arts de Boston en 1912. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Quand on a restauré le bronze, Dallin a exigé qu'on lui rende sa patine verte, qu'il préférait au brun d'origine. Le musée invite aujourd'hui des auteurs amérindiens à en discuter le sens. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Paolo Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. On surnomme aussitôt le monument « l'Hippopotame » ; sous les Soviets, on y grave « l'épouvantail en fonte ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Antoine Bourdelle, enfin, reçoit en 1913 la commande du monument au général Carlos María de Alvear, l'un des héros de l'indépendance argentine, à Buenos Aires. Il lui faudra près de dix ans, et cinquante-sept études, avant de trouver la bonne forme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Le général, bras levé et cape au vent, domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Inauguré en 1926, il retrouve le socle peuplé de Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
+En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. Sa tête est au Louvre, son corps à Athènes : on ne les a réunis qu'en 1936. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Ce « chat au miel », c'est Erasmo da Narni, un condottiere, chef de mercenaires, mort en 1443 au service de Venise. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Une statue équestre était réservée aux souverains : le Sénat de Venise a fait une exception. Donatello s'inspire de Marc Aurèle, mais son cavalier est un homme d'armes, cuirassé, l'épée au côté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Il se méfie pourtant : sous le sabot levé, une boule de bronze sert de point d'appui. Fêté à Padoue, il rentre à Florence, dit Vasari, de peur que les louanges lui fassent oublier son métier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Andrea del Verrocchio, à Venise, supprime la béquille : dans le *Colleoni*, le sabot se lève dans le vide, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Bartolomeo Colleoni, condottiere et capitaine général de Venise, lègue sa fortune à la République, à condition qu'on lui dresse une statue place Saint-Marc. Or les statues y sont interdites. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Venise place donc le cavalier devant la Scuola di San Marco, une autre « Saint-Marc ». Verrocchio meurt en 1488 avant la fonte : Alessandro Leopardi coule le bronze, et la statue est dressée en 1496. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Jean de Boulogne, dit Giambologna, né à Douai, en Flandre, termine en 1594 *Cosme Ier*, premier grand-duc de Toscane : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite pour *Ferdinand Ier*, fils de Cosme, d'après un projet du maître, qui meurt en 1608, l'année de l'inauguration. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]On raconte que le bronze vient de canons pris aux Turcs par les chevaliers de Saint-Étienne, l'ordre fondé par les Médicis contre les corsaires ; Ferdinand en porte la croix. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Derrière le cheval, deux fontaines aux monstres marins, que Tacca avait d'abord conçues pour une statue de Ferdinand à Livourne : le grand-duc a droit à toute une mise en scène. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Francesco Mochi, venu de Toscane, élève en 1625 le monument d'Alexandre Farnèse, ce duc de Parme qui commanda les armées de l'Espagne en Flandre et prit Anvers en 1585. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Manteau et crinière au vent, le cheval semble sauvage : c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin, et le bronze semble s'élancer. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Mochi a sculpté cinq ans plus tôt le fils d'Alexandre, Ranuccio, et ces deux cavaliers ont donné son nom à la place : la Piazza dei Cavalli, la place des Chevaux. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Philippe IV d'Espagne veut une statue plus prestigieuse que celle de son père, et Pietro Tacca, d'après un dessin de Velázquez, réalise un cheval cabré : [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. Sur le socle, le roi décore Velázquez, l'homme dont le dessin a servi de modèle ; mais la statue ne gagne la place d'Orient qu'en 1843. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Martin Desjardins, puis François Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]À Lyon, la statue de Desjardins, coulée en 1694, voyage sept ans par la Seine, la mer et le Rhône, et n'est inaugurée qu'en 1713, deux ans avant la mort du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Détruite en 1792, elle est refaite par Lemot en 1825. Selon une légende, il se serait tué d'avoir oublié les étriers : c'est faux, le roi monte simplement à la romaine, sans étriers. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol, où le Flamand John Michael Rysbrack habille à la romaine Guillaume III d'Orange. Coulée en 1733, la statue est dressée en 1736 sur Queen Square. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]La ville pensait d'abord à George II ; ses notables, partisans du Parlement, ont préféré Guillaume III. Évacuée à Badminton pendant la guerre, elle est revenue en 1948. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, le Danois Bertel Thorvaldsen représente le prince Józef Poniatowski, noyé dans l'Elster, à Leipzig, en 1813, trois jours après avoir été nommé maréchal de France par Napoléon. Il le sculpte en général romain presque nu, ce qui déplaît à beaucoup. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Surtout, après le soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Christian Daniel Rauch place Frédéric le Grand en uniforme, au-dessus d'un socle où défilent soixante-quatorze généraux, ministres et penseurs de son règne. Démonté en 1950 par l'Allemagne de l'Est, il revient en 1980, quand Honecker se met à dire « Frédéric le Grand ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, l'Américain Thomas Crawford, installé à Rome, le place à cheval au sommet d'un monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Autour de lui, d'autres grandes figures de la Révolution virginienne, dont Jefferson et Patrick Henry. Les bronzes sont modelés à Rome, puis fondus à Munich avant de traverser l'Atlantique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Mais Crawford perd la vue en 1856 à cause d'un cancer de l'œil. Il meurt à Londres en 1857, avant que la statue soit dressée, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]En 1859, à Saint-Pétersbourg, Piotr Klodt va plus loin que Tacca : le cheval de Nicolas Ier ne touche le socle que par ses deux pattes arrière. On plaisante : Nicolas veut rattraper Pierre le Grand, mais la cathédrale Saint-Isaac l'en empêche. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Antoine-Louis Barye, le sculpteur des fauves, habille Napoléon en empereur romain et ses frères en toges, pour éviter les costumes d'époque. Le monument regardait la mer mais depuis 1969, il fait face à la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure, ce roi que Jeanne d'Arc a fait sacrer à Reims en 1429, et qui ne fera rien pour la sauver. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Emmanuel Frémiet met Jeanne en selle en 1874, place des Pyramides, là où elle fut blessée en 1429 : une paysanne devenue chef de guerre, en bronze doré, pour une France meurtrie par la défaite de 1870. Mécontent du cheval, il l'a discrètement fait remplacer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]Le peintre Jean-Léon Gérôme s'essaie aussi au bronze avec son *Bonaparte entrant au Caire*, en 1798, qui est présenté au Salon de 1897 puis acheté par l'État pour le Luxembourg, avec une patine colorée et dorée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]En 1899, Paolo Troubetzkoy, que Tolstoï aimait beaucoup, le montre à cheval. Il le modèle comme un écrivain en promenade, sans uniforme ni couronne. Ils étaient tous deux végétariens, Troubetzkoy refusait la viande en s'écriant : « Je ne mange pas de cadavre ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Auguste Bartholdi, père de la Liberté de New York et du Lion de Belfort, offre en 1903 à la France un héros dont personne ne connaît le visage : Vercingétorix, l'épée levée sur son cheval cabré, un Romain mort sous les sabots. Inauguré par Émile Combes. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Augustus Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la Victoire, précède le cheval, et le bronze est doré. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Son modèle, Hettie Anderson, une jeune femme noire, ne fut connue du public que dans les années 1980. Onze ans séparent le projet de l'inauguration, où le sculpteur, très fragile, était présent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, Cyrus Dallin, né dans l'Utah, offre en 1908 un tout autre visage de l'Amérique : enfant, il côtoyait des petits Amérindiens, et il en garde ce cavalier sans arme, les bras ouverts vers le ciel. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Le cheval ne sert plus à la guerre mais à la prière. Fondue à Paris, la statue reçoit une médaille d'or au Salon, puis est installée devant le musée des Beaux-Arts de Boston en 1912. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Quand on a restauré le bronze, Dallin a exigé qu'on lui rende sa patine verte, qu'il préférait au brun d'origine. Le musée invite aujourd'hui des auteurs amérindiens à en discuter le sens. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Paolo Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. On surnomme aussitôt le monument « l'Hippopotame » ; sous les Soviets, on y grave « l'épouvantail en fonte ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Antoine Bourdelle, enfin, reçoit en 1913 la commande du monument au général Carlos María de Alvear, l'un des héros de l'indépendance argentine, à Buenos Aires. Il lui faudra près de dix ans, et cinquante-sept études, avant de trouver la bonne forme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Le général, bras levé et cape au vent, domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Inauguré en 1926, il retrouve le socle peuplé de Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
 [sortie: noir]</v>
       </c>
       <c r="D2" t="str">
-        <v>24/10/2026 09:39:19</v>
+        <v>24/10/2026 14:04:38</v>
       </c>
       <c r="E2" t="str">
         <v>Terminé</v>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -432,11 +432,11 @@
       </c>
       <c r="C2" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: Le monument équestre]
-En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 5]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. Sa tête est au Louvre, son corps à Athènes : on ne les a réunis qu'en 1936. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Ce « chat au miel », c'est Erasmo da Narni, un condottiere, chef de mercenaires, mort en 1443 au service de Venise. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Une statue équestre était réservée aux souverains : le Sénat de Venise a fait une exception. Donatello s'inspire de Marc Aurèle, mais son cavalier est un homme d'armes, cuirassé, l'épée au côté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Il se méfie pourtant : sous le sabot levé, une boule de bronze sert de point d'appui. Fêté à Padoue, il rentre à Florence, dit Vasari, de peur que les louanges lui fassent oublier son métier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Andrea del Verrocchio, à Venise, supprime la béquille : dans le *Colleoni*, le sabot se lève dans le vide, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Bartolomeo Colleoni, condottiere et capitaine général de Venise, lègue sa fortune à la République, à condition qu'on lui dresse une statue place Saint-Marc. Or les statues y sont interdites. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Venise place donc le cavalier devant la Scuola di San Marco, une autre « Saint-Marc ». Verrocchio meurt en 1488 avant la fonte : Alessandro Leopardi coule le bronze, et la statue est dressée en 1496. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Jean de Boulogne, dit Giambologna, né à Douai, en Flandre, termine en 1594 *Cosme Ier*, premier grand-duc de Toscane : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite pour *Ferdinand Ier*, fils de Cosme, d'après un projet du maître, qui meurt en 1608, l'année de l'inauguration. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]On raconte que le bronze vient de canons pris aux Turcs par les chevaliers de Saint-Étienne, l'ordre fondé par les Médicis contre les corsaires ; Ferdinand en porte la croix. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Derrière le cheval, deux fontaines aux monstres marins, que Tacca avait d'abord conçues pour une statue de Ferdinand à Livourne : le grand-duc a droit à toute une mise en scène. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Francesco Mochi, venu de Toscane, élève en 1625 le monument d'Alexandre Farnèse, ce duc de Parme qui commanda les armées de l'Espagne en Flandre et prit Anvers en 1585. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Manteau et crinière au vent, le cheval semble sauvage : c'est l'élan du baroque, tout le contraire de la sérénité du modèle florentin, et le bronze semble s'élancer. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Mochi a sculpté cinq ans plus tôt le fils d'Alexandre, Ranuccio, et ces deux cavaliers ont donné son nom à la place : la Piazza dei Cavalli, la place des Chevaux. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Philippe IV d'Espagne veut une statue plus prestigieuse que celle de son père, et Pietro Tacca, d'après un dessin de Velázquez, réalise un cheval cabré : [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]seules les deux pattes arrière et, discrètement, la queue touchent le socle. On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. Sur le socle, le roi décore Velázquez, l'homme dont le dessin a servi de modèle ; mais la statue ne gagne la place d'Orient qu'en 1843. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Martin Desjardins, puis François Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]À Lyon, la statue de Desjardins, coulée en 1694, voyage sept ans par la Seine, la mer et le Rhône, et n'est inaugurée qu'en 1713, deux ans avant la mort du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Détruite en 1792, elle est refaite par Lemot en 1825. Selon une légende, il se serait tué d'avoir oublié les étriers : c'est faux, le roi monte simplement à la romaine, sans étriers. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol, où le Flamand John Michael Rysbrack habille à la romaine Guillaume III d'Orange. Coulée en 1733, la statue est dressée en 1736 sur Queen Square. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]La ville pensait d'abord à George II ; ses notables, partisans du Parlement, ont préféré Guillaume III. Évacuée à Badminton pendant la guerre, elle est revenue en 1948. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, le Danois Bertel Thorvaldsen représente le prince Józef Poniatowski, noyé dans l'Elster, à Leipzig, en 1813, trois jours après avoir été nommé maréchal de France par Napoléon. Il le sculpte en général romain presque nu, ce qui déplaît à beaucoup. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Surtout, après le soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Christian Daniel Rauch place Frédéric le Grand en uniforme, au-dessus d'un socle où défilent soixante-quatorze généraux, ministres et penseurs de son règne. Démonté en 1950 par l'Allemagne de l'Est, il revient en 1980, quand Honecker se met à dire « Frédéric le Grand ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, l'Américain Thomas Crawford, installé à Rome, le place à cheval au sommet d'un monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Autour de lui, d'autres grandes figures de la Révolution virginienne, dont Jefferson et Patrick Henry. Les bronzes sont modelés à Rome, puis fondus à Munich avant de traverser l'Atlantique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Mais Crawford perd la vue en 1856 à cause d'un cancer de l'œil. Il meurt à Londres en 1857, avant que la statue soit dressée, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]En 1859, à Saint-Pétersbourg, Piotr Klodt va plus loin que Tacca : le cheval de Nicolas Ier ne touche le socle que par ses deux pattes arrière. On plaisante : Nicolas veut rattraper Pierre le Grand, mais la cathédrale Saint-Isaac l'en empêche. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Antoine-Louis Barye, le sculpteur des fauves, habille Napoléon en empereur romain et ses frères en toges, pour éviter les costumes d'époque. Le monument regardait la mer mais depuis 1969, il fait face à la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure, ce roi que Jeanne d'Arc a fait sacrer à Reims en 1429, et qui ne fera rien pour la sauver. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Emmanuel Frémiet met Jeanne en selle en 1874, place des Pyramides, là où elle fut blessée en 1429 : une paysanne devenue chef de guerre, en bronze doré, pour une France meurtrie par la défaite de 1870. Mécontent du cheval, il l'a discrètement fait remplacer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]Le peintre Jean-Léon Gérôme s'essaie aussi au bronze avec son *Bonaparte entrant au Caire*, en 1798, qui est présenté au Salon de 1897 puis acheté par l'État pour le Luxembourg, avec une patine colorée et dorée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]En 1899, Paolo Troubetzkoy, que Tolstoï aimait beaucoup, le montre à cheval. Il le modèle comme un écrivain en promenade, sans uniforme ni couronne. Ils étaient tous deux végétariens, Troubetzkoy refusait la viande en s'écriant : « Je ne mange pas de cadavre ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Auguste Bartholdi, père de la Liberté de New York et du Lion de Belfort, offre en 1903 à la France un héros dont personne ne connaît le visage : Vercingétorix, l'épée levée sur son cheval cabré, un Romain mort sous les sabots. Inauguré par Émile Combes. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Augustus Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la Victoire, précède le cheval, et le bronze est doré. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Son modèle, Hettie Anderson, une jeune femme noire, ne fut connue du public que dans les années 1980. Onze ans séparent le projet de l'inauguration, où le sculpteur, très fragile, était présent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, Cyrus Dallin, né dans l'Utah, offre en 1908 un tout autre visage de l'Amérique : enfant, il côtoyait des petits Amérindiens, et il en garde ce cavalier sans arme, les bras ouverts vers le ciel. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Le cheval ne sert plus à la guerre mais à la prière. Fondue à Paris, la statue reçoit une médaille d'or au Salon, puis est installée devant le musée des Beaux-Arts de Boston en 1912. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Quand on a restauré le bronze, Dallin a exigé qu'on lui rende sa patine verte, qu'il préférait au brun d'origine. Le musée invite aujourd'hui des auteurs amérindiens à en discuter le sens. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Paolo Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. On surnomme aussitôt le monument « l'Hippopotame » ; sous les Soviets, on y grave « l'épouvantail en fonte ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Antoine Bourdelle, enfin, reçoit en 1913 la commande du monument au général Carlos María de Alvear, l'un des héros de l'indépendance argentine, à Buenos Aires. Il lui faudra près de dix ans, et cinquante-sept études, avant de trouver la bonne forme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Le général, bras levé et cape au vent, domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Inauguré en 1926, il retrouve le socle peuplé de Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir, plus conservatrice ou plus en mouvement selon les époques.
+En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 10]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. Sa tête est au Louvre, son corps à Athènes : on ne les a réunis qu'en 1936. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Ce « chat au miel », c'est Erasmo da Narni, un condottiere, chef de mercenaires, mort en 1443 au service de Venise. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Une statue équestre était réservée aux souverains : le Sénat de Venise a fait une exception. Donatello s'inspire de Marc Aurèle, mais son cavalier est un homme d'armes, cuirassé, l'épée au côté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Il se méfie pourtant : sous le sabot levé, une boule de bronze sert de point d'appui. Fêté à Padoue, il rentre à Florence, dit Vasari, de peur que les louanges lui fassent oublier son métier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Andrea del Verrocchio, à Venise, supprime la béquille : dans le *Colleoni*, le sabot se lève dans le vide, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Bartolomeo Colleoni, condottiere et capitaine général de Venise, lègue sa fortune à la République, à condition qu'on lui dresse une statue place Saint-Marc. Or les statues y sont interdites. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Venise place donc le cavalier devant la Scuola di San Marco, une autre « Saint-Marc ». Verrocchio meurt en 1488 avant la fonte : Alessandro Leopardi coule le bronze, et la statue est dressée en 1496. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Jean de Boulogne, dit Giambologna, né à Douai, en Flandre, termine en 1594 *Cosme Ier*, premier grand-duc de Toscane : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite pour *Ferdinand Ier*, fils de Cosme, d'après un projet du maître, qui meurt en 1608, l'année de l'inauguration. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]On raconte que le bronze vient de canons pris aux Turcs par les chevaliers de Saint-Étienne, l'ordre fondé par les Médicis contre les corsaires ; Ferdinand en porte la croix. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Piazza_SS_Annunziata_Firenze_Apr_2008.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Derrière le cheval, deux fontaines aux monstres marins, que Tacca avait d'abord conçues pour une statue de Ferdinand à Livourne : le grand-duc a droit à toute une mise en scène. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Francesco Mochi, venu de Toscane, élève en 1625 le monument d'Alexandre Farnèse, ce duc de Parme qui commanda les armées de l'Espagne en Flandre et prit Anvers en 1585. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Manteau et crinière au vent, le cheval semble sauvage : c'est l'élan du baroque, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Padre_e_figlio_nella_storia.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]tout le contraire de la sérénité du modèle florentin, et le bronze semble s'élancer. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Mochi a sculpté cinq ans plus tôt le fils d'Alexandre, Ranuccio, et ces deux cavaliers ont donné son nom à la place : la Piazza dei Cavalli, la place des Chevaux. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Philippe IV d'Espagne veut une statue plus prestigieuse que celle de son père, et Pietro Tacca, d'après un dessin de Velázquez, réalise un cheval cabré : seules les deux pattes arrière et, discrètement, la queue touchent le socle. [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]Sur le socle, le roi décore Velázquez, l'homme dont le dessin a servi de modèle ; mais la statue ne gagne la place d'Orient qu'en 1843. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Martin Desjardins, puis François Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]À Lyon, la statue de Desjardins, coulée en 1694, voyage sept ans par la Seine, la mer et le Rhône, et n'est inaugurée qu'en 1713, deux ans avant la mort du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Détruite en 1792, elle est refaite par Lemot en 1825. Selon une légende, il se serait tué d'avoir oublié les étriers : c'est faux, le roi monte simplement à la romaine, sans étriers. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol, où le Flamand John Michael Rysbrack habille à la romaine Guillaume III d'Orange. Coulée en 1733, la statue est dressée en 1736 sur Queen Square. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]La ville pensait d'abord à George II ; ses notables, partisans du Parlement, ont préféré Guillaume III. Évacuée à Badminton pendant la guerre, elle est revenue en 1948. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, le Danois Bertel Thorvaldsen représente le prince Józef Poniatowski, noyé dans l'Elster, à Leipzig, en 1813, trois jours après avoir été nommé maréchal de France par Napoléon. Il le sculpte en général romain presque nu, ce qui déplaît à beaucoup. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Surtout, après le soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Christian Daniel Rauch place Frédéric le Grand en uniforme, au-dessus d'un socle où défilent soixante-quatorze généraux, ministres et penseurs de son [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]règne. Démonté en 1950 par l'Allemagne de l'Est, il revient en 1980, quand Honecker se met à dire « Frédéric le Grand ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, l'Américain Thomas Crawford, installé à Rome, le place à cheval au sommet d'un monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Autour de lui, d'autres grandes figures de la Révolution virginienne, dont Jefferson et Patrick Henry. Les bronzes sont modelés à Rome, puis fondus à Munich avant de traverser l'Atlantique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Mais Crawford perd la vue en 1856 à cause d'un cancer de l'œil. Il meurt à Londres en 1857, avant que la statue soit dressée, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]En 1859, à Saint-Pétersbourg, Piotr Klodt va plus loin que Tacca : le cheval de Nicolas Ier ne touche le socle que par ses deux pattes arrière. On plaisante : Nicolas veut rattraper Pierre le Grand, mais la cathédrale Saint-Isaac l'en empêche. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Antoine-Louis Barye, le sculpteur des fauves, habille Napoléon en empereur romain et ses frères en toges, pour éviter les costumes d'époque. Le monument regardait la mer mais depuis 1969, il fait face à la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure, ce roi que Jeanne d'Arc a fait sacrer à Reims en 1429, et qui ne fera rien pour la sauver. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Emmanuel Frémiet met Jeanne en selle en 1874, place des Pyramides, là où elle fut blessée en 1429 : une paysanne devenue chef de guerre, en bronze doré, pour une France meurtrie par la défaite de 1870. Mécontent du cheval, il l'a discrètement fait remplacer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]Le peintre Jean-Léon Gérôme s'essaie aussi au bronze avec son *Bonaparte entrant au Caire*, en 1798, qui est présenté au Salon de 1897 puis acheté par l'État pour le jardin du Luxembourg, avec une patine colorée et dorée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]En 1899, Paolo Troubetzkoy, que Tolstoï aimait beaucoup, le montre à cheval. Il le modèle comme un écrivain en promenade, sans uniforme ni couronne. Ils étaient tous deux végétariens, Troubetzkoy refusait la viande en s'écriant : « Je ne mange pas de cadavre ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Auguste Bartholdi, père de la Liberté de New York et du Lion de Belfort, offre en 1903 à la France un héros dont personne ne connaît le visage : Vercingétorix, l'épée levée sur son cheval cabré, un Romain mort sous les sabots. Inauguré par Émile Combes. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Augustus Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la Victoire, précède le cheval, et le bronze est doré. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Son modèle, Hettie Anderson, une jeune femme noire, ne fut connue du public que dans les [image: https://commons.wikimedia.org/wiki/Special:FilePath/Sherman_gilded_jeh.JPG | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]années 1980. Onze ans séparent le projet de l'inauguration, où le sculpteur, très fragile, était présent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, Cyrus Dallin, né dans l'Utah, offre en 1908 un tout autre visage de l'Amérique : enfant, il côtoyait des petits Amérindiens, et il en garde ce cavalier sans arme, les bras ouverts vers le ciel. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Le cheval ne sert plus à la guerre mais à la prière. Fondue à Paris, la statue reçoit une médaille d'or au Salon, puis est installée devant le musée des Beaux-Arts de Boston en 1912. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Quand on a restauré le bronze, Dallin a exigé qu'on lui rende sa patine verte, qu'il préférait au brun d'origine. Le musée invite aujourd'hui des auteurs amérindiens à en discuter le sens. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Paolo Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. On surnomme aussitôt le monument « l'Hippopotame » ; sous les Soviets, on y grave « l'épouvantail en fonte ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Antoine Bourdelle, enfin, reçoit en 1913 la commande du monument au général Carlos María de Alvear, l'un des héros de l'indépendance argentine, à Buenos Aires. Il lui faudra près de dix ans, et cinquante-sept études, avant de trouver la bonne forme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Le général, bras levé et cape au vent, domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Inauguré en 1926, il retrouve le socle peuplé de Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir et de la société, plus conservatrice ou plus en mouvement selon les époques.
 [sortie: noir]</v>
       </c>
       <c r="D2" t="str">
-        <v>24/10/2026 14:04:38</v>
+        <v>24/10/2026 15:25:08</v>
       </c>
       <c r="E2" t="str">
         <v>Terminé</v>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -442,9 +442,28 @@
         <v>Terminé</v>
       </c>
     </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>sc.sub.fontaine</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Fontaine</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">[titre: Fontaines | | 3]
+[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg/1280px-I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]Pendant des siècles, une fontaine publique n'est pas un décor : c'est un service. Dans la civilisation romaine, les lacus sont des bassins de pierre rectangulaires avec une borne souvent adossée à un mur d'où l'eau jaillissait par une bouche sculptée. [image: https://upload.wikimedia.org/wikipedia/commons/5/5e/SEPTIZODIUM_Rome.jpg | Le Septizodium | enchaîné 10]Sous l'Empire apparaissent des nymphées, les bassins sont plus vastes et sont surmontés d'un édifice à colonne, orné de statues, toujours adossé, comme un vaste mur de scène. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG/1280px-Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG | Reconstitution de la maison des Vetii à Pompéi | enchaîné 10]Les fontaines centrales sont plutôt réservés à l'habitation privée, ornant atrium et péristyles. [image: https://upload.wikimedia.org/wikipedia/commons/9/91/Fontaine.medievale.png | Fontaine médiévale | enchaîné 10]Au Moyen-Age, à coté de fontaines qui reprennent le schéma de la fontaine publique adossée romaine, [image: https://upload.wikimedia.org/wikipedia/commons/d/d8/Fontaine.XIIIe.siecle.2.png | Fontaine du 13e siècle | enchaîné 10]les villes se dotent de fontaines de forme circulaire ou polygonale, avec une pile centrale sculptée de motifs religieux qui distribue l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Beblenheim-0003.jpg/960px-Beblenheim-0003.jpg | Fontaine gothique de Beblenheim | enchaîné 10]Les chiffres ont une grande importance dans la conception de leur bassin: le 6 des bassins hexagonaux renvoie au nombre de jour de la création, le 8 des bassins octogonaux, à la vie éternelle promise le 8e jour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Fontana_Maggiore%2C_Perugia.jpg/1280px-Fontana_Maggiore%2C_Perugia.jpg | Fontana Maggiore, Perugia | enchaîné 10]En Italie, à Pérouse, ce modèle se décline dans des grandes proportions qui dépassent le cadre religieux et proposent une vision encyclopédique: en 1278, la Fontana Maggiore de Nicola Pisano et son fils Giovanni est conçue comme un double bassin où les Pisano sculptent les mois de l'année, les arts libéraux, des scènes bibliques en bas-relief et ajoutent 24 statues en hommage à la Cité de Pérouse et à ses dirigeants. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | noir 5]Plus modestement et reprenant la tradition des fontaines bassins à la romaine, à Sienne, Jacopo della Quercia sculpte entre 1409 et 1419 les reliefs de la Fonte Gaia, mêlant scènes bibliques et mythes fondateurs de la ville. [image: https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | enchaîné 10]Ce nom, « fontaine joyeuse », date de 1342 : l'eau, amenée par vingt-cinq kilomètres de canalisations souterraines, arrive enfin sur la place du Campo, et les Siennois font la fête.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]À la Renaissance, le programme iconographqie des fontaines s'éloigne de la religion. Les jardins des grandes villas patriciennes s'ornent de fontaines centrales à la gloire du propriétaire: à  Florence, pour la villa de Castello, Niccolò Pericoli, dit le Tribolo, conçoit dès 1538, avec son assistant Pierino da Vinci, la fontaine d'Hercule et Antée, pour Cosme Ier de Médicis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG/960px-Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]Le bronze, de Bartolomeo Ammannati, montre Hercule étouffant Antée, dont la bouche crache l'eau : on y représente Cosme Ier triomphant de ses ennemis. Il a été déplacé depuis à la Petraia. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Même volonté de glorification politique en ville où, en 1565, pour les noces de l'héritier des Médicis, Bartolomeo Ammannati livre en hâte son Neptune sur la piazza della Signoria à Florence : inachevé, il est complété en stuc peint. Le dieu a le visage de Cosme Ier. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Le bloc de marbre avait été choisi par Baccio Bandinelli, mort en 1560. Michel-Ange, vieillard, aurait lancé à Ammannati : « Quel beau marbre tu as gâché ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Les Florentins le surnomment *il Biancone*, le grand blanc, et s'en servent comme lavoir : l'encre et le linge tachent le marbre presque dès le début. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, le cardinal Charles Borromée, légat du pape, fait ériger en 1566 une fontaine pour fêter l'élection de son oncle Pie IV : on rase tout un bâtiment pour lui faire place. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg/960px-1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Le Neptune de bronze est de Jean Bologne, un Flamand né à Douai, évincé du concours de Florence. Sa main tendue symbolise, dit-on, l'autorité du pape sur la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bologne_fontaine_neptune.jpg/1280px-Bologne_fontaine_neptune.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Quatre sirènes, dont les seins font jaillir l'eau, entourent le dieu. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Piazza_navona_0511-01.JPG/1280px-Piazza_navona_0511-01.JPG | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]À Rome, les papes remettent en service les anciens aqueducs. Place Navone, Giacomo della Porta dessine en 1575 la fontaine du More, bordée de tritons de Taddeo Landini, d'abord conçus pour la place du Peuple. [image: https://upload.wikimedia.org/wikipedia/commons/7/7f/Piazza_Navona%2C_Roma_-_fontana_fc07.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]En 1654, sur un dessin du Bernin, Giovanni Antonio Mari sculpte au centre le « More », aux prises avec un dauphin, qui donne son nom à la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Fontana_del_Moro_Piazza_Navona_Rome_04_2016_6563.jpg/1280px-Fontana_del_Moro_Piazza_Navona_Rome_04_2016_6563.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]Landini signe aussi les jeunes bronzes de la fontaine des Tortues : selon la légende, un duc ruiné par le jeu l'aurait fait construire en une nuit pour séduire un beau-père fortuné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Au XVIIe siècle, la fontaine devient théâtre. Au pied de l'escalier de la Trinité-des-Monts, Pietro Bernini sculpte, de 1627 à 1629, pour le pape Urbain VIII, la Barcaccia, une barque à demi coulée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Barcaccia_e_scalinata.jpg/1280px-Barcaccia_e_scalinata.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Selon la légende, une crue du Tibre aurait laissé une barque échouée sur la place en 1598. En vérité, l'eau de l'aqueduc manque de pression : il fallait enfoncer la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg/1280px-The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Le poète John Keats, mourant en 1821 dans la maison voisine, entendait son murmure : il demande pour épitaphe « Ci-gît celui dont le nom fut écrit dans l'eau ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Son fils, Gian Lorenzo Bernini, le Bernin, change d'échelle. Tenu à l'écart par le pape Innocent X, il voit sa maquette placée discrètement sur le passage du pontife, qui s'arrête, ébloui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]La fontaine des Quatre-Fleuves, inaugurée en 1651, dresse un obélisque sur un rocher percé, autour duquel quatre géants figurent les fleuves de quatre continents. Le Danube est d'Antonio Raggi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Le Nil a la tête voilée, dit-on, pour ne pas voir l'église de Borromini, rival du Bernin. C'est faux : la fontaine est achevée avant la façade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg/960px-Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]À Versailles, Louis XIV pousse plus loin encore le spectacle. Gaspard de Marsy sculpte, de 1668 à 1670, la déesse Latone implorant Jupiter contre les paysans qui l'insultent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Versailles_garden.JPG/1280px-Versailles_garden.JPG | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]Son frère Balthazar les change en grenouilles de plomb : on y lit souvent une allégorie de la Fronde, la révolte contre le jeune Louis XIV. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg/1280px-Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg | Château de Versailles | enchaîné 10]Mais Versailles manque d'eau. Le roi fait pomper la Seine par la machine de Marly dès 1684, et les jets ne s'ouvrent que devant lui, au fil de sa promenade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Au XVIIIe siècle, on dote les villes de nombreuse fontaines, pour assurer l'hygiène et la santé des habitants. Edme Bouchardon sculpte à Paris, de 1739 à 1745, la fontaine des Quatre-Saisons, rue de Grenelle, commandée par la Ville pour le quartier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Elle ressemble à un hôtel particulier : ses deux portes sont fausses, et seuls quatre masques de bronze révèlent sa fonction. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/4_saisons_vue_d%27ensembleG.jpg/1280px-4_saisons_vue_d%27ensembleG.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Voltaire s'en moque : trop de pierre pour si peu d'eau. Elle a coûté plus de cent trente mille livres, et son faible débit lui vaut le surnom de « la Trompeuse ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]À Vienne, sur le Neuer Markt, Georg Raphael Donner dresse en 1739 la fontaine de la Providence, commandée par la Ville et non par un noble, ce qui est rare à l'époque baroque. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Wien_-_Donnerbrunnen.JPG/1280px-Wien_-_Donnerbrunnen.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]Quatre figures de plomb évoquent des affluents du Danube : la Traun, l'Enns, l'Ybbs et la March. Les Viennois, déroutés par le mot « providentia », l'ont vite rebaptisée fontaine de Donner. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]En 1773, on retire les figures : une légende accuse la commission de chasteté de Marie-Thérèse. En vérité, le sculpteur chargé de les fondre les sauve. Elles reviennent en 1801. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Oceanus_%28Trevi_fountain%29.jpg/960px-Oceanus_%28Trevi_fountain%29.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]À Rome, la fontaine de Trevi naît d'une querelle : en 1730, le concours est gagné par un Florentin, Alessandro Galilei. Les Romains protestent, et le chantier échoit à Nicola Salvi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Fontana_di_Trevi_a_Roma.jpg/1280px-Fontana_di_Trevi_a_Roma.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Salvi meurt en 1751, à mi-chemin. Giuseppe Pannini achève l'œuvre en 1762 : l'Océan de Pietro Bracci, sur un char tiré par des chevaux de mer, s'adosse au palais comme à un décor. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Panorama_of_Trevi_fountain_2015.jpg/1280px-Panorama_of_Trevi_fountain_2015.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Selon la légende, Salvi cache derrière un grand vase l'enseigne d'un barbier qui le critiquait. Chaque jour, on y jette environ trois mille euros, pour l'association Caritas. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Au XIXe siècle, l'eau courante arrive dans les maisons, et la fontaine devient un monument plus décoratif qui veut promouvoir les valeurs universelles d'un continent au faîte de sa puissance. À Paris, Jean-Baptiste Carpeaux sculpte pour l'Observatoire quatre jeunes femmes qui portent le globe terrestre. [image: https://upload.wikimedia.org/wikipedia/commons/3/38/FontaineQuatrePartiesDuMonde02.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Elles figurent l'Europe, l'Asie, l'Afrique et l'Amérique. Le critique Jules Clarétie les juge d'abord maigres et malsaines, avant de changer d'avis après la mort du sculpteur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg/1280px-Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Emmanuel Frémiet sculpte les chevaux du bassin. Inaugurée en 1874, la fontaine est regardée de loin par un Carpeaux malade, qui meurt l'année suivante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Neptun_1a_2.jpg/1280px-Neptun_1a_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]À Berlin, Reinhold Begas place en 1891 un Neptune devant le château des Hohenzollern, sur la Schlossplatz : une vasque monumentale de dix-huit mètres de diamètre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Neptunbrunnen_B-Mitte_06-2017.jpg/1280px-Neptunbrunnen_B-Mitte_06-2017.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quatre femmes l'entourent, chacune avec la richesse de son fleuve : le Rhin, filet et raisin ; l'Elbe, les épis ; l'Oder, des chèvres ; la Vistule, aujourd'hui polonaise, du bois. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quand l'Allemagne de l'Est démolit le château, la fontaine est démontée en 1951. Elle ne revient qu'en 1969, entre l'église Sainte-Marie et l'hôtel de ville rouge. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Lyon_fontaine_bartholdi_congres.jpg/1280px-Lyon_fontaine_bartholdi_congres.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]À Lyon, Auguste Bartholdi, père de la statue de la Liberté, signe en 1892 la fontaine de la place des Terreaux : la France, en char tiré par quatre chevaux. [image: https://upload.wikimedia.org/wikipedia/commons/1/12/Lyon_1er_-_Fontaine_Bartholdi_-_Statue_et_bassin.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Les chevaux, qui figurent de grands fleuves, bondissent hors de l'eau et soufflent par les naseaux. Les ateliers de la statue de la Liberté ont travaillé ce monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Fontaine_Bartholdi_01.jpg/1280px-Fontaine_Bartholdi_01.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Bartholdi l'avait imaginée à vingt-trois ans pour Bordeaux, qui ne l'a jamais réalisée. Lyon l'achète cent mille francs en 1889, un prix qui le déçoit. [image: https://upload.wikimedia.org/wikipedia/commons/a/a3/Angel_of_Christian_Charity_Eros_Piccadilly_Circus_London_3.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]À Londres, la fontaine d'Éros, en 1893, n'a plus rien d'utilitaire : Alfred Gilbert y élève un mémorial à lord Shaftesbury, un philanthrope. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Ce n'est pas Éros, mais son frère Antéros. C'est la première sculpture coulée en aluminium, et son modèle, Angelo Colarossi, n'a que seize ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/MK17690_Piccadilly_Circus.jpg/1280px-MK17690_Piccadilly_Circus.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Le chantier coûte plus du double du devis : Gilbert s'endette, fait faillite en 1901 et s'exile à Bruges. Il ne reviendra qu'en 1926, et sera fait chevalier en 1932. [image: https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]À Munich, Adolf von Hildebrand, choisi après un concours à condition de s'installer à Munich, célèbre en 1895 l'arrivée de l'eau de source des montagnes, achevée en 1883. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG/1280px-Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]D'un côté, un jeune homme sur un cheval à queue de poisson s'apprête à lancer un rocher : la fureur des torrents. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/20220917_Wittelsbacher_Fountain_Munich.jpg/1280px-20220917_Wittelsbacher_Fountain_Munich.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]De l'autre, une amazone offre une coupe d'eau : la ressource domptée. Bombardée pendant la guerre, la fontaine est restaurée en 1952 par un élève de Hildebrand, Theodor Georgii. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]À Chicago, Lorado Taft fait couler, en 1913, l'eau de bassin en bassin, comme elle passe d'un Grand Lac à l'autre, du lac Supérieur jusqu'à l'Ontario. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/2014_Chicago_Art_Institute_01.jpg/1280px-2014_Chicago_Art_Institute_01.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]Cinq femmes de bronze figurent les cinq lacs. Leur nudité partielle nourrit, cette année-là, un débat à Chicago sur l'obscénité de l'art public. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg/1280px-Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg | Art Institute of Chicago | enchaîné 10]C'est la première commande du fonds d'un million de dollars de Benjamin Ferguson, dont le portrait en relief est caché depuis le déplacement de 1963. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Chicago%2C_Illinois_%282026%29_-_471.jpg/1280px-Chicago%2C_Illinois_%282026%29_-_471.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]Sa *Fontaine du Temps*, inaugurée en 1922, commémore un siècle de paix entre les États-Unis et la Grande-Bretagne depuis 1814. Un Temps encapuchonné y regarde passer cent figures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]D'après un poème d'Austin Dobson, le temps reste, c'est nous qui passons. Taft s'est glissé lui-même dans la procession, en blouse, la tête baissée. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]En vingt siècles, la fontaine est passée d'un simple service public chez les Romains, à un monument marqué par une forte symbolique religieuse au Moyen-âge, devenant plus politique à la Renaissance et à l'âge classique, puis, quand l'eau a gagné les maisons, à un monument qui exalte des valeurs universelles comme l'Amour et la Paix.
+[sortie: noir]</v>
+      </c>
+      <c r="D3" t="str">
+        <v>25/10/2026 07:25:28</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Terminé</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -451,14 +451,14 @@
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: Fontaines | | 3]
-[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg/1280px-I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]Pendant des siècles, une fontaine publique n'est pas un décor : c'est un service. Dans la civilisation romaine, les lacus sont des bassins de pierre rectangulaires avec une borne souvent adossée à un mur d'où l'eau jaillissait par une bouche sculptée. [image: https://upload.wikimedia.org/wikipedia/commons/5/5e/SEPTIZODIUM_Rome.jpg | Le Septizodium | enchaîné 10]Sous l'Empire apparaissent des nymphées, les bassins sont plus vastes et sont surmontés d'un édifice à colonne, orné de statues, toujours adossé, comme un vaste mur de scène. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG/1280px-Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG | Reconstitution de la maison des Vetii à Pompéi | enchaîné 10]Les fontaines centrales sont plutôt réservés à l'habitation privée, ornant atrium et péristyles. [image: https://upload.wikimedia.org/wikipedia/commons/9/91/Fontaine.medievale.png | Fontaine médiévale | enchaîné 10]Au Moyen-Age, à coté de fontaines qui reprennent le schéma de la fontaine publique adossée romaine, [image: https://upload.wikimedia.org/wikipedia/commons/d/d8/Fontaine.XIIIe.siecle.2.png | Fontaine du 13e siècle | enchaîné 10]les villes se dotent de fontaines de forme circulaire ou polygonale, avec une pile centrale sculptée de motifs religieux qui distribue l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Beblenheim-0003.jpg/960px-Beblenheim-0003.jpg | Fontaine gothique de Beblenheim | enchaîné 10]Les chiffres ont une grande importance dans la conception de leur bassin: le 6 des bassins hexagonaux renvoie au nombre de jour de la création, le 8 des bassins octogonaux, à la vie éternelle promise le 8e jour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Fontana_Maggiore%2C_Perugia.jpg/1280px-Fontana_Maggiore%2C_Perugia.jpg | Fontana Maggiore, Perugia | enchaîné 10]En Italie, à Pérouse, ce modèle se décline dans des grandes proportions qui dépassent le cadre religieux et proposent une vision encyclopédique: en 1278, la Fontana Maggiore de Nicola Pisano et son fils Giovanni est conçue comme un double bassin où les Pisano sculptent les mois de l'année, les arts libéraux, des scènes bibliques en bas-relief et ajoutent 24 statues en hommage à la Cité de Pérouse et à ses dirigeants. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | noir 5]Plus modestement et reprenant la tradition des fontaines bassins à la romaine, à Sienne, Jacopo della Quercia sculpte entre 1409 et 1419 les reliefs de la Fonte Gaia, mêlant scènes bibliques et mythes fondateurs de la ville. [image: https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | enchaîné 10]Ce nom, « fontaine joyeuse », date de 1342 : l'eau, amenée par vingt-cinq kilomètres de canalisations souterraines, arrive enfin sur la place du Campo, et les Siennois font la fête.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]À la Renaissance, le programme iconographqie des fontaines s'éloigne de la religion. Les jardins des grandes villas patriciennes s'ornent de fontaines centrales à la gloire du propriétaire: à  Florence, pour la villa de Castello, Niccolò Pericoli, dit le Tribolo, conçoit dès 1538, avec son assistant Pierino da Vinci, la fontaine d'Hercule et Antée, pour Cosme Ier de Médicis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG/960px-Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]Le bronze, de Bartolomeo Ammannati, montre Hercule étouffant Antée, dont la bouche crache l'eau : on y représente Cosme Ier triomphant de ses ennemis. Il a été déplacé depuis à la Petraia. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Même volonté de glorification politique en ville où, en 1565, pour les noces de l'héritier des Médicis, Bartolomeo Ammannati livre en hâte son Neptune sur la piazza della Signoria à Florence : inachevé, il est complété en stuc peint. Le dieu a le visage de Cosme Ier. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Le bloc de marbre avait été choisi par Baccio Bandinelli, mort en 1560. Michel-Ange, vieillard, aurait lancé à Ammannati : « Quel beau marbre tu as gâché ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Les Florentins le surnomment *il Biancone*, le grand blanc, et s'en servent comme lavoir : l'encre et le linge tachent le marbre presque dès le début. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, le cardinal Charles Borromée, légat du pape, fait ériger en 1566 une fontaine pour fêter l'élection de son oncle Pie IV : on rase tout un bâtiment pour lui faire place. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg/960px-1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Le Neptune de bronze est de Jean Bologne, un Flamand né à Douai, évincé du concours de Florence. Sa main tendue symbolise, dit-on, l'autorité du pape sur la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bologne_fontaine_neptune.jpg/1280px-Bologne_fontaine_neptune.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Quatre sirènes, dont les seins font jaillir l'eau, entourent le dieu. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Piazza_navona_0511-01.JPG/1280px-Piazza_navona_0511-01.JPG | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]À Rome, les papes remettent en service les anciens aqueducs. Place Navone, Giacomo della Porta dessine en 1575 la fontaine du More, bordée de tritons de Taddeo Landini, d'abord conçus pour la place du Peuple. [image: https://upload.wikimedia.org/wikipedia/commons/7/7f/Piazza_Navona%2C_Roma_-_fontana_fc07.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]En 1654, sur un dessin du Bernin, Giovanni Antonio Mari sculpte au centre le « More », aux prises avec un dauphin, qui donne son nom à la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Fontana_del_Moro_Piazza_Navona_Rome_04_2016_6563.jpg/1280px-Fontana_del_Moro_Piazza_Navona_Rome_04_2016_6563.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]Landini signe aussi les jeunes bronzes de la fontaine des Tortues : selon la légende, un duc ruiné par le jeu l'aurait fait construire en une nuit pour séduire un beau-père fortuné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Au XVIIe siècle, la fontaine devient théâtre. Au pied de l'escalier de la Trinité-des-Monts, Pietro Bernini sculpte, de 1627 à 1629, pour le pape Urbain VIII, la Barcaccia, une barque à demi coulée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Barcaccia_e_scalinata.jpg/1280px-Barcaccia_e_scalinata.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Selon la légende, une crue du Tibre aurait laissé une barque échouée sur la place en 1598. En vérité, l'eau de l'aqueduc manque de pression : il fallait enfoncer la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg/1280px-The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Le poète John Keats, mourant en 1821 dans la maison voisine, entendait son murmure : il demande pour épitaphe « Ci-gît celui dont le nom fut écrit dans l'eau ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Son fils, Gian Lorenzo Bernini, le Bernin, change d'échelle. Tenu à l'écart par le pape Innocent X, il voit sa maquette placée discrètement sur le passage du pontife, qui s'arrête, ébloui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]La fontaine des Quatre-Fleuves, inaugurée en 1651, dresse un obélisque sur un rocher percé, autour duquel quatre géants figurent les fleuves de quatre continents. Le Danube est d'Antonio Raggi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Le Nil a la tête voilée, dit-on, pour ne pas voir l'église de Borromini, rival du Bernin. C'est faux : la fontaine est achevée avant la façade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg/960px-Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]À Versailles, Louis XIV pousse plus loin encore le spectacle. Gaspard de Marsy sculpte, de 1668 à 1670, la déesse Latone implorant Jupiter contre les paysans qui l'insultent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Versailles_garden.JPG/1280px-Versailles_garden.JPG | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]Son frère Balthazar les change en grenouilles de plomb : on y lit souvent une allégorie de la Fronde, la révolte contre le jeune Louis XIV. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg/1280px-Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg | Château de Versailles | enchaîné 10]Mais Versailles manque d'eau. Le roi fait pomper la Seine par la machine de Marly dès 1684, et les jets ne s'ouvrent que devant lui, au fil de sa promenade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Au XVIIIe siècle, on dote les villes de nombreuse fontaines, pour assurer l'hygiène et la santé des habitants. Edme Bouchardon sculpte à Paris, de 1739 à 1745, la fontaine des Quatre-Saisons, rue de Grenelle, commandée par la Ville pour le quartier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Elle ressemble à un hôtel particulier : ses deux portes sont fausses, et seuls quatre masques de bronze révèlent sa fonction. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/4_saisons_vue_d%27ensembleG.jpg/1280px-4_saisons_vue_d%27ensembleG.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Voltaire s'en moque : trop de pierre pour si peu d'eau. Elle a coûté plus de cent trente mille livres, et son faible débit lui vaut le surnom de « la Trompeuse ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]À Vienne, sur le Neuer Markt, Georg Raphael Donner dresse en 1739 la fontaine de la Providence, commandée par la Ville et non par un noble, ce qui est rare à l'époque baroque. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Wien_-_Donnerbrunnen.JPG/1280px-Wien_-_Donnerbrunnen.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]Quatre figures de plomb évoquent des affluents du Danube : la Traun, l'Enns, l'Ybbs et la March. Les Viennois, déroutés par le mot « providentia », l'ont vite rebaptisée fontaine de Donner. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]En 1773, on retire les figures : une légende accuse la commission de chasteté de Marie-Thérèse. En vérité, le sculpteur chargé de les fondre les sauve. Elles reviennent en 1801. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Oceanus_%28Trevi_fountain%29.jpg/960px-Oceanus_%28Trevi_fountain%29.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]À Rome, la fontaine de Trevi naît d'une querelle : en 1730, le concours est gagné par un Florentin, Alessandro Galilei. Les Romains protestent, et le chantier échoit à Nicola Salvi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Fontana_di_Trevi_a_Roma.jpg/1280px-Fontana_di_Trevi_a_Roma.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Salvi meurt en 1751, à mi-chemin. Giuseppe Pannini achève l'œuvre en 1762 : l'Océan de Pietro Bracci, sur un char tiré par des chevaux de mer, s'adosse au palais comme à un décor. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Panorama_of_Trevi_fountain_2015.jpg/1280px-Panorama_of_Trevi_fountain_2015.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Selon la légende, Salvi cache derrière un grand vase l'enseigne d'un barbier qui le critiquait. Chaque jour, on y jette environ trois mille euros, pour l'association Caritas. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Au XIXe siècle, l'eau courante arrive dans les maisons, et la fontaine devient un monument plus décoratif qui veut promouvoir les valeurs universelles d'un continent au faîte de sa puissance. À Paris, Jean-Baptiste Carpeaux sculpte pour l'Observatoire quatre jeunes femmes qui portent le globe terrestre. [image: https://upload.wikimedia.org/wikipedia/commons/3/38/FontaineQuatrePartiesDuMonde02.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Elles figurent l'Europe, l'Asie, l'Afrique et l'Amérique. Le critique Jules Clarétie les juge d'abord maigres et malsaines, avant de changer d'avis après la mort du sculpteur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg/1280px-Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Emmanuel Frémiet sculpte les chevaux du bassin. Inaugurée en 1874, la fontaine est regardée de loin par un Carpeaux malade, qui meurt l'année suivante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Neptun_1a_2.jpg/1280px-Neptun_1a_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]À Berlin, Reinhold Begas place en 1891 un Neptune devant le château des Hohenzollern, sur la Schlossplatz : une vasque monumentale de dix-huit mètres de diamètre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Neptunbrunnen_B-Mitte_06-2017.jpg/1280px-Neptunbrunnen_B-Mitte_06-2017.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quatre femmes l'entourent, chacune avec la richesse de son fleuve : le Rhin, filet et raisin ; l'Elbe, les épis ; l'Oder, des chèvres ; la Vistule, aujourd'hui polonaise, du bois. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quand l'Allemagne de l'Est démolit le château, la fontaine est démontée en 1951. Elle ne revient qu'en 1969, entre l'église Sainte-Marie et l'hôtel de ville rouge. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Lyon_fontaine_bartholdi_congres.jpg/1280px-Lyon_fontaine_bartholdi_congres.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]À Lyon, Auguste Bartholdi, père de la statue de la Liberté, signe en 1892 la fontaine de la place des Terreaux : la France, en char tiré par quatre chevaux. [image: https://upload.wikimedia.org/wikipedia/commons/1/12/Lyon_1er_-_Fontaine_Bartholdi_-_Statue_et_bassin.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Les chevaux, qui figurent de grands fleuves, bondissent hors de l'eau et soufflent par les naseaux. Les ateliers de la statue de la Liberté ont travaillé ce monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Fontaine_Bartholdi_01.jpg/1280px-Fontaine_Bartholdi_01.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Bartholdi l'avait imaginée à vingt-trois ans pour Bordeaux, qui ne l'a jamais réalisée. Lyon l'achète cent mille francs en 1889, un prix qui le déçoit. [image: https://upload.wikimedia.org/wikipedia/commons/a/a3/Angel_of_Christian_Charity_Eros_Piccadilly_Circus_London_3.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]À Londres, la fontaine d'Éros, en 1893, n'a plus rien d'utilitaire : Alfred Gilbert y élève un mémorial à lord Shaftesbury, un philanthrope. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Ce n'est pas Éros, mais son frère Antéros. C'est la première sculpture coulée en aluminium, et son modèle, Angelo Colarossi, n'a que seize ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/MK17690_Piccadilly_Circus.jpg/1280px-MK17690_Piccadilly_Circus.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Le chantier coûte plus du double du devis : Gilbert s'endette, fait faillite en 1901 et s'exile à Bruges. Il ne reviendra qu'en 1926, et sera fait chevalier en 1932. [image: https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]À Munich, Adolf von Hildebrand, choisi après un concours à condition de s'installer à Munich, célèbre en 1895 l'arrivée de l'eau de source des montagnes, achevée en 1883. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG/1280px-Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]D'un côté, un jeune homme sur un cheval à queue de poisson s'apprête à lancer un rocher : la fureur des torrents. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/20220917_Wittelsbacher_Fountain_Munich.jpg/1280px-20220917_Wittelsbacher_Fountain_Munich.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]De l'autre, une amazone offre une coupe d'eau : la ressource domptée. Bombardée pendant la guerre, la fontaine est restaurée en 1952 par un élève de Hildebrand, Theodor Georgii. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]À Chicago, Lorado Taft fait couler, en 1913, l'eau de bassin en bassin, comme elle passe d'un Grand Lac à l'autre, du lac Supérieur jusqu'à l'Ontario. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/2014_Chicago_Art_Institute_01.jpg/1280px-2014_Chicago_Art_Institute_01.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]Cinq femmes de bronze figurent les cinq lacs. Leur nudité partielle nourrit, cette année-là, un débat à Chicago sur l'obscénité de l'art public. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg/1280px-Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg | Art Institute of Chicago | enchaîné 10]C'est la première commande du fonds d'un million de dollars de Benjamin Ferguson, dont le portrait en relief est caché depuis le déplacement de 1963. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Chicago%2C_Illinois_%282026%29_-_471.jpg/1280px-Chicago%2C_Illinois_%282026%29_-_471.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]Sa *Fontaine du Temps*, inaugurée en 1922, commémore un siècle de paix entre les États-Unis et la Grande-Bretagne depuis 1814. Un Temps encapuchonné y regarde passer cent figures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]D'après un poème d'Austin Dobson, le temps reste, c'est nous qui passons. Taft s'est glissé lui-même dans la procession, en blouse, la tête baissée. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]En vingt siècles, la fontaine est passée d'un simple service public chez les Romains, à un monument marqué par une forte symbolique religieuse au Moyen-âge, devenant plus politique à la Renaissance et à l'âge classique, puis, quand l'eau a gagné les maisons, à un monument qui exalte des valeurs universelles comme l'Amour et la Paix.
+[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg/1280px-I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]Pendant des siècles, une fontaine publique n'est pas un décor : c'est un service. Dans la civilisation romaine, les lacus sont [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg/960px-Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]des bassins de pierre rectangulaires avec une borne souvent adossée à un mur d'où l'eau jaillissait par une bouche sculptée. [image: https://upload.wikimedia.org/wikipedia/commons/5/5e/SEPTIZODIUM_Rome.jpg | Le Septizodium | enchaîné 10]Sous l'Empire apparaissent des nymphées, les bassins sont plus vastes et sont surmontés d'un édifice à colonne, orné de statues, toujours adossé, comme un vaste mur de scène. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG/1280px-Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG | Reconstitution de la maison des Vetii à Pompéi | enchaîné 10]Les fontaines centrales sont plutôt réservés à l'habitation privée, ornant atrium et péristyles. [image: https://upload.wikimedia.org/wikipedia/commons/9/91/Fontaine.medievale.png | Fontaine médiévale | enchaîné 10]Au Moyen-âge, à coté de fontaines qui reprennent le schéma de la fontaine publique adossée romaine, [image: https://upload.wikimedia.org/wikipedia/commons/d/d8/Fontaine.XIIIe.siecle.2.png | Fontaine du 13e siècle | enchaîné 10]les villes se dotent de fontaines de forme circulaire ou polygonale, avec une pile centrale sculptée de motifs religieux qui distribue l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Beblenheim-0003.jpg/960px-Beblenheim-0003.jpg | Fontaine gothique de Beblenheim | enchaîné 10]Les chiffres ont une grande importance dans la conception de leur bassin: le 6 des bassins hexagonaux renvoie au nombre de jour de la création, le 8 des bassins octogonaux, à la vie éternelle promise le 8e jour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Fontana_Maggiore%2C_Perugia.jpg/1280px-Fontana_Maggiore%2C_Perugia.jpg | Fontana Maggiore, Perugia | enchaîné 10]En Italie, à Pérouse, ce modèle se décline dans des grandes proportions qui dépassent le cadre religieux et proposent une vision encyclopédique: en 1278, la Fontana Maggiore de Nicola Pisano et son fils Giovanni est conçue comme un double bassin [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/35/La_Fontana_Maggiore_e_la_nebbia.jpg/1280px-La_Fontana_Maggiore_e_la_nebbia.jpg | Fontana Maggiore, Pérouse | enchaîné 10]où les Pisano sculptent les mois de l'année, les arts libéraux, des scènes bibliques en bas-relief et ajoutent 24 statues en hommage à la Cité de Pérouse et à ses dirigeants. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | noir 5]Plus modestement et reprenant la tradition des fontaines bassins à la romaine, à Sienne, Jacopo della Quercia sculpte entre 1409 et 1419 les reliefs de la Fonte Gaia, mêlant scènes bibliques et mythes fondateurs de la ville. [image: https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | enchaîné 10]Ce nom, « fontaine joyeuse », date de 1342 : l'eau, amenée par vingt-cinq kilomètres de canalisations souterraines, arrive enfin sur la place du Campo, et les Siennois font la fête.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]À la Renaissance, le programme iconographique des fontaines s'éloigne de la religion. Les jardins des grandes villas patriciennes s'ornent de fontaines centrales à la gloire du propriétaire: à  Florence, pour la villa de Castello, Niccolò Pericoli, dit le Tribolo, conçoit dès 1538, avec son assistant Pierino da Vinci, la fontaine d'Hercule et Antée, pour Cosme Ier de Médicis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG/960px-Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]Le bronze, de Bartolomeo Ammannati, montre Hercule étouffant Antée, dont la bouche crache l'eau : on y représente Cosme Ier triomphant de ses ennemis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Même volonté de glorification politique en ville où, en 1565, pour les noces de l'héritier des Médicis, Bartolomeo Ammannati livre en hâte son Neptune sur la piazza della Signoria à Florence : inachevé, il est complété en stuc peint. Le dieu a le visage de Cosme Ier. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Le bloc de marbre avait été choisi par Baccio Bandinelli, mort en 1560. Michel-Ange, vieillard, aurait lancé à Ammannati : « Quel beau marbre tu as gâché ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Les Florentins le surnomment *il Biancone*, le grand blanc, et s'en servent comme lavoir : l'encre et le linge tachent le marbre presque dès le début. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, le cardinal Charles Borromée, légat du pape, fait ériger en 1566 une fontaine pour fêter l'élection de son oncle Pie IV : on rase tout un bâtiment pour lui faire place. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg/960px-1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Le Neptune de bronze est de Jean Bologne, un Flamand né à Douai, évincé du concours de Florence. Sa main tendue symbolise, dit-on, l'autorité du pape sur la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bologne_fontaine_neptune.jpg/1280px-Bologne_fontaine_neptune.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Quatre sirènes, dont les seins font jaillir l'eau, entourent le dieu. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Piazza_navona_0511-01.JPG/1280px-Piazza_navona_0511-01.JPG | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]À Rome, les papes remettent en service les anciens aqueducs. Place Navone, Giacomo della Porta dessine en 1575 la fontaine du More, bordée de tritons de Taddeo Landini, d'abord conçus pour la place du Peuple. [image: https://upload.wikimedia.org/wikipedia/commons/7/7f/Piazza_Navona%2C_Roma_-_fontana_fc07.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]En 1654, sur un dessin du Bernin, Giovanni Antonio Mari sculpte au centre le « More », aux prises avec un dauphin, qui donne son nom à la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Fontana_delle_Tartarughe_Roma.jpg/960px-Fontana_delle_Tartarughe_Roma.jpg | La Fontaine des Tortues | enchaîné 10]Landini signe aussi les jeunes bronzes de la fontaine des Tortues : selon la légende, un duc ruiné par le jeu l'aurait fait construire en une nuit pour séduire un beau-père fortuné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Au XVIIe siècle, la fontaine devient théâtre. Au pied de l'escalier de la Trinité-des-Monts, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Barcaccia_e_scalinata.jpg/1280px-Barcaccia_e_scalinata.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Pietro Bernini sculpte, de 1627 à 1629, pour le pape Urbain VIII, la Barcaccia, une barque à demi coulée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg/1280px-The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Selon la légende, une crue du Tibre aurait laissé une barque échouée sur la place en 1598. En vérité, l'eau de l'aqueduc manque de pression : il fallait enfoncer la fontaine. . [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Son fils, Gian Lorenzo Bernini, le Bernin, change d'échelle. Tenu à l'écart par le pape Innocent X, il voit sa maquette placée discrètement sur le passage du pontife, qui s'arrête, ébloui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]La fontaine des Quatre-Fleuves, inaugurée en 1651, dresse un obélisque sur un rocher percé, autour duquel quatre géants figurent les fleuves de quatre continents. Le Danube est d'Antonio Raggi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Le Nil a la tête voilée, dit-on, pour ne pas voir l'église de Borromini, rival du Bernin. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg/960px-Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]À Versailles, Louis XIV pousse plus loin encore le spectacle. Gaspard de Marsy sculpte, de 1668 à 1670, la déesse Latone implorant Jupiter contre les paysans qui l'insultent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Versailles_garden.JPG/1280px-Versailles_garden.JPG | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]Son frère Balthazar les change en grenouilles de plomb : on y lit souvent une allégorie de la Fronde, la révolte contre le jeune Louis XIV et la vengeance de sa mère, Anne d'Autriche, contre les rebelles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg/1280px-Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg | Château de Versailles | enchaîné 10]Mais Versailles manque d'eau. Le roi fait pomper la Seine par la machine de Marly dès 1684, et les jets ne s'ouvrent que devant lui, au fil de sa promenade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Au XVIIIe siècle, on dote les villes de nombreuse fontaines, pour assurer l'hygiène et la santé des habitants. Edme Bouchardon sculpte à Paris, de 1739 à 1745, la fontaine des Quatre-Saisons, rue de Grenelle, commandée par la Ville pour le quartier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Elle ressemble à un hôtel particulier : ses deux portes sont fausses, et seuls quatre masques de bronze révèlent sa fonction. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/4_saisons_vue_d%27ensembleG.jpg/1280px-4_saisons_vue_d%27ensembleG.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Voltaire s'en moque : trop de pierre pour si peu d'eau. Elle a coûté plus de cent trente mille livres, et son faible débit lui vaut le surnom de « la Trompeuse ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]À Vienne, sur le Neuer Markt, Georg Raphael Donner dresse en 1739 la fontaine de la Providence, commandée par la Ville et non par un noble, ce qui est rare à l'époque baroque. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Wien_-_Donnerbrunnen.JPG/1280px-Wien_-_Donnerbrunnen.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]Quatre figures de plomb évoquent des affluents du Danube : la Traun, l'Enns, l'Ybbs et la March. Les Viennois, déroutés par le mot « providentia », l'ont vite rebaptisée fontaine de Donner. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]En 1773, on retire les figures : une légende accuse la commission de chasteté de Marie-Thérèse. En vérité, le sculpteur chargé de les fondre les sauve. Elles reviennent en 1801. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Oceanus_%28Trevi_fountain%29.jpg/960px-Oceanus_%28Trevi_fountain%29.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]À Rome, la fontaine de Trevi naît d'une querelle : en 1730, le concours est gagné par un Florentin, Alessandro Galilei. Les Romains protestent, et le chantier échoit à Nicola Salvi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Fontana_di_Trevi_a_Roma.jpg/1280px-Fontana_di_Trevi_a_Roma.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Salvi meurt en 1751, à mi-chemin. Giuseppe Pannini achève l'œuvre en 1762 : l'Océan de Pietro Bracci, sur un char tiré par des chevaux de mer, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Panorama_of_Trevi_fountain_2015.jpg/1280px-Panorama_of_Trevi_fountain_2015.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]s'adosse au palais comme à un décor.  Chaque jour, les touristes jettent dans son bassin environ trois mille euros, pour l'association Caritas. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Au XIXe siècle, l'eau courante arrive dans les maisons, et la fontaine devient un monument plus décoratif qui veut promouvoir les valeurs universelles d'un continent au faîte de sa puissance. À Paris, Jean-Baptiste Carpeaux sculpte pour l'Observatoire quatre jeunes femmes qui portent le globe terrestre. [image: https://upload.wikimedia.org/wikipedia/commons/3/38/FontaineQuatrePartiesDuMonde02.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Elles figurent l'Europe, l'Asie, l'Afrique et l'Amérique. Le critique Jules Clarétie les juge d'abord maigres et malsaines, avant de changer d'avis après la mort du sculpteur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg/1280px-Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Emmanuel Frémiet sculpte les chevaux du bassin. Inaugurée en 1874, la fontaine est regardée de loin par un Carpeaux malade, qui meurt l'année suivante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Neptun_1a_2.jpg/1280px-Neptun_1a_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]À Berlin, Reinhold Begas place en 1891 un Neptune devant le château des Hohenzollern, sur la Schlossplatz : une vasque monumentale de dix-huit mètres de diamètre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Neptunbrunnen_B-Mitte_06-2017.jpg/1280px-Neptunbrunnen_B-Mitte_06-2017.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quatre femmes l'entourent, chacune avec la richesse de son fleuve : le Rhin, filet et raisin ; l'Elbe, les épis ; l'Oder, des chèvres ; la Vistule, aujourd'hui polonaise, du bois. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quand l'Allemagne de l'Est démolit le château, la fontaine est démontée en 1951. Elle ne revient qu'en 1969, entre l'église Sainte-Marie et l'hôtel de ville rouge. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Lyon_fontaine_bartholdi_congres.jpg/1280px-Lyon_fontaine_bartholdi_congres.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]À Lyon, Auguste Bartholdi, père de la statue de la Liberté, signe en 1892 la fontaine de la place des Terreaux : la France, en char tiré par quatre chevaux. [image: https://upload.wikimedia.org/wikipedia/commons/1/12/Lyon_1er_-_Fontaine_Bartholdi_-_Statue_et_bassin.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Les chevaux, qui figurent de grands fleuves, bondissent hors de l'eau et soufflent par les naseaux. Les ateliers de la statue de la Liberté ont travaillé ce monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Fontaine_Bartholdi_01.jpg/1280px-Fontaine_Bartholdi_01.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Bartholdi l'avait imaginée à vingt-trois ans pour Bordeaux, qui ne l'a jamais réalisée. Lyon l'achète cent mille francs en 1889, un prix qui le déçoit. [image: https://upload.wikimedia.org/wikipedia/commons/a/a3/Angel_of_Christian_Charity_Eros_Piccadilly_Circus_London_3.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]À Londres, la fontaine d'Éros, en 1893, n'a plus rien d'utilitaire : Alfred Gilbert y élève un mémorial à lord Shaftesbury, un philanthrope. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]C'est la première sculpture coulée en aluminium, et son modèle, Angelo Colarossi, n'a que seize ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/MK17690_Piccadilly_Circus.jpg/1280px-MK17690_Piccadilly_Circus.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Le chantier coûte plus du double du devis : Gilbert s'endette, fait faillite en 1901 et s'exile à Bruges. Il ne reviendra qu'en 1926, et sera fait chevalier en 1932. [image: https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]À Munich, Adolf von Hildebrand, choisi après un concours à condition de s'installer à Munich, célèbre en 1895 l'arrivée de l'eau de source des montagnes, achevée en 1883. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG/1280px-Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]D'un côté, un jeune homme sur un cheval à queue de poisson s'apprête à lancer un rocher : la fureur des torrents. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/20220917_Wittelsbacher_Fountain_Munich.jpg/1280px-20220917_Wittelsbacher_Fountain_Munich.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]De l'autre, une amazone offre une coupe d'eau : la ressource domptée. Bombardée pendant la guerre, la fontaine est restaurée en 1952 par un élève de Hildebrand, Theodor Georgii. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]À Chicago, Lorado Taft fait couler, en 1913, l'eau de bassin en bassin, comme elle passe d'un Grand Lac à l'autre, du lac Supérieur jusqu'à l'Ontario. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/2014_Chicago_Art_Institute_01.jpg/1280px-2014_Chicago_Art_Institute_01.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]Cinq femmes de bronze figurent les cinq lacs. Leur nudité partielle nourrit, cette année-là, un débat à Chicago sur l'obscénité de l'art public. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg/1280px-Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg | Art Institute of Chicago | enchaîné 10]C'est la première commande du fonds d'un million de dollars de Benjamin Ferguson, dont le portrait en relief est caché depuis le déplacement de 1963. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Chicago%2C_Illinois_%282026%29_-_471.jpg/1280px-Chicago%2C_Illinois_%282026%29_-_471.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]Sa *Fontaine du Temps*, inaugurée en 1922, commémore un siècle de paix entre les États-Unis et la Grande-Bretagne depuis 1814. Un Temps encapuchonné y regarde passer cent figures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]D'après un poème d'Austin Dobson, le temps reste, c'est nous qui passons. Taft s'est glissé lui-même dans la procession, en blouse, la tête baissée. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]En vingt siècles, la fontaine est passée d'un simple service public chez les Romains, à un monument marqué par une forte symbolique religieuse au Moyen-âge, devenant plus politique à la Renaissance et à l'âge classique, puis, quand l'eau a gagné les maisons, à un monument qui exalte des valeurs universelles comme l'Amour et la Paix.
 [sortie: noir]</v>
       </c>
       <c r="D3" t="str">
-        <v>25/10/2026 07:25:28</v>
+        <v>25/10/2026 09:59:56</v>
       </c>
       <c r="E3" t="str">
-        <v>Terminé</v>
+        <v>En préparation</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -458,7 +458,7 @@
         <v>25/10/2026 09:59:56</v>
       </c>
       <c r="E3" t="str">
-        <v>En préparation</v>
+        <v>Terminé</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -451,11 +451,11 @@
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: Fontaines | | 3]
-[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg/1280px-I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]Pendant des siècles, une fontaine publique n'est pas un décor : c'est un service. Dans la civilisation romaine, les lacus sont [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg/960px-Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]des bassins de pierre rectangulaires avec une borne souvent adossée à un mur d'où l'eau jaillissait par une bouche sculptée. [image: https://upload.wikimedia.org/wikipedia/commons/5/5e/SEPTIZODIUM_Rome.jpg | Le Septizodium | enchaîné 10]Sous l'Empire apparaissent des nymphées, les bassins sont plus vastes et sont surmontés d'un édifice à colonne, orné de statues, toujours adossé, comme un vaste mur de scène. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG/1280px-Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG | Reconstitution de la maison des Vetii à Pompéi | enchaîné 10]Les fontaines centrales sont plutôt réservés à l'habitation privée, ornant atrium et péristyles. [image: https://upload.wikimedia.org/wikipedia/commons/9/91/Fontaine.medievale.png | Fontaine médiévale | enchaîné 10]Au Moyen-âge, à coté de fontaines qui reprennent le schéma de la fontaine publique adossée romaine, [image: https://upload.wikimedia.org/wikipedia/commons/d/d8/Fontaine.XIIIe.siecle.2.png | Fontaine du 13e siècle | enchaîné 10]les villes se dotent de fontaines de forme circulaire ou polygonale, avec une pile centrale sculptée de motifs religieux qui distribue l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Beblenheim-0003.jpg/960px-Beblenheim-0003.jpg | Fontaine gothique de Beblenheim | enchaîné 10]Les chiffres ont une grande importance dans la conception de leur bassin: le 6 des bassins hexagonaux renvoie au nombre de jour de la création, le 8 des bassins octogonaux, à la vie éternelle promise le 8e jour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Fontana_Maggiore%2C_Perugia.jpg/1280px-Fontana_Maggiore%2C_Perugia.jpg | Fontana Maggiore, Perugia | enchaîné 10]En Italie, à Pérouse, ce modèle se décline dans des grandes proportions qui dépassent le cadre religieux et proposent une vision encyclopédique: en 1278, la Fontana Maggiore de Nicola Pisano et son fils Giovanni est conçue comme un double bassin [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/35/La_Fontana_Maggiore_e_la_nebbia.jpg/1280px-La_Fontana_Maggiore_e_la_nebbia.jpg | Fontana Maggiore, Pérouse | enchaîné 10]où les Pisano sculptent les mois de l'année, les arts libéraux, des scènes bibliques en bas-relief et ajoutent 24 statues en hommage à la Cité de Pérouse et à ses dirigeants. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | noir 5]Plus modestement et reprenant la tradition des fontaines bassins à la romaine, à Sienne, Jacopo della Quercia sculpte entre 1409 et 1419 les reliefs de la Fonte Gaia, mêlant scènes bibliques et mythes fondateurs de la ville. [image: https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | enchaîné 10]Ce nom, « fontaine joyeuse », date de 1342 : l'eau, amenée par vingt-cinq kilomètres de canalisations souterraines, arrive enfin sur la place du Campo, et les Siennois font la fête.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]À la Renaissance, le programme iconographique des fontaines s'éloigne de la religion. Les jardins des grandes villas patriciennes s'ornent de fontaines centrales à la gloire du propriétaire: à  Florence, pour la villa de Castello, Niccolò Pericoli, dit le Tribolo, conçoit dès 1538, avec son assistant Pierino da Vinci, la fontaine d'Hercule et Antée, pour Cosme Ier de Médicis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG/960px-Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]Le bronze, de Bartolomeo Ammannati, montre Hercule étouffant Antée, dont la bouche crache l'eau : on y représente Cosme Ier triomphant de ses ennemis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Même volonté de glorification politique en ville où, en 1565, pour les noces de l'héritier des Médicis, Bartolomeo Ammannati livre en hâte son Neptune sur la piazza della Signoria à Florence : inachevé, il est complété en stuc peint. Le dieu a le visage de Cosme Ier. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Le bloc de marbre avait été choisi par Baccio Bandinelli, mort en 1560. Michel-Ange, vieillard, aurait lancé à Ammannati : « Quel beau marbre tu as gâché ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Les Florentins le surnomment *il Biancone*, le grand blanc, et s'en servent comme lavoir : l'encre et le linge tachent le marbre presque dès le début. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, le cardinal Charles Borromée, légat du pape, fait ériger en 1566 une fontaine pour fêter l'élection de son oncle Pie IV : on rase tout un bâtiment pour lui faire place. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg/960px-1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Le Neptune de bronze est de Jean Bologne, un Flamand né à Douai, évincé du concours de Florence. Sa main tendue symbolise, dit-on, l'autorité du pape sur la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bologne_fontaine_neptune.jpg/1280px-Bologne_fontaine_neptune.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Quatre sirènes, dont les seins font jaillir l'eau, entourent le dieu. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Piazza_navona_0511-01.JPG/1280px-Piazza_navona_0511-01.JPG | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]À Rome, les papes remettent en service les anciens aqueducs. Place Navone, Giacomo della Porta dessine en 1575 la fontaine du More, bordée de tritons de Taddeo Landini, d'abord conçus pour la place du Peuple. [image: https://upload.wikimedia.org/wikipedia/commons/7/7f/Piazza_Navona%2C_Roma_-_fontana_fc07.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]En 1654, sur un dessin du Bernin, Giovanni Antonio Mari sculpte au centre le « More », aux prises avec un dauphin, qui donne son nom à la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Fontana_delle_Tartarughe_Roma.jpg/960px-Fontana_delle_Tartarughe_Roma.jpg | La Fontaine des Tortues | enchaîné 10]Landini signe aussi les jeunes bronzes de la fontaine des Tortues : selon la légende, un duc ruiné par le jeu l'aurait fait construire en une nuit pour séduire un beau-père fortuné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Au XVIIe siècle, la fontaine devient théâtre. Au pied de l'escalier de la Trinité-des-Monts, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Barcaccia_e_scalinata.jpg/1280px-Barcaccia_e_scalinata.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Pietro Bernini sculpte, de 1627 à 1629, pour le pape Urbain VIII, la Barcaccia, une barque à demi coulée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg/1280px-The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Selon la légende, une crue du Tibre aurait laissé une barque échouée sur la place en 1598. En vérité, l'eau de l'aqueduc manque de pression : il fallait enfoncer la fontaine. . [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Son fils, Gian Lorenzo Bernini, le Bernin, change d'échelle. Tenu à l'écart par le pape Innocent X, il voit sa maquette placée discrètement sur le passage du pontife, qui s'arrête, ébloui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]La fontaine des Quatre-Fleuves, inaugurée en 1651, dresse un obélisque sur un rocher percé, autour duquel quatre géants figurent les fleuves de quatre continents. Le Danube est d'Antonio Raggi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Le Nil a la tête voilée, dit-on, pour ne pas voir l'église de Borromini, rival du Bernin. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg/960px-Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]À Versailles, Louis XIV pousse plus loin encore le spectacle. Gaspard de Marsy sculpte, de 1668 à 1670, la déesse Latone implorant Jupiter contre les paysans qui l'insultent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Versailles_garden.JPG/1280px-Versailles_garden.JPG | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]Son frère Balthazar les change en grenouilles de plomb : on y lit souvent une allégorie de la Fronde, la révolte contre le jeune Louis XIV et la vengeance de sa mère, Anne d'Autriche, contre les rebelles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg/1280px-Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg | Château de Versailles | enchaîné 10]Mais Versailles manque d'eau. Le roi fait pomper la Seine par la machine de Marly dès 1684, et les jets ne s'ouvrent que devant lui, au fil de sa promenade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Au XVIIIe siècle, on dote les villes de nombreuse fontaines, pour assurer l'hygiène et la santé des habitants. Edme Bouchardon sculpte à Paris, de 1739 à 1745, la fontaine des Quatre-Saisons, rue de Grenelle, commandée par la Ville pour le quartier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Elle ressemble à un hôtel particulier : ses deux portes sont fausses, et seuls quatre masques de bronze révèlent sa fonction. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/4_saisons_vue_d%27ensembleG.jpg/1280px-4_saisons_vue_d%27ensembleG.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Voltaire s'en moque : trop de pierre pour si peu d'eau. Elle a coûté plus de cent trente mille livres, et son faible débit lui vaut le surnom de « la Trompeuse ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]À Vienne, sur le Neuer Markt, Georg Raphael Donner dresse en 1739 la fontaine de la Providence, commandée par la Ville et non par un noble, ce qui est rare à l'époque baroque. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Wien_-_Donnerbrunnen.JPG/1280px-Wien_-_Donnerbrunnen.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]Quatre figures de plomb évoquent des affluents du Danube : la Traun, l'Enns, l'Ybbs et la March. Les Viennois, déroutés par le mot « providentia », l'ont vite rebaptisée fontaine de Donner. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]En 1773, on retire les figures : une légende accuse la commission de chasteté de Marie-Thérèse. En vérité, le sculpteur chargé de les fondre les sauve. Elles reviennent en 1801. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Oceanus_%28Trevi_fountain%29.jpg/960px-Oceanus_%28Trevi_fountain%29.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]À Rome, la fontaine de Trevi naît d'une querelle : en 1730, le concours est gagné par un Florentin, Alessandro Galilei. Les Romains protestent, et le chantier échoit à Nicola Salvi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Fontana_di_Trevi_a_Roma.jpg/1280px-Fontana_di_Trevi_a_Roma.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Salvi meurt en 1751, à mi-chemin. Giuseppe Pannini achève l'œuvre en 1762 : l'Océan de Pietro Bracci, sur un char tiré par des chevaux de mer, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Panorama_of_Trevi_fountain_2015.jpg/1280px-Panorama_of_Trevi_fountain_2015.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]s'adosse au palais comme à un décor.  Chaque jour, les touristes jettent dans son bassin environ trois mille euros, pour l'association Caritas. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Au XIXe siècle, l'eau courante arrive dans les maisons, et la fontaine devient un monument plus décoratif qui veut promouvoir les valeurs universelles d'un continent au faîte de sa puissance. À Paris, Jean-Baptiste Carpeaux sculpte pour l'Observatoire quatre jeunes femmes qui portent le globe terrestre. [image: https://upload.wikimedia.org/wikipedia/commons/3/38/FontaineQuatrePartiesDuMonde02.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Elles figurent l'Europe, l'Asie, l'Afrique et l'Amérique. Le critique Jules Clarétie les juge d'abord maigres et malsaines, avant de changer d'avis après la mort du sculpteur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg/1280px-Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Emmanuel Frémiet sculpte les chevaux du bassin. Inaugurée en 1874, la fontaine est regardée de loin par un Carpeaux malade, qui meurt l'année suivante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Neptun_1a_2.jpg/1280px-Neptun_1a_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]À Berlin, Reinhold Begas place en 1891 un Neptune devant le château des Hohenzollern, sur la Schlossplatz : une vasque monumentale de dix-huit mètres de diamètre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Neptunbrunnen_B-Mitte_06-2017.jpg/1280px-Neptunbrunnen_B-Mitte_06-2017.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quatre femmes l'entourent, chacune avec la richesse de son fleuve : le Rhin, filet et raisin ; l'Elbe, les épis ; l'Oder, des chèvres ; la Vistule, aujourd'hui polonaise, du bois. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quand l'Allemagne de l'Est démolit le château, la fontaine est démontée en 1951. Elle ne revient qu'en 1969, entre l'église Sainte-Marie et l'hôtel de ville rouge. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Lyon_fontaine_bartholdi_congres.jpg/1280px-Lyon_fontaine_bartholdi_congres.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]À Lyon, Auguste Bartholdi, père de la statue de la Liberté, signe en 1892 la fontaine de la place des Terreaux : la France, en char tiré par quatre chevaux. [image: https://upload.wikimedia.org/wikipedia/commons/1/12/Lyon_1er_-_Fontaine_Bartholdi_-_Statue_et_bassin.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Les chevaux, qui figurent de grands fleuves, bondissent hors de l'eau et soufflent par les naseaux. Les ateliers de la statue de la Liberté ont travaillé ce monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Fontaine_Bartholdi_01.jpg/1280px-Fontaine_Bartholdi_01.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Bartholdi l'avait imaginée à vingt-trois ans pour Bordeaux, qui ne l'a jamais réalisée. Lyon l'achète cent mille francs en 1889, un prix qui le déçoit. [image: https://upload.wikimedia.org/wikipedia/commons/a/a3/Angel_of_Christian_Charity_Eros_Piccadilly_Circus_London_3.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]À Londres, la fontaine d'Éros, en 1893, n'a plus rien d'utilitaire : Alfred Gilbert y élève un mémorial à lord Shaftesbury, un philanthrope. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]C'est la première sculpture coulée en aluminium, et son modèle, Angelo Colarossi, n'a que seize ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/MK17690_Piccadilly_Circus.jpg/1280px-MK17690_Piccadilly_Circus.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Le chantier coûte plus du double du devis : Gilbert s'endette, fait faillite en 1901 et s'exile à Bruges. Il ne reviendra qu'en 1926, et sera fait chevalier en 1932. [image: https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]À Munich, Adolf von Hildebrand, choisi après un concours à condition de s'installer à Munich, célèbre en 1895 l'arrivée de l'eau de source des montagnes, achevée en 1883. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG/1280px-Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]D'un côté, un jeune homme sur un cheval à queue de poisson s'apprête à lancer un rocher : la fureur des torrents. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/20220917_Wittelsbacher_Fountain_Munich.jpg/1280px-20220917_Wittelsbacher_Fountain_Munich.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]De l'autre, une amazone offre une coupe d'eau : la ressource domptée. Bombardée pendant la guerre, la fontaine est restaurée en 1952 par un élève de Hildebrand, Theodor Georgii. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]À Chicago, Lorado Taft fait couler, en 1913, l'eau de bassin en bassin, comme elle passe d'un Grand Lac à l'autre, du lac Supérieur jusqu'à l'Ontario. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/2014_Chicago_Art_Institute_01.jpg/1280px-2014_Chicago_Art_Institute_01.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]Cinq femmes de bronze figurent les cinq lacs. Leur nudité partielle nourrit, cette année-là, un débat à Chicago sur l'obscénité de l'art public. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg/1280px-Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg | Art Institute of Chicago | enchaîné 10]C'est la première commande du fonds d'un million de dollars de Benjamin Ferguson, dont le portrait en relief est caché depuis le déplacement de 1963. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Chicago%2C_Illinois_%282026%29_-_471.jpg/1280px-Chicago%2C_Illinois_%282026%29_-_471.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]Sa *Fontaine du Temps*, inaugurée en 1922, commémore un siècle de paix entre les États-Unis et la Grande-Bretagne depuis 1814. Un Temps encapuchonné y regarde passer cent figures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]D'après un poème d'Austin Dobson, le temps reste, c'est nous qui passons. Taft s'est glissé lui-même dans la procession, en blouse, la tête baissée. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]En vingt siècles, la fontaine est passée d'un simple service public chez les Romains, à un monument marqué par une forte symbolique religieuse au Moyen-âge, devenant plus politique à la Renaissance et à l'âge classique, puis, quand l'eau a gagné les maisons, à un monument qui exalte des valeurs universelles comme l'Amour et la Paix.
+[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg/1280px-I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]Pendant des siècles, une fontaine publique n'est pas un décor : c'est un service. Dans la civilisation romaine, les lacus sont [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg/960px-Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]des bassins de pierre rectangulaires avec une borne souvent adossée à un mur d'où l'eau jaillit par une bouche sculptée. [image: https://upload.wikimedia.org/wikipedia/commons/5/5e/SEPTIZODIUM_Rome.jpg | Le Septizodium | enchaîné 10]Sous l'Empire apparaissent des nymphées, les bassins sont plus vastes et sont surmontés d'un édifice à colonne, orné de statues, toujours adossé, comme un vaste mur de scène. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG/1280px-Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG | Reconstitution de la maison des Vetii à Pompéi | enchaîné 10]Les fontaines centrales sont plutôt réservés à l'habitation privée, ornant atrium et péristyles. [image: https://upload.wikimedia.org/wikipedia/commons/9/91/Fontaine.medievale.png | Fontaine médiévale | enchaîné 10]Au Moyen-âge, à coté de fontaines qui reprennent le schéma de la fontaine publique adossée romaine, [image: https://upload.wikimedia.org/wikipedia/commons/d/d8/Fontaine.XIIIe.siecle.2.png | Fontaine du 13e siècle | enchaîné 10]les villes se dotent de fontaines de forme circulaire ou polygonale, avec une pile centrale sculptée de motifs religieux qui distribue l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Beblenheim-0003.jpg/960px-Beblenheim-0003.jpg | Fontaine gothique de Beblenheim | enchaîné 10]Les chiffres ont une grande importance dans la conception de leur bassin: le 6 des bassins hexagonaux renvoie au nombre de jour de la création, le 8 des bassins octogonaux, à la vie éternelle promise le 8e jour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Fontana_Maggiore%2C_Perugia.jpg/1280px-Fontana_Maggiore%2C_Perugia.jpg | Fontana Maggiore, Perugia | enchaîné 10]En Italie, à Pérouse, ce modèle se décline dans des grandes proportions qui dépassent le cadre religieux et proposent une vision encyclopédique: en 1278, la Fontana Maggiore de Nicola Pisano et son fils Giovanni est conçue comme un double bassin [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/35/La_Fontana_Maggiore_e_la_nebbia.jpg/1280px-La_Fontana_Maggiore_e_la_nebbia.jpg | Fontana Maggiore, Pérouse | enchaîné 10]où les Pisano sculptent les mois de l'année, les arts libéraux, des scènes bibliques en bas-relief et ajoutent 24 statues en hommage à la Cité de Pérouse et à ses dirigeants. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | noir 5]Plus modestement et reprenant la tradition des fontaines bassins à la romaine, à Sienne, Jacopo della Quercia sculpte entre 1409 et 1419 les reliefs de la Fonte Gaia, mêlant scènes bibliques et mythes fondateurs de la ville. [image: https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | enchaîné 10]Ce nom, « fontaine joyeuse », date de 1342 : l'eau, amenée par vingt-cinq kilomètres de canalisations souterraines, arrive enfin sur la place du Campo, et les Siennois font la fête.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]À la Renaissance, le programme iconographique des fontaines s'éloigne de la religion. Les jardins des grandes villas patriciennes s'ornent de fontaines centrales à la gloire du propriétaire: à  Florence, pour la villa de Castello, Niccolò Pericoli, dit le Tribolo, conçoit dès 1538, avec son assistant Pierino da Vinci, la fontaine d'Hercule et Antée, pour Cosme Ier de Médicis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG/960px-Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]Le bronze, de Bartolomeo Ammannati, montre Hercule étouffant Antée, dont la bouche crache l'eau : on y représente Cosme Ier triomphant de ses ennemis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Même volonté de glorification politique en ville où, en 1565, pour les noces de l'héritier des Médicis, Bartolomeo Ammannati livre en hâte son Neptune sur la piazza della Signoria à Florence : inachevé, il est complété en stuc peint. Le dieu a le visage de Cosme Ier. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Le bloc de marbre avait été choisi par Baccio Bandinelli, mort en 1560. Michel-Ange, vieillard, aurait lancé à Ammannati : « Quel beau marbre tu as gâché ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Les Florentins le surnomment *il Biancone*, le grand blanc, et s'en servent comme lavoir : l'encre et le linge tachent le marbre presque dès le début. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, le cardinal Charles Borromée, légat du pape, fait ériger en 1566 une fontaine pour fêter l'élection de son oncle Pie IV : on rase tout un bâtiment pour lui faire place. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg/960px-1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Le Neptune de bronze est de Jean Bologne, un Flamand né à Douai, évincé du concours de Florence. Sa main tendue symbolise, dit-on, l'autorité du pape sur la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bologne_fontaine_neptune.jpg/1280px-Bologne_fontaine_neptune.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Quatre sirènes, dont les seins font jaillir l'eau, entourent le dieu. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Piazza_navona_0511-01.JPG/1280px-Piazza_navona_0511-01.JPG | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]À Rome, les papes remettent en service les anciens aqueducs. Place Navone, Giacomo della Porta dessine en 1575 la fontaine du More, bordée de tritons de Taddeo Landini, d'abord conçus pour la place du Peuple. [image: https://upload.wikimedia.org/wikipedia/commons/7/7f/Piazza_Navona%2C_Roma_-_fontana_fc07.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]En 1654, sur un dessin du Bernin, Giovanni Antonio Mari sculpte au centre le « More », aux prises avec un dauphin, qui donne son nom à la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Fontana_delle_Tartarughe_Roma.jpg/960px-Fontana_delle_Tartarughe_Roma.jpg | La Fontaine des Tortues | enchaîné 10]Landini signe aussi les jeunes bronzes de la fontaine des Tortues : selon la légende, un duc ruiné par le jeu l'aurait fait construire en une nuit pour séduire un beau-père fortuné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Au XVIIe siècle, la fontaine devient théâtre. Au pied de l'escalier de la Trinité-des-Monts, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Barcaccia_e_scalinata.jpg/1280px-Barcaccia_e_scalinata.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Pietro Bernini sculpte, de 1627 à 1629, pour le pape Urbain VIII, la Barcaccia, une barque à demi coulée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg/1280px-The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Selon la légende, une crue du Tibre aurait laissé une barque échouée sur la place en 1598. En vérité, l'eau de l'aqueduc manque de pression : il fallait enfoncer la fontaine. . [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Son fils, Gian Lorenzo Bernini, le Bernin, change d'échelle. Tenu à l'écart par le pape Innocent X, il voit sa maquette placée discrètement sur le passage du pontife, qui s'arrête, ébloui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]La fontaine des Quatre-Fleuves, inaugurée en 1651, dresse un obélisque sur un rocher percé, autour duquel quatre géants figurent les fleuves de quatre continents. Le Danube est d'Antonio Raggi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Le Nil a la tête voilée, dit-on, pour ne pas voir l'église de Borromini, rival du Bernin. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg/960px-Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]À Versailles, Louis XIV pousse plus loin encore le spectacle. Gaspard de Marsy sculpte, de 1668 à 1670, la déesse Latone implorant Jupiter contre les paysans qui l'insultent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Versailles_garden.JPG/1280px-Versailles_garden.JPG | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]Son frère Balthazar les change en grenouilles de plomb : on y lit souvent une allégorie de la Fronde, la révolte contre le jeune Louis XIV et la vengeance de sa mère, Anne d'Autriche, contre les rebelles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg/1280px-Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg | Château de Versailles | enchaîné 10]Mais Versailles manque d'eau. Le roi fait pomper la Seine par la machine de Marly dès 1684, et les jets ne s'ouvrent que devant lui, au fil de sa promenade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Au XVIIIe siècle, on dote les villes de nombreuse fontaines, pour assurer l'hygiène et la santé des habitants. Edme Bouchardon sculpte à Paris, de 1739 à 1745, la fontaine des Quatre-Saisons, rue de Grenelle, commandée par la Ville pour le quartier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Elle ressemble à un hôtel particulier : ses deux portes sont fausses, et seuls quatre masques de bronze révèlent sa fonction. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/4_saisons_vue_d%27ensembleG.jpg/1280px-4_saisons_vue_d%27ensembleG.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Voltaire s'en moque : trop de pierre pour si peu d'eau. Elle a coûté plus de cent trente mille livres, et son faible débit lui vaut le surnom de « la Trompeuse ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]À Vienne, sur le Neuer Markt, Georg Raphael Donner dresse en 1739 la fontaine de la Providence, commandée par la Ville et non par un noble, ce qui est rare à l'époque baroque. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Wien_-_Donnerbrunnen.JPG/1280px-Wien_-_Donnerbrunnen.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]Quatre figures de plomb évoquent des affluents du Danube : la Traun, l'Enns, l'Ybbs et la March. Les Viennois, déroutés par le mot « providentia », l'ont vite rebaptisée fontaine de Donner. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]En 1773, on retire les figures : une légende accuse la commission de chasteté de Marie-Thérèse. En vérité, le sculpteur chargé de les fondre les sauve. Elles reviennent en 1801. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Oceanus_%28Trevi_fountain%29.jpg/960px-Oceanus_%28Trevi_fountain%29.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]À Rome, la fontaine de Trevi naît d'une querelle : en 1730, le concours est gagné par un Florentin, Alessandro Galilei. Les Romains protestent, et le chantier échoit à Nicola Salvi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Fontana_di_Trevi_a_Roma.jpg/1280px-Fontana_di_Trevi_a_Roma.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Salvi meurt en 1751, à mi-chemin. Giuseppe Pannini achève l'œuvre en 1762 : l'Océan de Pietro Bracci, sur un char tiré par des chevaux de mer, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Panorama_of_Trevi_fountain_2015.jpg/1280px-Panorama_of_Trevi_fountain_2015.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]s'adosse au palais comme à un décor.  Chaque jour, les touristes jettent dans son bassin environ trois mille euros, pour l'association Caritas. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Au XIXe siècle, l'eau courante arrive dans les maisons, et la fontaine devient un monument plus décoratif qui veut promouvoir les valeurs universelles d'un continent au faîte de sa puissance. À Paris, Jean-Baptiste Carpeaux sculpte pour l'Observatoire quatre jeunes femmes qui portent le globe terrestre. [image: https://upload.wikimedia.org/wikipedia/commons/3/38/FontaineQuatrePartiesDuMonde02.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Elles figurent l'Europe, l'Asie, l'Afrique et l'Amérique. Le critique Jules Clarétie les juge d'abord maigres et malsaines, avant de changer d'avis après la mort du sculpteur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg/1280px-Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Emmanuel Frémiet sculpte les chevaux du bassin. Inaugurée en 1874, la fontaine est regardée de loin par un Carpeaux malade, qui meurt l'année suivante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Neptun_1a_2.jpg/1280px-Neptun_1a_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]À Berlin, Reinhold Begas place en 1891 un Neptune devant le château des Hohenzollern, sur la Schlossplatz : une vasque monumentale de dix-huit mètres de diamètre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Neptunbrunnen_B-Mitte_06-2017.jpg/1280px-Neptunbrunnen_B-Mitte_06-2017.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quatre femmes l'entourent, chacune avec la richesse de son fleuve : le Rhin, filet et raisin ; l'Elbe, les épis ; l'Oder, des chèvres ; la Vistule, aujourd'hui polonaise, du bois. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quand l'Allemagne de l'Est démolit le château, la fontaine est démontée en 1951. Elle ne revient qu'en 1969, entre l'église Sainte-Marie et l'hôtel de ville rouge. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Lyon_fontaine_bartholdi_congres.jpg/1280px-Lyon_fontaine_bartholdi_congres.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]À Lyon, Auguste Bartholdi, père de la statue de la Liberté, signe en 1892 la fontaine de la place des Terreaux : la France, en char tiré par quatre chevaux. [image: https://upload.wikimedia.org/wikipedia/commons/1/12/Lyon_1er_-_Fontaine_Bartholdi_-_Statue_et_bassin.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Les chevaux, qui figurent de grands fleuves, bondissent hors de l'eau et soufflent par les naseaux. Les ateliers de la statue de la Liberté ont travaillé ce monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Fontaine_Bartholdi_01.jpg/1280px-Fontaine_Bartholdi_01.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Bartholdi l'avait imaginée à vingt-trois ans pour Bordeaux, qui ne l'a jamais réalisée. Lyon l'achète cent mille francs en 1889, un prix qui le déçoit. [image: https://upload.wikimedia.org/wikipedia/commons/a/a3/Angel_of_Christian_Charity_Eros_Piccadilly_Circus_London_3.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]À Londres, la fontaine d'Éros, en 1893, n'a plus rien d'utilitaire : Alfred Gilbert y élève un mémorial à lord Shaftesbury, un philanthrope. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]C'est la première sculpture coulée en aluminium, et son modèle, Angelo Colarossi, n'a que seize ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/MK17690_Piccadilly_Circus.jpg/1280px-MK17690_Piccadilly_Circus.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Le chantier coûte plus du double du devis : Gilbert s'endette, fait faillite en 1901 et s'exile à Bruges. Il ne reviendra qu'en 1926, et sera fait chevalier en 1932. [image: https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]À Munich, Adolf von Hildebrand, choisi après un concours à condition de s'installer à Munich, célèbre en 1895 l'arrivée de l'eau de source des montagnes, achevée en 1883. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG/1280px-Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]D'un côté, un jeune homme sur un cheval à queue de poisson s'apprête à lancer un rocher : la fureur des torrents. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/20220917_Wittelsbacher_Fountain_Munich.jpg/1280px-20220917_Wittelsbacher_Fountain_Munich.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]De l'autre, une amazone offre une coupe d'eau : la ressource domptée. Bombardée pendant la guerre, la fontaine est restaurée en 1952 par un élève de Hildebrand, Theodor Georgii. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]À Chicago, Lorado Taft fait couler, en 1913, l'eau de bassin en bassin, comme elle passe d'un Grand Lac à l'autre, du lac Supérieur jusqu'à l'Ontario. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/2014_Chicago_Art_Institute_01.jpg/1280px-2014_Chicago_Art_Institute_01.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]Cinq femmes de bronze figurent les cinq lacs. Leur nudité partielle nourrit, cette année-là, un débat à Chicago sur l'obscénité de l'art public. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg/1280px-Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg | Art Institute of Chicago | enchaîné 10]C'est la première commande du fonds d'un million de dollars de Benjamin Ferguson, dont le portrait en relief est caché depuis le déplacement de 1963. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Chicago%2C_Illinois_%282026%29_-_471.jpg/1280px-Chicago%2C_Illinois_%282026%29_-_471.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]Sa *Fontaine du Temps*, inaugurée en 1922, commémore un siècle de paix entre les États-Unis et la Grande-Bretagne depuis 1814. Un Temps encapuchonné y regarde passer cent figures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]D'après un poème d'Austin Dobson, le temps reste, c'est nous qui passons. Taft s'est glissé lui-même dans la procession, en blouse, la tête baissée. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]En vingt siècles, la fontaine est passée d'un simple service public chez les Romains, à un monument marqué par une forte symbolique religieuse au Moyen-âge, devenant plus politique à la Renaissance et à l'âge classique, puis, quand l'eau a gagné les maisons, à un monument qui exalte des valeurs universelles comme l'Amour et la Paix.
 [sortie: noir]</v>
       </c>
       <c r="D3" t="str">
-        <v>25/10/2026 09:59:56</v>
+        <v>25/10/2026 15:34:55</v>
       </c>
       <c r="E3" t="str">
         <v>Terminé</v>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -461,9 +461,28 @@
         <v>Terminé</v>
       </c>
     </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>sc.nature.funeraire</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Monument funéraire</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">[titre: L'évolution du monument funéraire | | 5]
+En [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg | Della Quercia, Tombeau d’Ilaria del Carretto, Lucques, 1406 | noir 10]Occident, la forme du tombeau change avec la façon dont chaque époque pense la mort. Au Moyen-âge, la tombe porte un gisant : le défunt, couché sur un sarcophage, les mains jointes, attend la résurrection. Dès le milieu du XIVe siècle, il ferme les yeux et semble dormir. À Lucques, Jacopo della Quercia sculpte en 1406 Ilaria del Carretto, morte à vingt-six ans, un chien à ses pieds, symbole de fidélité. Elle n'a pourtant jamais reposé dans ce sarcophage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Le_Transi_de_Ren%C3%A9_de_Chalon_%28Ligier_Richier%29.jpg/1280px-Le_Transi_de_Ren%C3%A9_de_Chalon_%28Ligier_Richier%29.jpg | Richier, Le Transi de René de Chalon, Bar-le-Duc, 1545-1547 | enchaîné 10]À la fin du XIVe siècle apparaît le transi : non plus un dormeur serein, mais un cadavre réaliste, nu, parfois décharné, qui rappelle que la vie est brève. À Bar-le-Duc, Ligier Richier sculpte vers 1547 René de Chalon, mort à vingt-cinq ans au siège de Saint-Dizier : écorché, debout, il tend son propre cœur vers le ciel. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG | Rossellino, Tombeau de Leonardo Bruni, Florence, 1445-1450 | enchaîné 10]À la Renaissance, on retrouve le vocabulaire de l'Antiquité. À Florence, Bernardo Rossellino sculpte vers 1445 le tombeau de Leonardo Bruni : sous une arcade en plein cintre, entre deux pilastres, le gisant repose sur un lit funèbre que deux Victoires ailées encadrent. À ses funérailles, on avait posé son *Histoire de Florence* sur sa poitrine : l'effigie la tient encore. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Santa_Maria_del_Popolo_Presbyterium_Grabmal_Ascanio_Sforza.JPG/960px-Santa_Maria_del_Popolo_Presbyterium_Grabmal_Ascanio_Sforza.JPG | Sansovino, Tombeau d’Ascanio Sforza, Rome, 1505-1507 | enchaîné 10]À Rome, Andrea Sansovino sculpte en 1505 le tombeau du cardinal Ascanio Sforza sur le modèle de l'arc de triomphe romain : pilastres, entablement, sarcophage, et des figures de Vertus. Ce cardinal avait fait élire pape Alexandre VI en 1492, contre la charge de vice-chancelier et un palais. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg | Ammannati, Tombe de Marco Mantova Benavides, Padoue, 1546 | enchaîné 10]À Padoue, Bartolomeo Ammannati élève en 1546 le monument de Marco Mantova Benavides : une structure en pierre jaune, des statues de marbre blanc, un véritable mausolée allégorique. Au centre, le sarcophage, entre le Travail et la Patience ; au-dessus, le défunt, entre le Temps et la Renommée, couronné par l'Immortalité. Il le commande de son vivant et ne mourra qu'en 1582. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg | Michel-Ange, Tombeau de Laurent de Médicis, Florence, 1520-1534 | enchaîné 10]À Florence, Michelangelo Buonarroti, dit Michel-Ange, sculpte de 1520 à 1534 le tombeau de Laurent de Médicis : le duc médite, assis dans une niche ; sur le couvercle galbé du sarcophage, le Crépuscule et l'Aurore glissent, instables. C'est le maniérisme. Son modèle ne lui ressemble pas ? Dans mille ans, aurait répondu Michel-Ange, personne ne verra la différence. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg | Pilon, Tombeau d’Henri II et de Catherine de Médicis, Saint-Denis, 1560-1573 | enchaîné 10]En France, le tombeau royal se construit sur deux niveaux. À Saint-Denis, Germain Pilon sculpte de 1560 à 1573 celui d'Henri II et de Catherine de Médicis [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/99/Saint-Denis_-_Basilique_Saint-Denis_-_Tombeau_monumental_de_Henri_II_et_Catherine_de_M%C3%A9dicis_%28Germain_Pilon%29_01.jpg/1280px-Saint-Denis_-_Basilique_Saint-Denis_-_Tombeau_monumental_de_Henri_II_et_Catherine_de_M%C3%A9dicis_%28Germain_Pilon%29_01.jpg | Tombeau d'Henri II et Catherine de Médicis, Germain Pilon | enchaîné 10]: en haut, le couple prie, agenouillé, en bronze, vêtu comme de son vivant. Le roi était mort en 1559, l'œil percé par une lance lors d'un tournoi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG/1280px-Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG | Pilon, Tombeau d’Henri II et de Catherine de Médicis, Saint-Denis, 1560-1573 | enchaîné 10]En bas, le même couple gît, nu, en marbre, comme deux cadavres, tandis que quatre Vertus de bronze veillent aux angles. Ces gisants nus, idéalisés, rappellent que le roi, malgré sa gloire, reste soumis à la mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d1/0_Monument_fun%C3%A9raire_du_pape_Alexandre_VII_-_St-Pierre_-_Vatican_%281%29_brighter.jpg/960px-0_Monument_fun%C3%A9raire_du_pape_Alexandre_VII_-_St-Pierre_-_Vatican_%281%29_brighter.jpg | Bernin, Tombeau du pape Alexandre VII, Rome, 1671-1678 | enchaîné 10]Au XVIIe siècle, le tombeau devient un théâtre : c'est le baroque. À Rome, Gian Lorenzo Bernini, dit le Bernin, sculpte de 1671 à 1678 celui d'Alexandre VII : le pape prie, agenouillé, au sommet d'une composition pyramidale que gardent quatre Vertus. Dessous, une draperie de jaspe rouge gonfle, et la Mort, en bronze doré, brandit un sablier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Int%C3%A9rieur_%C3%89glise_St_Thomas_Strasbourg_114.jpg/960px-Int%C3%A9rieur_%C3%89glise_St_Thomas_Strasbourg_114.jpg | Pigalle, Tombeau de Maurice de Saxe, Strasbourg, 1777 | enchaîné 10]Un siècle plus tard, la mise en scène devient un récit. À Strasbourg, Jean-Baptiste Pigalle travaille de 1753 à 1777 au tombeau de Maurice de Saxe : le maréchal descend vers son cercueil, que la Mort ouvre ; la France tente de le retenir, Hercule pleure. Protestant, vainqueur de Fontenoy, il est honoré dans une église luthérienne. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Tumba_de_Isaac_Newton_-_panoramio_%28cropped%29.jpg/960px-Tumba_de_Isaac_Newton_-_panoramio_%28cropped%29.jpg | Rysbrack, Tombeau d’Isaac Newton, Londres, 1731 | enchaîné 10]Le XVIIIe siècle anglais préfère l'ordre. À Westminster, John Michael Rysbrack sculpte en 1731, sur un dessin de William Kent, le monument de Newton : un sarcophage, Newton accoudé sur ses livres, une pyramide et un globe céleste où figure la comète de 1680. Des figures d'ange enfants jouent avec des prismes et des télescopes, symbolisant des recherches en optique et en physique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Wien_Augustinerkirche_Kenotaph_Maria_Christina_1.jpg/1280px-Wien_Augustinerkirche_Kenotaph_Maria_Christina_1.jpg | Canova, Cénotaphe de l’archiduchesse Marie-Christine, Vienne, 1798-1805 | enchaîné 10]Le néoclassicisme cherche la géométrie pure de l'Antiquité. À Vienne, Antonio Canova élève de 1798 à 1805 le cénotaphe de l'archiduchesse Marie-Christine : une pyramide, dont la porte ouverte accueille un cortège de pleureurs portant une urne. Le monument est vide ; elle repose dans la crypte des Capucins. [image: https://upload.wikimedia.org/wikipedia/de/4/40/MauLu.jpg | Rauch, Cénotaphe de la reine Louise de Prusse, Berlin, 1811-1814 | enchaîné 10]Le romantisme ramène le gisant. À Berlin, Christian Daniel Rauch sculpte de 1811 à 1814 la reine Louise de Prusse, morte à trente-quatre ans, endormie sur son sarcophage dans un mausolée en forme de temple antique.  On retrouve là le goût du Romantisme pour le Moyen-âge, mais avec des gisants plus réalistes, suscitant douleur et compassion. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Chopin_Grave_Grab_Pere_Lachaise.JPG/960px-Chopin_Grave_Grab_Pere_Lachaise.JPG | Clésinger, Tombe de Frédéric Chopin, Paris, 1850 | enchaîné 10]Autre thème romantique : la douleur de l'art. À Paris, Jean-Baptiste Clésinger sculpte en 1850 la tombe de Frédéric Chopin au Père-Lachaise : Euterpe, muse de la musique, pleure sur une lyre brisée. Il avait moulé le masque et la main du pianiste, dont le cœur repose à Varsovie. En cinq siècles, le tombeau est passé du mort qui attend aux vivants qui pleurent.
+[sortie: noir]</v>
+      </c>
+      <c r="D4" t="str">
+        <v>25/10/2026 19:42:26</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Terminé</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -431,12 +431,12 @@
         <v>Statue ou monument équestre</v>
       </c>
       <c r="C2" t="str" xml:space="preserve">
-        <v xml:space="preserve">[titre: Le monument équestre]
+        <v xml:space="preserve">[titre: L'évolution des monuments équestres | | 5]
 En Occident, les statues équestres [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg/960px-Kouros%27_Head_to_horse%2C_Acropolis%27_museum%2C_Athens.jpg | Le Cavalier Rampin | noir 10]ont existé en Grèce pour célébrer les héros des jeux, tels les fragments du cavalier Rampin, daté de 550 avant Jésus-Christ. Sa tête est au Louvre, son corps à Athènes : on ne les a réunis qu'en 1936. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/02-Capitolini_collections139.jpg/960px-02-Capitolini_collections139.jpg | Statue équestre de Marc Aurèle, vers 175 après Jésus-Christ | enchaîné 10]Mais le premier véritable monument équestre remonte à Rome, vers 175 après Jésus-Christ, avec la statue en bronze de l'empereur Marc Aurèle. Elle n'a survécu que par erreur : au Moyen-Âge, on la prenait pour une représentation de Constantin, le premier empereur chrétien, et on n'a donc pas fondu son métal. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/85/Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg/960px-Replica_of_the_Equestrian_statue_of_Marcus_Aurelius_in_Rome_%282%29.jpg | Réplique de la statue sur la place du Capitole | enchaîné 10]Michel-Ange lui a offert en 1538 un piédestal sur la colline du Capitole. Regardez le cheval : il avance, une patte avant levée, et ne repose donc que sur trois sabots. Pendant mille ans, plus personne ne fond un cavalier de cette taille. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]En 1453, Donatello ose enfin, à Padoue, avec le *Gattamelata*. Ce « chat au miel », c'est Erasmo da Narni, un condottiere, chef de mercenaires, mort en 1443 au service de Venise. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Une statue équestre était réservée aux souverains : le Sénat de Venise a fait une exception. Donatello s'inspire de Marc Aurèle, mais son cavalier est un homme d'armes, cuirassé, l'épée au côté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg | Donatello, Gattamelata, Padoue, 1453 | enchaîné 10]Il se méfie pourtant : sous le sabot levé, une boule de bronze sert de point d'appui. Fêté à Padoue, il rentre à Florence, dit Vasari, de peur que les louanges lui fassent oublier son métier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Andrea del Verrocchio, à Venise, supprime la béquille : dans le *Colleoni*, le sabot se lève dans le vide, le cavalier se dresse sur ses étriers et fixe l'horizon. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Venice_%2850444397307%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Bartolomeo Colleoni, condottiere et capitaine général de Venise, lègue sa fortune à la République, à condition qu'on lui dresse une statue place Saint-Marc. Or les statues y sont interdites. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg | Verrocchio, Colleoni, Venise, 1488 | enchaîné 10]Venise place donc le cavalier devant la Scuola di San Marco, une autre « Saint-Marc ». Verrocchio meurt en 1488 avant la fonte : Alessandro Leopardi coule le bronze, et la statue est dressée en 1496. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Giambologne, Cosme Ier, Florence, 1594 | enchaîné 10]À Florence, Jean de Boulogne, dit Giambologna, né à Douai, en Flandre, termine en 1594 *Cosme Ier*, premier grand-duc de Toscane : un cheval au pas, un sabot levé, qui servira de modèle à toute l'Europe. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Monumento_equestre_a_ferdinando_I_02.JPG | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Son élève Pietro Tacca l'imite pour *Ferdinand Ier*, fils de Cosme, d'après un projet du maître, qui meurt en 1608, l'année de l'inauguration. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]On raconte que le bronze vient de canons pris aux Turcs par les chevaliers de Saint-Étienne, l'ordre fondé par les Médicis contre les corsaires ; Ferdinand en porte la croix. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Piazza_SS_Annunziata_Firenze_Apr_2008.jpg | TACCA Pietro, Statue équestre de Ferdinand Ier de Médicis, 1608 | enchaîné 10]Derrière le cheval, deux fontaines aux monstres marins, que Tacca avait d'abord conçues pour une statue de Ferdinand à Livourne : le grand-duc a droit à toute une mise en scène. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Francesco_Mochi%2C_Monumento_in_bronzo_ad_Ranuccio_I_Farnese_02.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]À Plaisance, Francesco Mochi, venu de Toscane, élève en 1625 le monument d'Alexandre Farnèse, ce duc de Parme qui commanda les armées de l'Espagne en Flandre et prit Anvers en 1585. [image: https://commons.wikimedia.org/wiki/Special:FilePath/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Manteau et crinière au vent, le cheval semble sauvage : c'est l'élan du baroque, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Padre_e_figlio_nella_storia.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]tout le contraire de la sérénité du modèle florentin, et le bronze semble s'élancer. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%22_Un_cavallo_del_Mochi_%22.jpg | Mochi, monument aux Farnèse, Plaisance, 1625 | enchaîné 10]Mochi a sculpté cinq ans plus tôt le fils d'Alexandre, Ranuccio, et ces deux cavaliers ont donné son nom à la place : la Piazza dei Cavalli, la place des Chevaux. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]En 1640 vient le grand saut. Philippe IV d'Espagne veut une statue plus prestigieuse que celle de son père, et Pietro Tacca, d'après un dessin de Velázquez, réalise un cheval cabré : seules les deux pattes arrière et, discrètement, la queue touchent le socle. [image: https://upload.wikimedia.org/wikipedia/commons/f/f3/Madrid_-_Plaza_de_Oriente%2C_Monumento_a_Felipe_IV_1.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]On raconte que Galilée a aidé à calculer l'équilibre de ces tonnes de bronze, un défi dont Léonard de Vinci avait rêvé deux siècles plus tôt. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Madrid_2015_10_24_2510_%2826487296566%29.jpg/1280px-Madrid_2015_10_24_2510_%2826487296566%29.jpg | Tacca, Philippe IV, Madrid, 1640 | enchaîné 10]Sur le socle, le roi décore Velázquez, l'homme dont le dessin a servi de modèle ; mais la statue ne gagne la place d'Orient qu'en 1843. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Louis_XIV-Equestre-Pl-Bellecour.jpg/1280px-Louis_XIV-Equestre-Pl-Bellecour.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]En France, sous Louis XIV, le classicisme préfère la sérénité : Martin Desjardins, puis François Girardon, montrent le roi en empereur romain sur un cheval au pas, comme Marc Aurèle. [image: https://upload.wikimedia.org/wikipedia/commons/e/e7/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV%2C_apr%C3%A8s_restauration_02.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]À Lyon, la statue de Desjardins, coulée en 1694, voyage sept ans par la Seine, la mer et le Rhône, et n'est inaugurée qu'en 1713, deux ans avant la mort du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg | Louis XIV, place Bellecour, Lyon | enchaîné 10]Détruite en 1792, elle est refaite par Lemot en 1825. Selon une légende, il se serait tué d'avoir oublié les étriers : c'est faux, le roi monte simplement à la romaine, sans étriers. [image: https://commons.wikimedia.org/wiki/Special:FilePath/070522_ukbris_qsqs.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]Même retour à l'antique à Bristol, où le Flamand John Michael Rysbrack habille à la romaine Guillaume III d'Orange. Coulée en 1733, la statue est dressée en 1736 sur Queen Square. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg/960px-In_Queen_Square_%285%29_-_geograph.org.uk_-_6454498.jpg | RYSBRACK John Michael, Statue équestre de Guillaume III, 1733 | enchaîné 10]La ville pensait d'abord à George II ; ses notables, partisans du Parlement, ont préféré Guillaume III. Évacuée à Badminton pendant la guerre, elle est revenue en 1948. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg/960px-Thorwaldsen_J%C3%B3zef_Poniatowski_Warsaw_01.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Au XIXe siècle, le monument devient un récit national, et parfois un enjeu politique. À Varsovie, le Danois Bertel Thorvaldsen représente le prince Józef Poniatowski, noyé dans l'Elster, à Leipzig, en 1813, trois jours après avoir été nommé maréchal de France par Napoléon. Il le sculpte en général romain presque nu, ce qui déplaît à beaucoup. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/71/Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg/960px-Pomnik_Ksi%C4%99cia_J%C3%B3zefa_Poniatowskiego_w_Warszawie_2019.jpg | Thorvaldsen, prince Józef Poniatowski, Varsovie, 1829-1832 | enchaîné 10]Surtout, après le soulèvement polonais de 1830, le tsar retire son autorisation : la statue, fondue en 1832, est envoyée à Gomel, en Biélorussie, et ne revient à Varsovie qu'en 1922. Dynamitée par les Allemands en 1944, elle a été refaite d'après le modèle conservé à Copenhague. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin%2C_Mitte%2C_Unter_den_Linden%2C_Reiterstandbild_Friedrich_II.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]À Berlin, Christian Daniel Rauch place Frédéric le Grand en uniforme, au-dessus d'un socle où défilent soixante-quatorze généraux, ministres et penseurs de son [image: https://commons.wikimedia.org/wiki/Special:FilePath/Berlin_Friedrich_II_Denkmal_09-2017_img1.jpg | Rauch, Frédéric le Grand, Berlin, 1851 | enchaîné 10]règne. Démonté en 1950 par l'Allemagne de l'Est, il revient en 1980, quand Honecker se met à dire « Frédéric le Grand ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg/1280px-George_Washington_Statue_-_Capitol_Hill_Richmond_%28VA%29_2013_%288759158238%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Aux États-Unis, la jeune république n'a pas de roi, mais elle a Washington. À Richmond, en Virginie, l'Américain Thomas Crawford, installé à Rome, le place à cheval au sommet d'un monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f5/Virginia_Washington_Monument_2011.JPG/1280px-Virginia_Washington_Monument_2011.JPG | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Autour de lui, d'autres grandes figures de la Révolution virginienne, dont Jefferson et Patrick Henry. Les bronzes sont modelés à Rome, puis fondus à Munich avant de traverser l'Atlantique. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Richmond%2C_VA_%285608604860%29.jpg/1280px-Richmond%2C_VA_%285608604860%29.jpg | Crawford, George Washington, Richmond, 1857 | enchaîné 10]Mais Crawford perd la vue en 1856 à cause d'un cancer de l'œil. Il meurt à Londres en 1857, avant que la statue soit dressée, et c'est Randolph Rogers qui achève l'ensemble en 1869. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/45/RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg/1280px-RUS-2016-SPB-Monument_to_Nicholas_I_of_Russia.jpg | Klodt, Nicolas Ier, Saint-Pétersbourg, 1859 | enchaîné 10]En 1859, à Saint-Pétersbourg, Piotr Klodt va plus loin que Tacca : le cheval de Nicolas Ier ne touche le socle que par ses deux pattes arrière. On plaisante : Nicolas veut rattraper Pierre le Grand, mais la cathédrale Saint-Isaac l'en empêche. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Corsica_Ajaccio_monument_Napoleon_Place_du_G%C3%A9n%C3%A9ral_de_Gaulle.jpg | BARYE Antoine-Louis, Statue équestre de Napoléon Ier, 1865 | enchaîné 10]À Ajaccio, Antoine-Louis Barye, le sculpteur des fauves, habille Napoléon en empereur romain et ses frères en toges, pour éviter les costumes d'époque. Le monument regardait la mer mais depuis 1969, il fait face à la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg/1280px-Antoine-Louis_Barye%2C_Charles_VII_Victorious%2C_model_1836-1840_and_1857%2C_cast_by_1873%2C_NGA_176724.jpg | Barye, Charles VII victorieux, 1836 | enchaîné 10]Le même Barye avait fait revivre le Moyen-Âge dès 1836, avec *Charles VII victorieux*, en armure, ce roi que Jeanne d'Arc a fait sacrer à Reims en 1429, et qui ne fera rien pour la sauver. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg/960px-Statue_of_Jeanne_d%27Arc_in_Paris%2C_Place_des_Pyramides_-_France_-_4_July_2014.jpg | Frémiet, Jeanne d'Arc, Paris, 1874 | enchaîné 10]Emmanuel Frémiet met Jeanne en selle en 1874, place des Pyramides, là où elle fut blessée en 1429 : une paysanne devenue chef de guerre, en bronze doré, pour une France meurtrie par la défaite de 1870. Mécontent du cheval, il l'a discrètement fait remplacer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg/1280px-Bonaparte_Entering_Cairo%2C_by_Jean-Leon_Gerome%2C_c._1897%2C_multi-patinated_bronze_-_Montreal_Museum_of_Fine_Arts_-_Montreal%2C_Canada_-_DSC08775.jpg | Gérôme, Bonaparte entrant au Caire, 1897 | enchaîné 10]Le peintre Jean-Léon Gérôme s'essaie aussi au bronze avec son *Bonaparte entrant au Caire*, en 1798, qui est présenté au Salon de 1897 puis acheté par l'État pour le jardin du Luxembourg, avec une patine colorée et dorée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg/1280px-7217_-_Paolo_Troubetzkoy_-_Lev_Tolstoij_%281899%29_-_Museo_del_Paesaggio_%28Verbania%29_-_Foto_Giovanni_Dall%27Orto%2C_8-Jan-2012.jpg | Troubetzkoy, Tolstoï à cheval, 1899 | enchaîné 10]En 1899, Paolo Troubetzkoy, que Tolstoï aimait beaucoup, le montre à cheval. Il le modèle comme un écrivain en promenade, sans uniforme ni couronne. Ils étaient tous deux végétariens, Troubetzkoy refusait la viande en s'écriant : « Je ne mange pas de cadavre ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Jaude_statue2.jpg/960px-Jaude_statue2.jpg | Bartholdi, Vercingétorix, Clermont-Ferrand, 1903 | enchaîné 10]Auguste Bartholdi, père de la Liberté de New York et du Lion de Belfort, offre en 1903 à la France un héros dont personne ne connaît le visage : Vercingétorix, l'épée levée sur son cheval cabré, un Romain mort sous les sabots. Inauguré par Émile Combes. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg/1280px-Angel%2C_horse_%26_Sherman_at_Grand_Army_Plaza_in_Manhattan_07.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]À New York, Augustus Saint-Gaudens inaugure en 1903 une idée nouvelle pour son général Sherman : une femme ailée, la Victoire, précède le cheval, et le bronze est doré. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Plaza_Hotel_NYC_%287918848816%29.jpg/1280px-Plaza_Hotel_NYC_%287918848816%29.jpg | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]Son modèle, Hettie Anderson, une jeune femme noire, ne fut connue du public que dans les [image: https://commons.wikimedia.org/wiki/Special:FilePath/Sherman_gilded_jeh.JPG | Saint-Gaudens, général Sherman, New York, 1903 | enchaîné 10]années 1980. Onze ans séparent le projet de l'inauguration, où le sculpteur, très fragile, était présent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg/1280px-The_Appeal_to_the_Great_Spirit%2C_Cyrus_E._Dallin%2C_Boston%2C_Mass._%28cropped%29.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]À Boston, Cyrus Dallin, né dans l'Utah, offre en 1908 un tout autre visage de l'Amérique : enfant, il côtoyait des petits Amérindiens, et il en garde ce cavalier sans arme, les bras ouverts vers le ciel. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Appeal_to_the_Great_Spirit.jpg/500px-Appeal_to_the_Great_Spirit.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Le cheval ne sert plus à la guerre mais à la prière. Fondue à Paris, la statue reçoit une médaille d'or au Salon, puis est installée devant le musée des Beaux-Arts de Boston en 1912. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg/1280px-2018_Museun_of_Fine_Arts_Boston_Huntington_Avenue_facade_from_south.jpg | Dallin, Appeal to the Great Spirit, Boston, 1908 | enchaîné 10]Quand on a restauré le bronze, Dallin a exigé qu'on lui rende sa patine verte, qu'il préférait au brun d'origine. Le musée invite aujourd'hui des auteurs amérindiens à en discuter le sens. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Alex_Trub3.jpg/1280px-Alex_Trub3.jpg | Troubetzkoy, Alexandre III, Saint-Pétersbourg, 1909 | enchaîné 10]Pour Alexandre III, Paolo Troubetzkoy choisit en 1909, au contraire, la masse : un cheval aux quatre sabots plantés, immobile comme le pouvoir qu'il porte. On surnomme aussitôt le monument « l'Hippopotame » ; sous les Soviets, on y grave « l'épouvantail en fonte ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/32/ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg/1280px-ID_C679_Homenaje_al_General_Carlos_Mar%C3%ADa_de_Alvear_0894.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Antoine Bourdelle, enfin, reçoit en 1913 la commande du monument au général Carlos María de Alvear, l'un des héros de l'indépendance argentine, à Buenos Aires. Il lui faudra près de dix ans, et cinquante-sept études, avant de trouver la bonne forme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg/1280px-Monumento_General_Carlos_Mar%C3%ADa_de_Alvear_2.jpg | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Le général, bras levé et cape au vent, domine quatre allégories, la Force, l'Éloquence, la Victoire et la Liberté, sur un piédestal de granite rose de quatorze mètres. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG/1280px-Monumentos_a_Carlos_Mar%C3%ADa_y_a_Torcuato_de_Alvear.JPG | Bourdelle, général Alvear, Buenos Aires, 1913-1923 | enchaîné 10]Inauguré en 1926, il retrouve le socle peuplé de Rauch, mais avec des volumes simplifiés, presque architecturaux. En vingt siècles, cheval et cavalier illustrent une vision changeante du pouvoir et de la société, plus conservatrice ou plus en mouvement selon les époques.
 [sortie: noir]</v>
       </c>
       <c r="D2" t="str">
-        <v>24/10/2026 15:25:08</v>
+        <v>25/10/2026 19:53:14</v>
       </c>
       <c r="E2" t="str">
         <v>Terminé</v>
@@ -450,12 +450,12 @@
         <v>Fontaine</v>
       </c>
       <c r="C3" t="str" xml:space="preserve">
-        <v xml:space="preserve">[titre: Fontaines | | 3]
+        <v xml:space="preserve">[titre: L'évolution des fontaines | | 3]
 [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg/1280px-I08_306_Decumanus_maximus%2C_Herkulesbrunnen.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]Pendant des siècles, une fontaine publique n'est pas un décor : c'est un service. Dans la civilisation romaine, les lacus sont [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg/960px-Antigua_ciudad_de_Herculano%2C_Italia%2C_2023-03-27%2C_DD_54.jpg | Fontaine d'Hercule à Herculanum | enchaîné 10]des bassins de pierre rectangulaires avec une borne souvent adossée à un mur d'où l'eau jaillit par une bouche sculptée. [image: https://upload.wikimedia.org/wikipedia/commons/5/5e/SEPTIZODIUM_Rome.jpg | Le Septizodium | enchaîné 10]Sous l'Empire apparaissent des nymphées, les bassins sont plus vastes et sont surmontés d'un édifice à colonne, orné de statues, toujours adossé, comme un vaste mur de scène. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG/1280px-Ricostruzione_del_giardino_della_casa_dei_vetii_di_pompei_%28mostra_al_giardino_di_boboli%2C_2007%29_01.JPG | Reconstitution de la maison des Vetii à Pompéi | enchaîné 10]Les fontaines centrales sont plutôt réservés à l'habitation privée, ornant atrium et péristyles. [image: https://upload.wikimedia.org/wikipedia/commons/9/91/Fontaine.medievale.png | Fontaine médiévale | enchaîné 10]Au Moyen-âge, à coté de fontaines qui reprennent le schéma de la fontaine publique adossée romaine, [image: https://upload.wikimedia.org/wikipedia/commons/d/d8/Fontaine.XIIIe.siecle.2.png | Fontaine du 13e siècle | enchaîné 10]les villes se dotent de fontaines de forme circulaire ou polygonale, avec une pile centrale sculptée de motifs religieux qui distribue l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Beblenheim-0003.jpg/960px-Beblenheim-0003.jpg | Fontaine gothique de Beblenheim | enchaîné 10]Les chiffres ont une grande importance dans la conception de leur bassin: le 6 des bassins hexagonaux renvoie au nombre de jour de la création, le 8 des bassins octogonaux, à la vie éternelle promise le 8e jour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Fontana_Maggiore%2C_Perugia.jpg/1280px-Fontana_Maggiore%2C_Perugia.jpg | Fontana Maggiore, Perugia | enchaîné 10]En Italie, à Pérouse, ce modèle se décline dans des grandes proportions qui dépassent le cadre religieux et proposent une vision encyclopédique: en 1278, la Fontana Maggiore de Nicola Pisano et son fils Giovanni est conçue comme un double bassin [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/35/La_Fontana_Maggiore_e_la_nebbia.jpg/1280px-La_Fontana_Maggiore_e_la_nebbia.jpg | Fontana Maggiore, Pérouse | enchaîné 10]où les Pisano sculptent les mois de l'année, les arts libéraux, des scènes bibliques en bas-relief et ajoutent 24 statues en hommage à la Cité de Pérouse et à ses dirigeants. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | noir 5]Plus modestement et reprenant la tradition des fontaines bassins à la romaine, à Sienne, Jacopo della Quercia sculpte entre 1409 et 1419 les reliefs de la Fonte Gaia, mêlant scènes bibliques et mythes fondateurs de la ville. [image: https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg | Della Quercia, Fontaine de la Joie, Sienne, 1409-1419 | enchaîné 10]Ce nom, « fontaine joyeuse », date de 1342 : l'eau, amenée par vingt-cinq kilomètres de canalisations souterraines, arrive enfin sur la place du Campo, et les Siennois font la fête.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]À la Renaissance, le programme iconographique des fontaines s'éloigne de la religion. Les jardins des grandes villas patriciennes s'ornent de fontaines centrales à la gloire du propriétaire: à  Florence, pour la villa de Castello, Niccolò Pericoli, dit le Tribolo, conçoit dès 1538, avec son assistant Pierino da Vinci, la fontaine d'Hercule et Antée, pour Cosme Ier de Médicis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG/960px-Tribolo%2C_pierino_da_vinci_e_altri%2C_fontana_della_villa_di_castello%2C_02.JPG | Tribolo, fontaine d'Hercule et Antée, Florence, 1538-1548 | enchaîné 10]Le bronze, de Bartolomeo Ammannati, montre Hercule étouffant Antée, dont la bouche crache l'eau : on y représente Cosme Ier triomphant de ses ennemis. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Même volonté de glorification politique en ville où, en 1565, pour les noces de l'héritier des Médicis, Bartolomeo Ammannati livre en hâte son Neptune sur la piazza della Signoria à Florence : inachevé, il est complété en stuc peint. Le dieu a le visage de Cosme Ier. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Le bloc de marbre avait été choisi par Baccio Bandinelli, mort en 1560. Michel-Ange, vieillard, aurait lancé à Ammannati : « Quel beau marbre tu as gâché ! » [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg | Ammannati, Neptune, Florence, 1563-1565 | enchaîné 10]Les Florentins le surnomment *il Biancone*, le grand blanc, et s'en servent comme lavoir : l'encre et le linge tachent le marbre presque dès le début. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, le cardinal Charles Borromée, légat du pape, fait ériger en 1566 une fontaine pour fêter l'élection de son oncle Pie IV : on rase tout un bâtiment pour lui faire place. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg/960px-1067_-_Bologna_-_Fontana_del_Nettuno_-_Foto_Giovanni_Dall%27Orto%2C_9-Feb-2008.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Le Neptune de bronze est de Jean Bologne, un Flamand né à Douai, évincé du concours de Florence. Sa main tendue symbolise, dit-on, l'autorité du pape sur la ville. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Bologne_fontaine_neptune.jpg/1280px-Bologne_fontaine_neptune.jpg | Jean Bologne, fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]Quatre sirènes, dont les seins font jaillir l'eau, entourent le dieu. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Piazza_navona_0511-01.JPG/1280px-Piazza_navona_0511-01.JPG | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]À Rome, les papes remettent en service les anciens aqueducs. Place Navone, Giacomo della Porta dessine en 1575 la fontaine du More, bordée de tritons de Taddeo Landini, d'abord conçus pour la place du Peuple. [image: https://upload.wikimedia.org/wikipedia/commons/7/7f/Piazza_Navona%2C_Roma_-_fontana_fc07.jpg | Landini, tritons de la place Navone, Rome, 1575 | enchaîné 10]En 1654, sur un dessin du Bernin, Giovanni Antonio Mari sculpte au centre le « More », aux prises avec un dauphin, qui donne son nom à la fontaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/64/Fontana_delle_Tartarughe_Roma.jpg/960px-Fontana_delle_Tartarughe_Roma.jpg | La Fontaine des Tortues | enchaîné 10]Landini signe aussi les jeunes bronzes de la fontaine des Tortues : selon la légende, un duc ruiné par le jeu l'aurait fait construire en une nuit pour séduire un beau-père fortuné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9d/Barcaccia.JPG/1280px-Barcaccia.JPG | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Au XVIIe siècle, la fontaine devient théâtre. Au pied de l'escalier de la Trinité-des-Monts, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Barcaccia_e_scalinata.jpg/1280px-Barcaccia_e_scalinata.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Pietro Bernini sculpte, de 1627 à 1629, pour le pape Urbain VIII, la Barcaccia, une barque à demi coulée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg/1280px-The_fountain%2C_Piazza_di_Spagna%2C_Rome%2C_Sept._2011_-_Flickr_-_PhillipC.jpg | Pietro Bernini, Barcaccia, Rome, 1627-1629 | enchaîné 10]Selon la légende, une crue du Tibre aurait laissé une barque échouée sur la place en 1598. En vérité, l'eau de l'aqueduc manque de pression : il fallait enfoncer la fontaine. . [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/PiazzaNavonaPanoramicaVerticale.jpg/960px-PiazzaNavonaPanoramicaVerticale.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Son fils, Gian Lorenzo Bernini, le Bernin, change d'échelle. Tenu à l'écart par le pape Innocent X, il voit sa maquette placée discrètement sur le passage du pontife, qui s'arrête, ébloui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]La fontaine des Quatre-Fleuves, inaugurée en 1651, dresse un obélisque sur un rocher percé, autour duquel quatre géants figurent les fleuves de quatre continents. Le Danube est d'Antonio Raggi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg | Bernin, Fontaine des Quatre-Fleuves, Rome, 1648-1651 | enchaîné 10]Le Nil a la tête voilée, dit-on, pour ne pas voir l'église de Borromini, rival du Bernin. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/df/Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg/960px-Bassin_Latone_Jardin_Ch%C3%A2teau_Versailles_-_Versailles_%28FR78%29_-_2021-12-19_-_6.jpg | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]À Versailles, Louis XIV pousse plus loin encore le spectacle. Gaspard de Marsy sculpte, de 1668 à 1670, la déesse Latone implorant Jupiter contre les paysans qui l'insultent. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Versailles_garden.JPG/1280px-Versailles_garden.JPG | Marsy, bassin de Latone, Versailles, 1668-1670 | enchaîné 10]Son frère Balthazar les change en grenouilles de plomb : on y lit souvent une allégorie de la Fronde, la révolte contre le jeune Louis XIV et la vengeance de sa mère, Anne d'Autriche, contre les rebelles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg/1280px-Bassin_de_Latone_Chateau_de_Versailles_juillet_2023_Luc_Viatour.jpg | Château de Versailles | enchaîné 10]Mais Versailles manque d'eau. Le roi fait pomper la Seine par la machine de Marly dès 1684, et les jets ne s'ouvrent que devant lui, au fil de sa promenade. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/07/Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7_partie_centrale.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Au XVIIIe siècle, on dote les villes de nombreuse fontaines, pour assurer l'hygiène et la santé des habitants. Edme Bouchardon sculpte à Paris, de 1739 à 1745, la fontaine des Quatre-Saisons, rue de Grenelle, commandée par la Ville pour le quartier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Fontaine_des_Quatre-Saisons_Paris_7.jpg/1280px-Fontaine_des_Quatre-Saisons_Paris_7.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Elle ressemble à un hôtel particulier : ses deux portes sont fausses, et seuls quatre masques de bronze révèlent sa fonction. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/4_saisons_vue_d%27ensembleG.jpg/1280px-4_saisons_vue_d%27ensembleG.jpg | Bouchardon, Fontaine des Quatre-Saisons, Paris, 1739-1745 | enchaîné 10]Voltaire s'en moque : trop de pierre pour si peu d'eau. Elle a coûté plus de cent trente mille livres, et son faible débit lui vaut le surnom de « la Trompeuse ». [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG/1280px-Wien_-_Donnerbrunnen%2C_Quellnymphe.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]À Vienne, sur le Neuer Markt, Georg Raphael Donner dresse en 1739 la fontaine de la Providence, commandée par la Ville et non par un noble, ce qui est rare à l'époque baroque. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/ca/Wien_-_Donnerbrunnen.JPG/1280px-Wien_-_Donnerbrunnen.JPG | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]Quatre figures de plomb évoquent des affluents du Danube : la Traun, l'Enns, l'Ybbs et la March. Les Viennois, déroutés par le mot « providentia », l'ont vite rebaptisée fontaine de Donner. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Austria_august2010_0228.jpg/1280px-Austria_august2010_0228.jpg | Donner, Fontaine de la Providence, Vienne, 1739 | enchaîné 10]En 1773, on retire les figures : une légende accuse la commission de chasteté de Marie-Thérèse. En vérité, le sculpteur chargé de les fondre les sauve. Elles reviennent en 1801. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/91/Oceanus_%28Trevi_fountain%29.jpg/960px-Oceanus_%28Trevi_fountain%29.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]À Rome, la fontaine de Trevi naît d'une querelle : en 1730, le concours est gagné par un Florentin, Alessandro Galilei. Les Romains protestent, et le chantier échoit à Nicola Salvi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/Fontana_di_Trevi_a_Roma.jpg/1280px-Fontana_di_Trevi_a_Roma.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]Salvi meurt en 1751, à mi-chemin. Giuseppe Pannini achève l'œuvre en 1762 : l'Océan de Pietro Bracci, sur un char tiré par des chevaux de mer, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Panorama_of_Trevi_fountain_2015.jpg/1280px-Panorama_of_Trevi_fountain_2015.jpg | Bracci, Océan, fontaine de Trevi, Rome, 1762 | enchaîné 10]s'adosse au palais comme à un décor.  Chaque jour, les touristes jettent dans son bassin environ trois mille euros, pour l'association Caritas. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Au XIXe siècle, l'eau courante arrive dans les maisons, et la fontaine devient un monument plus décoratif qui veut promouvoir les valeurs universelles d'un continent au faîte de sa puissance. À Paris, Jean-Baptiste Carpeaux sculpte pour l'Observatoire quatre jeunes femmes qui portent le globe terrestre. [image: https://upload.wikimedia.org/wikipedia/commons/3/38/FontaineQuatrePartiesDuMonde02.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Elles figurent l'Europe, l'Asie, l'Afrique et l'Amérique. Le critique Jules Clarétie les juge d'abord maigres et malsaines, avant de changer d'avis après la mort du sculpteur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg/1280px-Fontaine_des_Quatre-Parties-du-Monde_%2834561519946%29.jpg | Carpeaux, Fontaine des Quatre-Parties-du-Monde, Paris, 1874 | enchaîné 10]Emmanuel Frémiet sculpte les chevaux du bassin. Inaugurée en 1874, la fontaine est regardée de loin par un Carpeaux malade, qui meurt l'année suivante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Neptun_1a_2.jpg/1280px-Neptun_1a_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]À Berlin, Reinhold Begas place en 1891 un Neptune devant le château des Hohenzollern, sur la Schlossplatz : une vasque monumentale de dix-huit mètres de diamètre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Neptunbrunnen_B-Mitte_06-2017.jpg/1280px-Neptunbrunnen_B-Mitte_06-2017.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quatre femmes l'entourent, chacune avec la richesse de son fleuve : le Rhin, filet et raisin ; l'Elbe, les épis ; l'Oder, des chèvres ; la Vistule, aujourd'hui polonaise, du bois. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg | Begas, fontaine de Neptune, Berlin, 1891 | enchaîné 10]Quand l'Allemagne de l'Est démolit le château, la fontaine est démontée en 1951. Elle ne revient qu'en 1969, entre l'église Sainte-Marie et l'hôtel de ville rouge. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Lyon_fontaine_bartholdi_congres.jpg/1280px-Lyon_fontaine_bartholdi_congres.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]À Lyon, Auguste Bartholdi, père de la statue de la Liberté, signe en 1892 la fontaine de la place des Terreaux : la France, en char tiré par quatre chevaux. [image: https://upload.wikimedia.org/wikipedia/commons/1/12/Lyon_1er_-_Fontaine_Bartholdi_-_Statue_et_bassin.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Les chevaux, qui figurent de grands fleuves, bondissent hors de l'eau et soufflent par les naseaux. Les ateliers de la statue de la Liberté ont travaillé ce monument. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Fontaine_Bartholdi_01.jpg/1280px-Fontaine_Bartholdi_01.jpg | Bartholdi, fontaine Bartholdi, Lyon, 1892 | enchaîné 10]Bartholdi l'avait imaginée à vingt-trois ans pour Bordeaux, qui ne l'a jamais réalisée. Lyon l'achète cent mille francs en 1889, un prix qui le déçoit. [image: https://upload.wikimedia.org/wikipedia/commons/a/a3/Angel_of_Christian_Charity_Eros_Piccadilly_Circus_London_3.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]À Londres, la fontaine d'Éros, en 1893, n'a plus rien d'utilitaire : Alfred Gilbert y élève un mémorial à lord Shaftesbury, un philanthrope. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Piccadilly.jpg/960px-Piccadilly.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]C'est la première sculpture coulée en aluminium, et son modèle, Angelo Colarossi, n'a que seize ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/MK17690_Piccadilly_Circus.jpg/1280px-MK17690_Piccadilly_Circus.jpg | Gilbert, Fontaine d'Éros, Londres, 1893 | enchaîné 10]Le chantier coûte plus du double du devis : Gilbert s'endette, fait faillite en 1901 et s'exile à Bruges. Il ne reviendra qu'en 1926, et sera fait chevalier en 1932. [image: https://upload.wikimedia.org/wikipedia/commons/f/f5/Fountain_On_Lenbachplatz_-_panoramio.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]À Munich, Adolf von Hildebrand, choisi après un concours à condition de s'installer à Munich, célèbre en 1895 l'arrivée de l'eau de source des montagnes, achevée en 1883. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG/1280px-Fuente_Wittelsbacher%2C_Lenbachplatz%2C_M%C3%BAnich%2C_Alemania%2C_2012-04-30%2C_DD_05.JPG | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]D'un côté, un jeune homme sur un cheval à queue de poisson s'apprête à lancer un rocher : la fureur des torrents. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fa/20220917_Wittelsbacher_Fountain_Munich.jpg/1280px-20220917_Wittelsbacher_Fountain_Munich.jpg | Hildebrand, Fontaine Wittelsbach, Munich, 1895 | enchaîné 10]De l'autre, une amazone offre une coupe d'eau : la ressource domptée. Bombardée pendant la guerre, la fontaine est restaurée en 1952 par un élève de Hildebrand, Theodor Georgii. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Fountain_Of_The_Great_Lakes.jpg/1280px-Fountain_Of_The_Great_Lakes.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]À Chicago, Lorado Taft fait couler, en 1913, l'eau de bassin en bassin, comme elle passe d'un Grand Lac à l'autre, du lac Supérieur jusqu'à l'Ontario. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/2014_Chicago_Art_Institute_01.jpg/1280px-2014_Chicago_Art_Institute_01.jpg | Taft, Fontaine des Grands Lacs, Chicago, 1913 | enchaîné 10]Cinq femmes de bronze figurent les cinq lacs. Leur nudité partielle nourrit, cette année-là, un débat à Chicago sur l'obscénité de l'art public. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg/1280px-Reflectiing_on_the_Fountain_of_the_Great_Lakes.jpg | Art Institute of Chicago | enchaîné 10]C'est la première commande du fonds d'un million de dollars de Benjamin Ferguson, dont le portrait en relief est caché depuis le déplacement de 1963. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Chicago%2C_Illinois_%282026%29_-_471.jpg/1280px-Chicago%2C_Illinois_%282026%29_-_471.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]Sa *Fontaine du Temps*, inaugurée en 1922, commémore un siècle de paix entre les États-Unis et la Grande-Bretagne depuis 1814. Un Temps encapuchonné y regarde passer cent figures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Fountain_of_Time_rear5.jpg/1280px-Fountain_of_Time_rear5.jpg | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]D'après un poème d'Austin Dobson, le temps reste, c'est nous qui passons. Taft s'est glissé lui-même dans la procession, en blouse, la tête baissée. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a3/Panorama_of_the_Fountain_of_Time.JPG/1280px-Panorama_of_the_Fountain_of_Time.JPG | Taft, Fontaine du Temps, Chicago, 1920-1922 | enchaîné 10]En vingt siècles, la fontaine est passée d'un simple service public chez les Romains, à un monument marqué par une forte symbolique religieuse au Moyen-âge, devenant plus politique à la Renaissance et à l'âge classique, puis, quand l'eau a gagné les maisons, à un monument qui exalte des valeurs universelles comme l'Amour et la Paix.
 [sortie: noir]</v>
       </c>
       <c r="D3" t="str">
-        <v>25/10/2026 15:34:55</v>
+        <v>25/10/2026 19:53:14</v>
       </c>
       <c r="E3" t="str">
         <v>Terminé</v>
@@ -474,15 +474,34 @@
 [sortie: noir]</v>
       </c>
       <c r="D4" t="str">
-        <v>25/10/2026 19:42:26</v>
+        <v>25/10/2026 19:53:14</v>
       </c>
       <c r="E4" t="str">
+        <v>Terminé</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>sc.sub.autel</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Autels et retables</v>
+      </c>
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">[titre: L'évolution des retables | | 5]
+[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Table_d%27autel.jpg/1280px-Table_d%27autel.jpg | Table d'autel du Ve siècle, abbaye de saint-Victor à Marseille. | enchaîné 10]À l'origine, l'autel est une simple table de pierre, la *mensa*, où l'on célèbre la messe et qui renferme souvent les reliques d'un martyr. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cf/%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg/1280px-%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg | Retable de Saint Orens, XIIe siècle | enchaîné 10]À partir de la fin du XIe siècle, on place derrière lui un retable, du latin *retro tabula altaris*, « derrière la table de l'autel ». En six siècles, ce décor deviendra la pièce maîtresse de l'église. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg | Autel d’argent de saint Jacques, Pistoia, 1287-1456 | noir 5]Au Moyen Âge, le retable est d'abord une œuvre d'orfèvre. À Pistoia, l'autel d'argent de saint Jacques est construit de 1287 à 1456 : un dossal, panneau dressé derrière l'autel, et un devant d'autel, le paliotto, en argent repoussé, orné d'émaux translucides, des scènes de la vie du Christ et de saint Jacques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg/1280px-Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg | Brunelleschi, Prophètes de l’autel d’argent de saint Jacques, Pistoia, 1400-1401 | enchaîné 10]Vers 1400, Filippo Brunelleschi y réalise deux prophètes, Jérémie et Isaïe, avant de bâtir la coupole de Florence. Dès 1293, un voleur, Vanni Fucci, avait pillé la chapelle : Dante l'a mis en Enfer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]Au début du XVe siècle, le marbre remplace l'argent. À Lucques, Jacopo della Quercia sculpte en 1413 le retable Trenta : un polyptyque, ensemble de panneaux juxtaposés, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG/1280px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]où la Vierge à l'Enfant entourée de saints se dresse dans un cadre architectural encore gothique, au-dessus de la prédelle, la bande de petits reliefs qui sert de socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Della Robbia, Autel des Médicis, Florence, 1475-1480 | enchaîné 10]À Florence s'impose un autre matériau : la terre cuite émaillée. Vers 1440, Luca della Robbia recouvre l'argile d'une glaçure à l'étain, un émail blanc opaque, puis la colore : bleu de cobalt, vert de cuivre, jaune d'antimoine, brun de manganèse. Son neveu Andrea diffuse le procédé : figures blanches sur fond bleu, brillantes et durables. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg | Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Au nord des Alpes, le retable devient une immense huche de bois sculpté, dont les volets s'ouvrent et se ferment. À Cracovie, Veit Stoss y travaille de 1477 à 1489 : treize mètres de haut, des figures de près de trois mètres, au centre la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Retable_de_Veit_Stoss_-_53336472978.jpg/1280px-Retable_de_Veit_Stoss_-_53336472978.jpg | Veit Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Dormition de la Vierge entourée des douze apôtres. Pillé par les nazis, le retable est retrouvé dans les caves du château de Nuremberg. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]À Münnerstadt, Tilman Riemenschneider livre entre 1490 et 1492 un retable de Marie-Madeleine [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]entourée d'anges, en tilleul laissé sans polychromie, alors que presque toutes les sculptures sont peintes et dorées. Le grain du bois suffit. En 1525, il passera deux mois en prison pour avoir refusé de marcher contre les paysans révoltés. [image: https://upload.wikimedia.org/wikipedia/commons/9/96/Retablo_forment_poblet_lou2.jpg | Forment, Retable majeur du monastère de Poblet, vers 1527-1529 | enchaîné 10]En Espagne, le retable majeur occupe tout le chevet. À Poblet, Damià Forment l'élève en albâtre blanc vers 1527-1529 : quatre étages, ou corps, divisés en compartiments par des colonnes et des pilastres à l'antique. C'est son premier retable pleinement Renaissance, après celui du Pilar à Saragosse, encore gothique par bien des traits. Alonso Berruguete, qui a étudié en Italie auprès de Michel-Ange, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]rapporte en Castille une sculpture inquiète. À Valladolid, son retable de saint Benoît, vers 1526-1532, est en bois polychromé [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg/1280px-Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]et doré, aux corps étirés et agités. On pose l'or, puis la couleur, qu'on gratte par endroits pour le faire reparaître : c'est l'estofado. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Bas%C3%ADlica_El_Escorial_2.JPG/960px-Bas%C3%ADlica_El_Escorial_2.JPG | Leoni, Statues du retable majeur de l’Escorial, 1579-1594 | enchaîné 10]Après le concile de Trente, le retable doit proclamer le dogme que les protestants contestent. À l'Escorial, Juan de Herrera dessine quatorze mètres de large sur [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg/960px-Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg | Retable majeur de l’Escorial, 1579-1594 | enchaîné 10]vingt-six de haut, en quatre niveaux d'ordres superposés : dorique, ionique, corinthien, composite. Marbres, jaspes, bronze doré au feu et toiles s'y mêlent ; Pompeo Leoni signe les statues en 1588. Au centre, le tabernacle garde l'eucharistie. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]À Rome, le baroque change l'autel en scène de théâtre. Dans la chapelle Cornaro, le Bernin place de 1647 à 1652 sainte Thérèse en marbre blanc, dans une niche d'édicule ; une fenêtre cachée dans la coupole l'éclaire, et des rayons de stuc doré l'inondent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Santa_Maria_della_Vittoria_-_2.jpg/1280px-Santa_Maria_della_Vittoria_-_2.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]Aux murs, les Cornaro, sculptés en haut-relief, regardent depuis des loges de théâtre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg | Günther, Saint Pierre, Rott am Inn, vers 1760 | enchaîné 10]Au XVIIIe siècle, le rococo allège le retable. En Bavière, Franz Ignaz Günther, né en 1725 et mort à Munich en 1775, sculpte à Rott [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg/960px-Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg | Maitre-autel de l'Eglise de Rott am Inn, vers 1760 | enchaîné 10]am Inn des figures de bois peint en blanc et or : corps élancés, drapés aux plis courbes, couleurs claires. L'autel n'est plus une façade, c'est une danse de lumière. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg | Thorvaldsen, Le Christ, Copenhague, 1821 | enchaîné 10]Au XIXe siècle, le retable se réduit à l'essentiel. À Copenhague, l'église Notre-Dame, rebâtie en style néoclassique après le bombardement britannique de 1807, reçoit de Bertel Thorvaldsen un Christ de marbre blanc, bras ouverts, dans une niche au-dessus de l'autel. D'orfèvrerie, de bois, de théâtre, le retable est devenu une seule figure.
+[sortie: noir]</v>
+      </c>
+      <c r="D5" t="str">
+        <v>25/10/2026 21:42:25</v>
+      </c>
+      <c r="E5" t="str">
         <v>Terminé</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -489,11 +489,11 @@
       </c>
       <c r="C5" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: L'évolution des retables | | 5]
-[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Table_d%27autel.jpg/1280px-Table_d%27autel.jpg | Table d'autel du Ve siècle, abbaye de saint-Victor à Marseille. | enchaîné 10]À l'origine, l'autel est une simple table de pierre, la *mensa*, où l'on célèbre la messe et qui renferme souvent les reliques d'un martyr. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cf/%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg/1280px-%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg | Retable de Saint Orens, XIIe siècle | enchaîné 10]À partir de la fin du XIe siècle, on place derrière lui un retable, du latin *retro tabula altaris*, « derrière la table de l'autel ». En six siècles, ce décor deviendra la pièce maîtresse de l'église. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg | Autel d’argent de saint Jacques, Pistoia, 1287-1456 | noir 5]Au Moyen Âge, le retable est d'abord une œuvre d'orfèvre. À Pistoia, l'autel d'argent de saint Jacques est construit de 1287 à 1456 : un dossal, panneau dressé derrière l'autel, et un devant d'autel, le paliotto, en argent repoussé, orné d'émaux translucides, des scènes de la vie du Christ et de saint Jacques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg/1280px-Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg | Brunelleschi, Prophètes de l’autel d’argent de saint Jacques, Pistoia, 1400-1401 | enchaîné 10]Vers 1400, Filippo Brunelleschi y réalise deux prophètes, Jérémie et Isaïe, avant de bâtir la coupole de Florence. Dès 1293, un voleur, Vanni Fucci, avait pillé la chapelle : Dante l'a mis en Enfer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]Au début du XVe siècle, le marbre remplace l'argent. À Lucques, Jacopo della Quercia sculpte en 1413 le retable Trenta : un polyptyque, ensemble de panneaux juxtaposés, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG/1280px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]où la Vierge à l'Enfant entourée de saints se dresse dans un cadre architectural encore gothique, au-dessus de la prédelle, la bande de petits reliefs qui sert de socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Della Robbia, Autel des Médicis, Florence, 1475-1480 | enchaîné 10]À Florence s'impose un autre matériau : la terre cuite émaillée. Vers 1440, Luca della Robbia recouvre l'argile d'une glaçure à l'étain, un émail blanc opaque, puis la colore : bleu de cobalt, vert de cuivre, jaune d'antimoine, brun de manganèse. Son neveu Andrea diffuse le procédé : figures blanches sur fond bleu, brillantes et durables. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg | Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Au nord des Alpes, le retable devient une immense huche de bois sculpté, dont les volets s'ouvrent et se ferment. À Cracovie, Veit Stoss y travaille de 1477 à 1489 : treize mètres de haut, des figures de près de trois mètres, au centre la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Retable_de_Veit_Stoss_-_53336472978.jpg/1280px-Retable_de_Veit_Stoss_-_53336472978.jpg | Veit Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Dormition de la Vierge entourée des douze apôtres. Pillé par les nazis, le retable est retrouvé dans les caves du château de Nuremberg. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]À Münnerstadt, Tilman Riemenschneider livre entre 1490 et 1492 un retable de Marie-Madeleine [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]entourée d'anges, en tilleul laissé sans polychromie, alors que presque toutes les sculptures sont peintes et dorées. Le grain du bois suffit. En 1525, il passera deux mois en prison pour avoir refusé de marcher contre les paysans révoltés. [image: https://upload.wikimedia.org/wikipedia/commons/9/96/Retablo_forment_poblet_lou2.jpg | Forment, Retable majeur du monastère de Poblet, vers 1527-1529 | enchaîné 10]En Espagne, le retable majeur occupe tout le chevet. À Poblet, Damià Forment l'élève en albâtre blanc vers 1527-1529 : quatre étages, ou corps, divisés en compartiments par des colonnes et des pilastres à l'antique. C'est son premier retable pleinement Renaissance, après celui du Pilar à Saragosse, encore gothique par bien des traits. Alonso Berruguete, qui a étudié en Italie auprès de Michel-Ange, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]rapporte en Castille une sculpture inquiète. À Valladolid, son retable de saint Benoît, vers 1526-1532, est en bois polychromé [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg/1280px-Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]et doré, aux corps étirés et agités. On pose l'or, puis la couleur, qu'on gratte par endroits pour le faire reparaître : c'est l'estofado. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Bas%C3%ADlica_El_Escorial_2.JPG/960px-Bas%C3%ADlica_El_Escorial_2.JPG | Leoni, Statues du retable majeur de l’Escorial, 1579-1594 | enchaîné 10]Après le concile de Trente, le retable doit proclamer le dogme que les protestants contestent. À l'Escorial, Juan de Herrera dessine quatorze mètres de large sur [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg/960px-Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg | Retable majeur de l’Escorial, 1579-1594 | enchaîné 10]vingt-six de haut, en quatre niveaux d'ordres superposés : dorique, ionique, corinthien, composite. Marbres, jaspes, bronze doré au feu et toiles s'y mêlent ; Pompeo Leoni signe les statues en 1588. Au centre, le tabernacle garde l'eucharistie. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]À Rome, le baroque change l'autel en scène de théâtre. Dans la chapelle Cornaro, le Bernin place de 1647 à 1652 sainte Thérèse en marbre blanc, dans une niche d'édicule ; une fenêtre cachée dans la coupole l'éclaire, et des rayons de stuc doré l'inondent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Santa_Maria_della_Vittoria_-_2.jpg/1280px-Santa_Maria_della_Vittoria_-_2.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]Aux murs, les Cornaro, sculptés en haut-relief, regardent depuis des loges de théâtre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg | Günther, Saint Pierre, Rott am Inn, vers 1760 | enchaîné 10]Au XVIIIe siècle, le rococo allège le retable. En Bavière, Franz Ignaz Günther, né en 1725 et mort à Munich en 1775, sculpte à Rott [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg/960px-Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg | Maitre-autel de l'Eglise de Rott am Inn, vers 1760 | enchaîné 10]am Inn des figures de bois peint en blanc et or : corps élancés, drapés aux plis courbes, couleurs claires. L'autel n'est plus une façade, c'est une danse de lumière. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg | Thorvaldsen, Le Christ, Copenhague, 1821 | enchaîné 10]Au XIXe siècle, le retable se réduit à l'essentiel. À Copenhague, l'église Notre-Dame, rebâtie en style néoclassique après le bombardement britannique de 1807, reçoit de Bertel Thorvaldsen un Christ de marbre blanc, bras ouverts, dans une niche au-dessus de l'autel. D'orfèvrerie, de bois, de théâtre, le retable est devenu une seule figure.
+[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Table_d%27autel.jpg/1280px-Table_d%27autel.jpg | Table d'autel du Ve siècle, abbaye de saint-Victor à Marseille. | enchaîné 10]À l'origine, l'autel est une simple table de pierre, la *mensa*, où l'on célèbre la messe et qui renferme souvent les reliques d'un martyr. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cf/%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg/1280px-%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg | Retable de Saint Orens, XIIe siècle | enchaîné 10]À partir de la fin du XIe siècle, on place derrière lui un retable, du latin *retro tabula altaris*, « derrière la table de l'autel ». En six siècles, ce décor deviendra la pièce maîtresse de l'église. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg | Autel d’argent de saint Jacques, Pistoia, 1287-1456 | noir 5]Au Moyen-âge, le retable est d'abord une œuvre d'orfèvre. À Pistoia, l'autel d'argent de saint Jacques est construit de 1287 à 1456 : un dossal, panneau dressé derrière l'autel, et un devant d'autel, le paliotto, en argent repoussé, orné d'émaux translucides, des scènes de la vie du Christ et de saint Jacques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg/1280px-Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg | Brunelleschi, Prophètes de l’autel d’argent de saint Jacques, Pistoia, 1400-1401 | enchaîné 10]Vers 1400, Filippo Brunelleschi y réalise deux prophètes, Jérémie et Isaïe, avant de bâtir la coupole de Florence. Dès 1293, un voleur, Vanni Fucci, avait pillé la chapelle : Dante l'a mis en Enfer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]Au début du XVe siècle, le marbre remplace l'argent. À Lucques, Jacopo della Quercia sculpte en 1413 le retable Trenta : un polyptyque, ensemble de panneaux juxtaposés, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG/1280px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]où la Vierge à l'Enfant entourée de saints se dresse dans un cadre architectural encore gothique, au-dessus de la prédelle, la bande de petits reliefs qui sert de socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Della Robbia, Autel des Médicis, Florence, 1475-1480 | enchaîné 10]À Florence s'impose un autre matériau : la terre cuite émaillée. Vers 1440, Luca della Robbia recouvre l'argile d'une glaçure à l'étain, un émail blanc opaque, puis la colore : bleu de cobalt, vert de cuivre, jaune d'antimoine, brun de manganèse. Son neveu Andrea diffuse le procédé : figures blanches sur fond bleu, brillantes et durables. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg | Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Au nord des Alpes, le retable devient une immense huche de bois sculpté, dont les volets s'ouvrent et se ferment. À Cracovie, Veit Stoss y travaille de 1477 à 1489 : treize mètres de haut, des figures de près de trois mètres, au centre la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Retable_de_Veit_Stoss_-_53336472978.jpg/1280px-Retable_de_Veit_Stoss_-_53336472978.jpg | Veit Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Dormition de la Vierge entourée des douze apôtres. Pillé par les nazis, le retable est retrouvé dans les caves du château de Nuremberg. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]À Münnerstadt, Tilman Riemenschneider livre entre 1490 et 1492 un retable de Marie-Madeleine [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]entourée d'anges, en tilleul laissé sans polychromie, alors que presque toutes les sculptures sont peintes et dorées. Le grain du bois suffit. [image: https://upload.wikimedia.org/wikipedia/commons/9/96/Retablo_forment_poblet_lou2.jpg | Forment, Retable majeur du monastère de Poblet, vers 1527-1529 | enchaîné 10]En Espagne, le retable majeur occupe tout le chevet. À Poblet, Damià Forment l'élève en albâtre blanc vers 1527-1529 : quatre étages, ou corps, divisés en compartiments par des colonnes et des pilastres à l'antique. C'est son premier retable pleinement Renaissance, après celui du Pilar à Saragosse, encore gothique par bien des traits. Alonso Berruguete, qui a étudié en Italie auprès de Michel-Ange, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]rapporte en Castille une sculpture inquiète. À Valladolid, son retable de saint Benoît, vers 1526-1532, est en bois polychromé [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg/1280px-Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]et doré, aux corps étirés et agités. On pose l'or, puis la couleur, qu'on gratte par endroits pour le faire reparaître : c'est l'estofado. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Bas%C3%ADlica_El_Escorial_2.JPG/960px-Bas%C3%ADlica_El_Escorial_2.JPG | Leoni, Statues du retable majeur de l’Escorial, 1579-1594 | enchaîné 10]Après le concile de Trente, le retable doit proclamer le dogme que les protestants contestent. À l'Escorial, Juan de Herrera dessine quatorze mètres de large sur [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg/960px-Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg | Retable majeur de l’Escorial, 1579-1594 | enchaîné 10]vingt-six de haut, en quatre niveaux d'ordres superposés : dorique, ionique, corinthien, composite. Marbres, jaspes, bronze doré au feu et toiles s'y mêlent ; Pompeo Leoni signe les statues en 1588. Au centre, le tabernacle garde l'eucharistie. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]À Rome, le baroque change l'autel en scène de théâtre. Dans la chapelle Cornaro, le Bernin place de 1647 à 1652 sainte Thérèse en marbre blanc, dans une niche d'édicule ; une fenêtre cachée dans la coupole l'éclaire, et des rayons de stuc doré l'inondent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Santa_Maria_della_Vittoria_-_2.jpg/1280px-Santa_Maria_della_Vittoria_-_2.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]Aux murs, les Cornaro, sculptés en haut-relief, regardent depuis des loges de théâtre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg | Günther, Saint Pierre, Rott am Inn, vers 1760 | enchaîné 10]Au XVIIIe siècle, le rococo allège le retable. En Bavière, Franz Ignaz Günther, né en 1725 et mort à Munich en 1775, sculpte à Rott [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg/960px-Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg | Maitre-autel de l'Eglise de Rott am Inn, vers 1760 | enchaîné 10]am Inn des figures de bois peint en blanc et or : corps élancés, drapés aux plis courbes, couleurs claires. L'autel n'est plus une façade, c'est une danse de lumière. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg | Thorvaldsen, Le Christ, Copenhague, 1821 | enchaîné 10]Au XIXe siècle, le retable se réduit à l'essentiel. À Copenhague, l'église Notre-Dame, rebâtie en style néoclassique après le bombardement britannique de 1807, reçoit de Bertel Thorvaldsen un Christ de marbre blanc, bras ouverts, dans une niche au-dessus de l'autel. D'orfèvrerie, de bois, de théâtre, le retable est devenu une seule figure.
 [sortie: noir]</v>
       </c>
       <c r="D5" t="str">
-        <v>25/10/2026 21:42:25</v>
+        <v>25/10/2026 21:54:59</v>
       </c>
       <c r="E5" t="str">
         <v>Terminé</v>

--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -499,9 +499,28 @@
         <v>Terminé</v>
       </c>
     </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>sc.nature.ronde</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Ronde-bosse (statue, buste…)</v>
+      </c>
+      <c r="C6" t="str" xml:space="preserve">
+        <v xml:space="preserve">[titre: L'évolution de la ronde-bosse | | 5]
+[image: https://mnemart.fr/assets/schemas/schema-relief-ronde-bosse.png |  | enchaîné 10]La ronde-bosse est une sculpture taillée en plein volume, que l'on contourne et que l'on regarde sous tous les angles, à la différence du relief, qui reste attaché à un fond. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Eglise_Saint-Ayoul_Provins_statues-colonnes.jpg/960px-Eglise_Saint-Ayoul_Provins_statues-colonnes.jpg | Portail central de l'église Saint-Ayoul, Provins, 1150-1160 | enchaîné 10]Au Moyen-âge, la statue sert d'abord l'architecture : les statues-colonnes des portails sont encore engagées dans la pierre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Amiens%2C_cathedral_Notre-Dame%2C_the_kings_galery-1.JPG/1280px-Amiens%2C_cathedral_Notre-Dame%2C_the_kings_galery-1.JPG | Galerie des Rois, Cathédrale d'Amiens, 1230-1240 | enchaîné 10]Au XIIIe siècle, sur des édifices comme la Cathédrale d'Amiens, les corps se détachent peu à peu du mur, se creusent d'un hanchement, les visages s'individualisent. Mais les figures demeurent dans leur niche. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG | Ghiberti, Saint Jean-Baptiste, Florence, 1412-1416 | noir 5]Vers 1412, à Florence, la corporation des marchands de draps commande à Lorenzo Ghiberti un saint Jean-Baptiste de bronze pour une niche d'Orsanmichele. [image: https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG | Ghiberti, Saint Jean-Baptiste, Florence, 1412-1416 | enchaîné 10]C'est l'une des premières grandes statues de bronze de la Renaissance. Le drapé aux plis amples reste gothique, et la figure demeure prisonnière de sa niche. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]Vers 1440, Donatello fond pour les Médicis un David de bronze d'environ un mètre soixante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Bronze_David_by_Donatello-Bargello-3.jpg/500px-Bronze_David_by_Donatello-Bargello-3.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]Il est nu, coiffé d'un chapeau et chaussé de bottes ; la plume du casque de Goliath remonte le long de sa cuisse. Dressée seule au milieu de la cour du palais, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/David%2C_Donatello%2C_ca._1440%2C_Bargello_Florenz-02.jpg/960px-David%2C_Donatello%2C_ca._1440%2C_Bargello_Florenz-02.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]c'est la première statue de nu masculin en bronze, libre dans l'espace, depuis l'Antiquité. Le poids repose sur une jambe : le contrapposto antique est retrouvé. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg | Rossellino, Buste de Matteo Palmieri, Florence, 1468 | enchaîné 10]Autre résurrection antique : le buste-portrait. En 1468, Antonio Rossellino taille dans le marbre le buste de l'humaniste Matteo Palmieri [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._02.jpg/960px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._02.jpg | Rossellino, Buste de Matteo Palmieri, Florence, 1468 | enchaîné 10]: rides, chairs fatiguées, regard concentré. Le sculpteur ne flatte plus, il observe, puis polit le marbre pour qu'il rende la peau. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 10]En 1501, Michel-Ange, vingt-six ans, reçoit un énorme bloc de marbre de Carrare, déjà entamé puis abandonné, qui traîne depuis un quart de siècle dans la cour [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/%27David%27_by_Michelangelo_JBU16.JPG/960px-%27David%27_by_Michelangelo_JBU16.JPG | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]de la cathédrale. Les Florentins l'appellent « le Géant ». Il en tire un David de cinq mètres dix-sept, saisi avant le combat : le front plissé, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/%27David%27_by_Michelangelo_FI_Acca_JBS_040.jpg/960px-%27David%27_by_Michelangelo_FI_Acca_JBS_040.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]la main gonflée de veines. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4b/David_michelange.jpg/1280px-David_michelange.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]Il faut quatre jours à plus de quarante hommes pour le rouler jusqu'à la place de la Seigneurie, et des opposants lui jettent des pierres. [image: https://upload.wikimedia.org/wikipedia/commons/4/48/Firenze.Loggia.Perseus01.JPG | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 3]Quatre décennies plus tard, Benvenuto Cellini coule pour le duc Cosme Ier un Persée de bronze, selon la technique de la cire perdue. Au moment de la coulée, le métal commence à figer ; Cellini raconte dans ses Mémoires qu'il jette dans le fourneau environ deux cents plats d'étain pour sauver la fonte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/%22Das_pulsierende_Herzst%C3%BCck_des_mittelalterlichen_Florenz%22._05.jpg/1280px-%22Das_pulsierende_Herzst%C3%BCck_des_mittelalterlichen_Florenz%22._05.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]Inauguré en 1554, le héros brandit la tête de Méduse dans une torsion maniériste [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Italie%2C_Florence%2C_Piazza_della_Signorina%2C_Loggia_dei_Lanzi%2C_Pers%C3%A9e_tenant_la_t%C3%AAte_de_la_Gorgone_par_Benvenuto_Cellini_%281545-1554%29_dont_voici_le_portrait_%2850131085132%29.jpg/960px-thumbnail.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]; derrière son casque, Cellini s'est lui-même caché. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg/500px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]Vers 1580, le Flamand Jean Bologne, sculpteur des Médicis à Florence, fond son Mercure volant. Le dieu ne touche le sol [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Giambologna%2C_mercurio_volante%2C_ante_1580%2C_10.jpg/960px-Giambologna%2C_mercurio_volante%2C_ante_1580%2C_10.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]que par la pointe d'un pied, porté par un souffle de vent, un bras tendu vers le ciel : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-02.jpg/960px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-02.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]seul le bronze, plus résistant que le marbre, permet un tel équilibre. Le corps s'enroule en spirale, la *figura serpentinata*, et oblige le spectateur à tourner autour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Bernini%27s_David_02.jpg/960px-Bernini%27s_David_02.jpg | Bernin, David, Rome, 1623-1624 | enchaîné 10]En 1623, à Rome, Le Bernin, vingt-cinq ans, sculpte pour le cardinal Borghèse un David de marbre. Michel-Ange montrait l'attente ; Le Bernin montre l'action : le corps se tord, la fronde est tendue, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Museo_borghese%2C_sala_del_sole%2C_g.l._bernini%2C_david%2C_1623-24%2C_18_autoritratto.JPG/960px-Museo_borghese%2C_sala_del_sole%2C_g.l._bernini%2C_david%2C_1623-24%2C_18_autoritratto.JPG | Bernin, David, Rome, 1623-1624 | enchaîné 3]le héros mord sa lèvre. Selon son biographe, l'œuvre fut achevée en sept mois, et le futur pape Urbain VIII tenait le miroir où Le Bernin étudiait son propre visage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Louvre_statue_DSC00917.jpg/960px-Louvre_statue_DSC00917.jpg | Puget, Milon de Crotone, Paris, 1671-1682 | enchaîné 10]Le baroque français a son sculpteur : Pierre Puget, né à Marseille, formé en Italie. Pour les jardins de Versailles, il taille de 1671 à 1682 Milon de Crotone : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Milo_of_Croton_by_Pierre_Puget_%28Louvre_MR_2075%29_20141107_134427.jpg/1280px-Milo_of_Croton_by_Pierre_Puget_%28Louvre_MR_2075%29_20141107_134427.jpg | Puget, Milon de Crotone, Paris, 1671-1682 | enchaîné 10]l'athlète vieilli, la main prise dans le tronc qu'il voulait fendre, est dévoré par un lion. La légende parlait de loups ; Puget préfère le lion, plus puissant. Le marbre devient muscle, cri, torsion : c'est la défaite de l'orgueil humain. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG/1280px-Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG | Houdon, Voltaire assis, Paris, 1778 | enchaîné 10]Au siècle des Lumières, la ronde-bosse se fait portrait. En 1778, Voltaire, de retour à Paris après vingt-huit ans d'absence, pose pour Houdon, quelques semaines avant sa mort. Le [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Voltaire-1781.jpg/960px-Voltaire-1781.jpg | Houdon, Voltaire assis, Paris, 1778 | enchaîné 10]sculpteur le montre assis, drapé à l'antique, décharné, un fin sourire aux lèvres. Il creuse la pupille et l'iris du marbre pour accrocher la lumière : le regard semble vivant. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/Apollo_of_the_Belvedere.jpg/960px-Apollo_of_the_Belvedere.jpg | L'Apollon du Belvedere | enchaîné 10]Lorsque Napoléon emporte à Paris l'Apollon du Belvédère, Canova taille un Persée de marbre pour combler la niche [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Persus-with-the-head-of-med.jpg/960px-Persus-with-the-head-of-med.jpg | Canova, Persée tenant la tête de Méduse, Rome, 1801 | enchaîné 5]vide du Vatican ; il est révélé en 1801. Plus de torsion : le héros, serein, tient la tête de Méduse à bout de bras, dans un calme idéal inspiré de l'Antiquité. Canova modèle d'abord le plâtre, fait dégrossir le marbre par ses praticiens, puis polit lui-même la surface jusqu'à la douceur de la peau. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG | Barye, Lion au serpent, Paris, 1832 | enchaîné 10]Au XIXe siècle, le romantisme sort la ronde-bosse des palais et des mythes. Antoine-Louis Barye, ancien apprenti orfèvre qui dessine les fauves au Jardin des plantes, modèle en 1832 le Lion au serpent, fondu en bronze en 1835. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Lion_et_serpent_-_Antoine-Louis_Barye.jpg/1280px-Lion_et_serpent_-_Antoine-Louis_Barye.jpg | Barye, Lion au serpent, Paris, 1832 | enchaîné 10]Le sujet n'est plus un dieu, mais la force brute de la nature. Louis-Philippe achète le bronze, qui reste aux Tuileries de 1836 à 1911. [image: https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG | Degas, La Petite Danseuse de quatorze ans, Washington, 1878-1881 | enchaîné 10]En 1881, à l'exposition des impressionnistes, Edgar Degas présente une danseuse de cire de quatorze ans, Marie van Goethem, élève de l'Opéra. Sur une armature métallique, il modèle de la cire colorée, puis l'habille d'un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Bailarina%2C_Degas.jpg/960px-Bailarina%2C_Degas.jpg | Degas, La Petite Danseuse de quatorze ans, Washington, 1878-1881 | enchaîné 10]vrai tutu, de vrais rubans et de vrais cheveux. Le public est choqué ; Huysmans y voit pourtant la première tentative vraiment moderne de sculpture. Degas n'exposera plus jamais de sculpture ; les bronzes ne seront fondus qu'après sa mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Rodin_The_bronze_age.jpg/500px-Rodin_The_bronze_age.jpg | Rodin, L'Age d'Airain, 1875 | enchaîné 10]Auguste Rodin fait vibrer la matière. Dès 1877, son Âge d'airain est si naturel qu'on l'accuse d'avoir moulé un modèle vivant. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG | Rodin, L’Homme qui marche, Paris, 1907 | enchaîné 10]Avec L'Homme qui marche, il va plus loin : une figure sans tête ni bras, issue d'une étude pour un saint Jean-Baptiste, assume le fragment comme œuvre achevée. Le bronze garde la trace des doigts et du modelage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG/1280px-La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG | Maillol, La Méditerranée, Paris, 1902-1905 | enchaîné 10]Face à ce tourment, Aristide Maillol retrouve le calme. Venu tard à la sculpture après la peinture et la tapisserie, il sculpte de 1902 à 1905 La Méditerranée, que lui commande le comte Harry Kessler : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Museum_of_Modern_Art_-_panoramio.jpg/1280px-Museum_of_Modern_Art_-_panoramio.jpg | Maillol, La Méditerranée, Paris, 1902-1905 | enchaîné 10]une femme assise, nue, sans geste ni histoire, aux volumes pleins et fermés, aux surfaces lisses. Le sujet ne raconte rien ; seule compte la forme. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG/1280px-Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG | Bourdelle, Héraklès archer, Paris, 1909 | enchaîné 10]Antoine Bourdelle, ancien praticien de Rodin, donne à la ronde-bosse une architecture. Son Héraklès archer, fondu en 1909 et montré au Salon de 1910, dépasse deux mètres cinquante : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1f/Hercules_boogschutter_-_Emile-Antoine_Bourdelle_-_Middelheimmuseum_-_4.jpg/1280px-Hercules_boogschutter_-_Emile-Antoine_Bourdelle_-_Middelheimmuseum_-_4.jpg | Bourdelle, Héraklès archer, Paris, 1909 | enchaîné 10]il bande son arc, le pied calé sur un rocher, tout le corps ramassé comme un ressort. Chaque muscle obéit à une géométrie : la statue n'est plus un récit, c'est une structure tendue dans l'espace. En six siècles, la ronde-bosse s'est détachée de la niche, puis du récit.
+[sortie: noir]</v>
+      </c>
+      <c r="D6" t="str">
+        <v>26/10/2026 16:53:15</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Terminé</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/quizzes/textes-natures-techniques.xlsx
+++ b/quizzes/textes-natures-techniques.xlsx
@@ -488,12 +488,12 @@
         <v>Autels et retables</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
-        <v xml:space="preserve">[titre: L'évolution des retables | | 5]
-[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Table_d%27autel.jpg/1280px-Table_d%27autel.jpg | Table d'autel du Ve siècle, abbaye de saint-Victor à Marseille. | enchaîné 10]À l'origine, l'autel est une simple table de pierre, la *mensa*, où l'on célèbre la messe et qui renferme souvent les reliques d'un martyr. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cf/%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg/1280px-%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg | Retable de Saint Orens, XIIe siècle | enchaîné 10]À partir de la fin du XIe siècle, on place derrière lui un retable, du latin *retro tabula altaris*, « derrière la table de l'autel ». En six siècles, ce décor deviendra la pièce maîtresse de l'église. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg | Autel d’argent de saint Jacques, Pistoia, 1287-1456 | noir 5]Au Moyen-âge, le retable est d'abord une œuvre d'orfèvre. À Pistoia, l'autel d'argent de saint Jacques est construit de 1287 à 1456 : un dossal, panneau dressé derrière l'autel, et un devant d'autel, le paliotto, en argent repoussé, orné d'émaux translucides, des scènes de la vie du Christ et de saint Jacques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg/1280px-Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg | Brunelleschi, Prophètes de l’autel d’argent de saint Jacques, Pistoia, 1400-1401 | enchaîné 10]Vers 1400, Filippo Brunelleschi y réalise deux prophètes, Jérémie et Isaïe, avant de bâtir la coupole de Florence. Dès 1293, un voleur, Vanni Fucci, avait pillé la chapelle : Dante l'a mis en Enfer. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]Au début du XVe siècle, le marbre remplace l'argent. À Lucques, Jacopo della Quercia sculpte en 1413 le retable Trenta : un polyptyque, ensemble de panneaux juxtaposés, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG/1280px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]où la Vierge à l'Enfant entourée de saints se dresse dans un cadre architectural encore gothique, au-dessus de la prédelle, la bande de petits reliefs qui sert de socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Della Robbia, Autel des Médicis, Florence, 1475-1480 | enchaîné 10]À Florence s'impose un autre matériau : la terre cuite émaillée. Vers 1440, Luca della Robbia recouvre l'argile d'une glaçure à l'étain, un émail blanc opaque, puis la colore : bleu de cobalt, vert de cuivre, jaune d'antimoine, brun de manganèse. Son neveu Andrea diffuse le procédé : figures blanches sur fond bleu, brillantes et durables. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg | Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Au nord des Alpes, le retable devient une immense huche de bois sculpté, dont les volets s'ouvrent et se ferment. À Cracovie, Veit Stoss y travaille de 1477 à 1489 : treize mètres de haut, des figures de près de trois mètres, au centre la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Retable_de_Veit_Stoss_-_53336472978.jpg/1280px-Retable_de_Veit_Stoss_-_53336472978.jpg | Veit Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Dormition de la Vierge entourée des douze apôtres. Pillé par les nazis, le retable est retrouvé dans les caves du château de Nuremberg. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]À Münnerstadt, Tilman Riemenschneider livre entre 1490 et 1492 un retable de Marie-Madeleine [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]entourée d'anges, en tilleul laissé sans polychromie, alors que presque toutes les sculptures sont peintes et dorées. Le grain du bois suffit. [image: https://upload.wikimedia.org/wikipedia/commons/9/96/Retablo_forment_poblet_lou2.jpg | Forment, Retable majeur du monastère de Poblet, vers 1527-1529 | enchaîné 10]En Espagne, le retable majeur occupe tout le chevet. À Poblet, Damià Forment l'élève en albâtre blanc vers 1527-1529 : quatre étages, ou corps, divisés en compartiments par des colonnes et des pilastres à l'antique. C'est son premier retable pleinement Renaissance, après celui du Pilar à Saragosse, encore gothique par bien des traits. Alonso Berruguete, qui a étudié en Italie auprès de Michel-Ange, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]rapporte en Castille une sculpture inquiète. À Valladolid, son retable de saint Benoît, vers 1526-1532, est en bois polychromé [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg/1280px-Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]et doré, aux corps étirés et agités. On pose l'or, puis la couleur, qu'on gratte par endroits pour le faire reparaître : c'est l'estofado. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Bas%C3%ADlica_El_Escorial_2.JPG/960px-Bas%C3%ADlica_El_Escorial_2.JPG | Leoni, Statues du retable majeur de l’Escorial, 1579-1594 | enchaîné 10]Après le concile de Trente, le retable doit proclamer le dogme que les protestants contestent. À l'Escorial, Juan de Herrera dessine quatorze mètres de large sur [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg/960px-Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg | Retable majeur de l’Escorial, 1579-1594 | enchaîné 10]vingt-six de haut, en quatre niveaux d'ordres superposés : dorique, ionique, corinthien, composite. Marbres, jaspes, bronze doré au feu et toiles s'y mêlent ; Pompeo Leoni signe les statues en 1588. Au centre, le tabernacle garde l'eucharistie. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]À Rome, le baroque change l'autel en scène de théâtre. Dans la chapelle Cornaro, le Bernin place de 1647 à 1652 sainte Thérèse en marbre blanc, dans une niche d'édicule ; une fenêtre cachée dans la coupole l'éclaire, et des rayons de stuc doré l'inondent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Santa_Maria_della_Vittoria_-_2.jpg/1280px-Santa_Maria_della_Vittoria_-_2.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]Aux murs, les Cornaro, sculptés en haut-relief, regardent depuis des loges de théâtre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg | Günther, Saint Pierre, Rott am Inn, vers 1760 | enchaîné 10]Au XVIIIe siècle, le rococo allège le retable. En Bavière, Franz Ignaz Günther, né en 1725 et mort à Munich en 1775, sculpte à Rott [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg/960px-Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg | Maitre-autel de l'Eglise de Rott am Inn, vers 1760 | enchaîné 10]am Inn des figures de bois peint en blanc et or : corps élancés, drapés aux plis courbes, couleurs claires. L'autel n'est plus une façade, c'est une danse de lumière. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg | Thorvaldsen, Le Christ, Copenhague, 1821 | enchaîné 10]Au XIXe siècle, le retable se réduit à l'essentiel. À Copenhague, l'église Notre-Dame, rebâtie en style néoclassique après le bombardement britannique de 1807, reçoit de Bertel Thorvaldsen un Christ de marbre blanc, bras ouverts, dans une niche au-dessus de l'autel. D'orfèvrerie, de bois, de théâtre, le retable est devenu une seule figure.
+        <v xml:space="preserve">[titre: L'évolution des retables sculptés | | 5]
+[image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Table_d%27autel.jpg/1280px-Table_d%27autel.jpg | Table d'autel du Ve siècle, abbaye de saint-Victor à Marseille. | enchaîné 10]À l'origine, l'autel est une simple table de pierre, la *mensa*, où l'on célèbre la messe et qui renferme souvent les reliques d'un martyr. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cf/%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg/1280px-%28Auch%29_Retable_de_Saint_Orens_XIIe_-_Mus%C3%A9e_des_Am%C3%A9riques_-_Auch.jpg | Retable de Saint Orens, XIIe siècle | enchaîné 10]À partir de la fin du XIe siècle, la liturgie évolue, les prêtres officient dos aux fidèles et devant l'autel, ce qui libère la place derrière celui-ci: on place donc derrière lui un retable, souvent bas et simple, du latin *retro tabula altaris*, « derrière la table de l'autel ». En six siècles, ce décor deviendra la pièce maîtresse de l'église. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg | Autel d’argent de saint Jacques, Pistoia, 1287-1456 | noir 5]Au XIIIe siècle, le retable devient parfois une œuvre d'orfèvre. À Pistoia, l'autel d'argent de saint Jacques est construit de 1287 à 1456. Le retable s'harmonise avec le devant d'autel, l'antependium: ils sont en argent repoussé, orné d'émaux translucides,  et représentent des scènes de la vie du Christ et de saint Jacques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg/1280px-Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg | Brunelleschi, Prophètes de l’autel d’argent de saint Jacques, Pistoia, 1400-1401 | enchaîné 10]Vers 1400, Filippo Brunelleschi y réalise deux prophètes, Jérémie et Isaïe, avant de bâtir la coupole de Florence. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]Au début du XVe siècle, le marbre remplace l'argent. À Lucques, Jacopo della Quercia sculpte en 1413 le retable Trenta. Il s'agit d'un polyptyque, un ensemble de panneaux juxtaposés, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG/1280px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_02.JPG | Della Quercia, Retable Trenta, Lucques, 1411-1413 | enchaîné 10]où la Vierge à l'Enfant entourée de saints se dresse dans un cadre architectural encore gothique, au-dessus de la prédelle, la bande de petits reliefs qui sert de socle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Della Robbia, Autel des Médicis, Florence, 1475-1480 | enchaîné 10]À Florence s'impose un autre matériau : la terre cuite émaillée. Vers 1440, Luca della Robbia recouvre l'argile d'une glaçure à l'étain, un émail blanc opaque, puis la colore : bleu de cobalt, vert de cuivre, jaune d'antimoine, brun de manganèse. Son neveu Andrea diffuse le procédé : figures blanches sur fond bleu, brillantes et durables. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg | Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Au nord des Alpes, le retable devient une immense huche de bois sculpté, dont les volets s'ouvrent et se ferment, surmontée d'un couronnement fait de flèches ciselées, pinacles gothiques et motifs de dentelle. À Cracovie, Veit Stoss y travaille de 1477 à 1489 : treize mètres de haut, des figures de près de trois mètres, au centre la [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/Retable_de_Veit_Stoss_-_53336472978.jpg/1280px-Retable_de_Veit_Stoss_-_53336472978.jpg | Veit Stoss, Retable de l’église Notre-Dame, Cracovie, 1477-1489 | enchaîné 10]Dormition de la Vierge entourée des douze apôtres. Pillé par les nazis, le retable est retrouvé dans les caves du château de Nuremberg. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]À Münnerstadt, Tilman Riemenschneider livre entre 1490 et 1492 un retable de Marie-Madeleine [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fb/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_007.JPG | Riemenschneider, Retable de Sainte Marie-Madeleine, Münnerstadt, 1490-1492 | enchaîné 10]entourée d'anges, en tilleul laissé sans polychromie, alors que presque toutes les sculptures de ce type à cette époque sont peintes et dorées. Ici le grain du bois suffit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Koninklijke_Musea_Kunst_en_Geschiedenis_Brussel_17.jpg/1280px-Koninklijke_Musea_Kunst_en_Geschiedenis_Brussel_17.jpg | Jan Borman, Retable de Saint Georges, 1493es, 1493es, | enchaîné 10]Cette tradition se retrouve à Bruxelles avec Jan Borman. En témoigne son très célèbre retable de Saint George [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c8/Retable_of_St._George2.JPG/1280px-Retable_of_St._George2.JPG | Jan Borman, Retable de saint Georges, 1493 | enchaîné 10]où celui-ci représente, de façon très réaliste, les différentes tortures qu’a subies saint Georges, ainsi que sa décapitation ultime.   [image: https://upload.wikimedia.org/wikipedia/commons/9/96/Retablo_forment_poblet_lou2.jpg | Forment, Retable majeur du monastère de Poblet, vers 1527-1529 | enchaîné 10]En Espagne, les grands retables majeurs occupent tout le chevet des édifices religieux. À Poblet, Damian Forment élève le sien en albâtre blanc vers 1527-1529 : quatre étages, ou corps, divisés en compartiments par des colonnes et des pilastres à l'antique. C'est son premier retable pleinement Renaissance, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a1/Altar_mayor_Bas%C3%ADlica_del_Pilar.jpg/960px-Altar_mayor_Bas%C3%ADlica_del_Pilar.jpg | Damian Forment, Retable Majeur de la Cathédrale de Saragosse, 1509-1518 | enchaîné 10]après celui du Pilar à Saragosse, encore gothique par bien des traits. Alonso Berruguete, qui a étudié en Italie auprès de Michel-Ange, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]rapporte en Castille une sculpture inquiète. À Valladolid, son retable de saint Benoît, vers 1526-1532, est en bois polychromé [image: https://upload.wikimedia.org/wikipedia/commons/thumb/c/cc/Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg/1280px-Alonso_Berruguete%2C_San_Benito_de_Nursia.jpg | Berruguete, Retable de Saint Benoît, Valladolid, 1526-1532 | enchaîné 10]et doré, aux corps étirés et agités. On pose l'or, puis la couleur, qu'on gratte par endroits pour le faire reparaître : c'est l'estofado. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Bas%C3%ADlica_El_Escorial_2.JPG/960px-Bas%C3%ADlica_El_Escorial_2.JPG | Leoni, Statues du retable majeur de l’Escorial, 1579-1594 | enchaîné 10]Après le concile de Trente, le retable doit proclamer avec encore plus d'éclat le dogme que les protestants contestent. À l'Escorial, Juan de Herrera dessine un retable à colonnes baroque de quatorze mètres de large sur [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg/960px-Retablo_mayor_de_San_Lorenzo_de_El_Escorial.jpg | Retable majeur de l’Escorial, 1579-1594 | enchaîné 10]vingt-six de haut, en quatre niveaux d'ordres superposés : dorique, ionique, corinthien, composite. Marbres, jaspes, bronze doré au feu et toiles s'y mêlent ; Pompeo Leoni signe les statues en 1588. Au centre, le tabernacle très visible garde l'eucharistie, dogme remis en cause par le protestantisme. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ecstasy_of_St._Teresa_HDR.jpg/1280px-Ecstasy_of_St._Teresa_HDR.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]À Rome, le baroque change l'autel en scène de théâtre. A la volonté pédagogique des grands retables du passé, c'est ici l'émotion pure qui est recherchée. Dans la chapelle Cornaro, le Bernin place de 1647 à 1652 sainte Thérèse en marbre blanc, dans une niche d'édicule ; une fenêtre cachée dans la coupole l'éclaire, et des rayons de stuc doré l'inondent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Santa_Maria_della_Vittoria_-_2.jpg/1280px-Santa_Maria_della_Vittoria_-_2.jpg | Bernin, L’Extase de sainte Thérèse, Rome, 1647-1652 | enchaîné 10]Aux murs, les Cornaro, sculptés en haut-relief, regardent depuis des loges de théâtre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e6/St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg/960px-St._Petrus_Hauptaltar_St._Peter_und_Paul_Neustift_Freising-1.jpg | Günther, Saint Pierre, Rott am Inn, vers 1760 | enchaîné 10]Au XVIIIe siècle, le rococo allège le retable. En Bavière, Franz Ignaz Günther, né en 1725 et mort à Munich en 1775, sculpte à Rott [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0d/Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg/960px-Rott_am_Inn_St._Marinus_und_Anianus_Hauptaltar_070.jpg | Maitre-autel de l'Eglise de Rott am Inn, vers 1760 | enchaîné 10]am Inn des figures de bois peint en blanc et or : corps élancés, drapés aux plis courbes, couleurs claires. Le retable n'est plus une façade immobile, c'est une danse de lumière. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/48/03_-_Autel_et_baldaquin_de_Saint-Bruno_des_Chartreux.JPG/960px-03_-_Autel_et_baldaquin_de_Saint-Bruno_des_Chartreux.JPG | Eglise Saint-Bruno des Chartreux, Lyon | enchaîné 10]A Lyon, à l'église Saint-Bruno des Chartreux, il disparaît déjà, remplacé par un baldaquin qui surplombe l'autel pour en délimiter l'espace spirituel ouvert à la lumière.  [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/Vor_Frue_Kirke_Copenhagen_altar.jpg/960px-Vor_Frue_Kirke_Copenhagen_altar.jpg | Thorvaldsen, Le Christ, Copenhague, 1821 | enchaîné 10]Au XIXe siècle, le retable, jugé trop surchargé, parfois détruit, se réduit souvent à l'essentiel quand il est conservé. À Copenhague, l'église Notre-Dame, rebâtie en style néoclassique après le bombardement britannique de 1807, reçoit de Bertel Thorvaldsen un Christ de marbre blanc, bras ouverts, dans une niche au-dessus de l'autel. [image: https://upload.wikimedia.org/wikipedia/commons/9/94/7_Evry-apsidal-area_photo_Pino-Musi.jpg | Cathédrale de la Résurrection d'Évry | enchaîné 10]Il disparaît totalement dans les églises à l'architecture contemporaine car après Vatican II, en 1965, la liturgie change à nouveau et les prêtres doivent dire la messe face aux fidèles, derrière l'autel, qui retrouve sa vocation de table épurée, rapprochée des fidèles, dans l'espace vide et lumineux du choeur.
 [sortie: noir]</v>
       </c>
       <c r="D5" t="str">
-        <v>25/10/2026 21:54:59</v>
+        <v>26/10/2026 21:37:01</v>
       </c>
       <c r="E5" t="str">
         <v>Terminé</v>
@@ -508,11 +508,11 @@
       </c>
       <c r="C6" t="str" xml:space="preserve">
         <v xml:space="preserve">[titre: L'évolution de la ronde-bosse | | 5]
-[image: https://mnemart.fr/assets/schemas/schema-relief-ronde-bosse.png |  | enchaîné 10]La ronde-bosse est une sculpture taillée en plein volume, que l'on contourne et que l'on regarde sous tous les angles, à la différence du relief, qui reste attaché à un fond. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Eglise_Saint-Ayoul_Provins_statues-colonnes.jpg/960px-Eglise_Saint-Ayoul_Provins_statues-colonnes.jpg | Portail central de l'église Saint-Ayoul, Provins, 1150-1160 | enchaîné 10]Au Moyen-âge, la statue sert d'abord l'architecture : les statues-colonnes des portails sont encore engagées dans la pierre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Amiens%2C_cathedral_Notre-Dame%2C_the_kings_galery-1.JPG/1280px-Amiens%2C_cathedral_Notre-Dame%2C_the_kings_galery-1.JPG | Galerie des Rois, Cathédrale d'Amiens, 1230-1240 | enchaîné 10]Au XIIIe siècle, sur des édifices comme la Cathédrale d'Amiens, les corps se détachent peu à peu du mur, se creusent d'un hanchement, les visages s'individualisent. Mais les figures demeurent dans leur niche. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG | Ghiberti, Saint Jean-Baptiste, Florence, 1412-1416 | noir 5]Vers 1412, à Florence, la corporation des marchands de draps commande à Lorenzo Ghiberti un saint Jean-Baptiste de bronze pour une niche d'Orsanmichele. [image: https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG | Ghiberti, Saint Jean-Baptiste, Florence, 1412-1416 | enchaîné 10]C'est l'une des premières grandes statues de bronze de la Renaissance. Le drapé aux plis amples reste gothique, et la figure demeure prisonnière de sa niche. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]Vers 1440, Donatello fond pour les Médicis un David de bronze d'environ un mètre soixante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Bronze_David_by_Donatello-Bargello-3.jpg/500px-Bronze_David_by_Donatello-Bargello-3.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]Il est nu, coiffé d'un chapeau et chaussé de bottes ; la plume du casque de Goliath remonte le long de sa cuisse. Dressée seule au milieu de la cour du palais, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/David%2C_Donatello%2C_ca._1440%2C_Bargello_Florenz-02.jpg/960px-David%2C_Donatello%2C_ca._1440%2C_Bargello_Florenz-02.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]c'est la première statue de nu masculin en bronze, libre dans l'espace, depuis l'Antiquité. Le poids repose sur une jambe : le contrapposto antique est retrouvé. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg | Rossellino, Buste de Matteo Palmieri, Florence, 1468 | enchaîné 10]Autre résurrection antique : le buste-portrait. En 1468, Antonio Rossellino taille dans le marbre le buste de l'humaniste Matteo Palmieri [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._02.jpg/960px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._02.jpg | Rossellino, Buste de Matteo Palmieri, Florence, 1468 | enchaîné 10]: rides, chairs fatiguées, regard concentré. Le sculpteur ne flatte plus, il observe, puis polit le marbre pour qu'il rende la peau. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 10]En 1501, Michel-Ange, vingt-six ans, reçoit un énorme bloc de marbre de Carrare, déjà entamé puis abandonné, qui traîne depuis un quart de siècle dans la cour [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/%27David%27_by_Michelangelo_JBU16.JPG/960px-%27David%27_by_Michelangelo_JBU16.JPG | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]de la cathédrale. Les Florentins l'appellent « le Géant ». Il en tire un David de cinq mètres dix-sept, saisi avant le combat : le front plissé, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/%27David%27_by_Michelangelo_FI_Acca_JBS_040.jpg/960px-%27David%27_by_Michelangelo_FI_Acca_JBS_040.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]la main gonflée de veines. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4b/David_michelange.jpg/1280px-David_michelange.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]Il faut quatre jours à plus de quarante hommes pour le rouler jusqu'à la place de la Seigneurie, et des opposants lui jettent des pierres. [image: https://upload.wikimedia.org/wikipedia/commons/4/48/Firenze.Loggia.Perseus01.JPG | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 3]Quatre décennies plus tard, Benvenuto Cellini coule pour le duc Cosme Ier un Persée de bronze, selon la technique de la cire perdue. Au moment de la coulée, le métal commence à figer ; Cellini raconte dans ses Mémoires qu'il jette dans le fourneau environ deux cents plats d'étain pour sauver la fonte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/%22Das_pulsierende_Herzst%C3%BCck_des_mittelalterlichen_Florenz%22._05.jpg/1280px-%22Das_pulsierende_Herzst%C3%BCck_des_mittelalterlichen_Florenz%22._05.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]Inauguré en 1554, le héros brandit la tête de Méduse dans une torsion maniériste [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Italie%2C_Florence%2C_Piazza_della_Signorina%2C_Loggia_dei_Lanzi%2C_Pers%C3%A9e_tenant_la_t%C3%AAte_de_la_Gorgone_par_Benvenuto_Cellini_%281545-1554%29_dont_voici_le_portrait_%2850131085132%29.jpg/960px-thumbnail.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]; derrière son casque, Cellini s'est lui-même caché. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg/500px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]Vers 1580, le Flamand Jean Bologne, sculpteur des Médicis à Florence, fond son Mercure volant. Le dieu ne touche le sol [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Giambologna%2C_mercurio_volante%2C_ante_1580%2C_10.jpg/960px-Giambologna%2C_mercurio_volante%2C_ante_1580%2C_10.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]que par la pointe d'un pied, porté par un souffle de vent, un bras tendu vers le ciel : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-02.jpg/960px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-02.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]seul le bronze, plus résistant que le marbre, permet un tel équilibre. Le corps s'enroule en spirale, la *figura serpentinata*, et oblige le spectateur à tourner autour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Bernini%27s_David_02.jpg/960px-Bernini%27s_David_02.jpg | Bernin, David, Rome, 1623-1624 | enchaîné 10]En 1623, à Rome, Le Bernin, vingt-cinq ans, sculpte pour le cardinal Borghèse un David de marbre. Michel-Ange montrait l'attente ; Le Bernin montre l'action : le corps se tord, la fronde est tendue, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Museo_borghese%2C_sala_del_sole%2C_g.l._bernini%2C_david%2C_1623-24%2C_18_autoritratto.JPG/960px-Museo_borghese%2C_sala_del_sole%2C_g.l._bernini%2C_david%2C_1623-24%2C_18_autoritratto.JPG | Bernin, David, Rome, 1623-1624 | enchaîné 3]le héros mord sa lèvre. Selon son biographe, l'œuvre fut achevée en sept mois, et le futur pape Urbain VIII tenait le miroir où Le Bernin étudiait son propre visage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Louvre_statue_DSC00917.jpg/960px-Louvre_statue_DSC00917.jpg | Puget, Milon de Crotone, Paris, 1671-1682 | enchaîné 10]Le baroque français a son sculpteur : Pierre Puget, né à Marseille, formé en Italie. Pour les jardins de Versailles, il taille de 1671 à 1682 Milon de Crotone : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Milo_of_Croton_by_Pierre_Puget_%28Louvre_MR_2075%29_20141107_134427.jpg/1280px-Milo_of_Croton_by_Pierre_Puget_%28Louvre_MR_2075%29_20141107_134427.jpg | Puget, Milon de Crotone, Paris, 1671-1682 | enchaîné 10]l'athlète vieilli, la main prise dans le tronc qu'il voulait fendre, est dévoré par un lion. La légende parlait de loups ; Puget préfère le lion, plus puissant. Le marbre devient muscle, cri, torsion : c'est la défaite de l'orgueil humain. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG/1280px-Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG | Houdon, Voltaire assis, Paris, 1778 | enchaîné 10]Au siècle des Lumières, la ronde-bosse se fait portrait. En 1778, Voltaire, de retour à Paris après vingt-huit ans d'absence, pose pour Houdon, quelques semaines avant sa mort. Le [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Voltaire-1781.jpg/960px-Voltaire-1781.jpg | Houdon, Voltaire assis, Paris, 1778 | enchaîné 10]sculpteur le montre assis, drapé à l'antique, décharné, un fin sourire aux lèvres. Il creuse la pupille et l'iris du marbre pour accrocher la lumière : le regard semble vivant. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/Apollo_of_the_Belvedere.jpg/960px-Apollo_of_the_Belvedere.jpg | L'Apollon du Belvedere | enchaîné 10]Lorsque Napoléon emporte à Paris l'Apollon du Belvédère, Canova taille un Persée de marbre pour combler la niche [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Persus-with-the-head-of-med.jpg/960px-Persus-with-the-head-of-med.jpg | Canova, Persée tenant la tête de Méduse, Rome, 1801 | enchaîné 5]vide du Vatican ; il est révélé en 1801. Plus de torsion : le héros, serein, tient la tête de Méduse à bout de bras, dans un calme idéal inspiré de l'Antiquité. Canova modèle d'abord le plâtre, fait dégrossir le marbre par ses praticiens, puis polit lui-même la surface jusqu'à la douceur de la peau. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG | Barye, Lion au serpent, Paris, 1832 | enchaîné 10]Au XIXe siècle, le romantisme sort la ronde-bosse des palais et des mythes. Antoine-Louis Barye, ancien apprenti orfèvre qui dessine les fauves au Jardin des plantes, modèle en 1832 le Lion au serpent, fondu en bronze en 1835. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Lion_et_serpent_-_Antoine-Louis_Barye.jpg/1280px-Lion_et_serpent_-_Antoine-Louis_Barye.jpg | Barye, Lion au serpent, Paris, 1832 | enchaîné 10]Le sujet n'est plus un dieu, mais la force brute de la nature. Louis-Philippe achète le bronze, qui reste aux Tuileries de 1836 à 1911. [image: https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG | Degas, La Petite Danseuse de quatorze ans, Washington, 1878-1881 | enchaîné 10]En 1881, à l'exposition des impressionnistes, Edgar Degas présente une danseuse de cire de quatorze ans, Marie van Goethem, élève de l'Opéra. Sur une armature métallique, il modèle de la cire colorée, puis l'habille d'un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Bailarina%2C_Degas.jpg/960px-Bailarina%2C_Degas.jpg | Degas, La Petite Danseuse de quatorze ans, Washington, 1878-1881 | enchaîné 10]vrai tutu, de vrais rubans et de vrais cheveux. Le public est choqué ; Huysmans y voit pourtant la première tentative vraiment moderne de sculpture. Degas n'exposera plus jamais de sculpture ; les bronzes ne seront fondus qu'après sa mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Rodin_The_bronze_age.jpg/500px-Rodin_The_bronze_age.jpg | Rodin, L'Age d'Airain, 1875 | enchaîné 10]Auguste Rodin fait vibrer la matière. Dès 1877, son Âge d'airain est si naturel qu'on l'accuse d'avoir moulé un modèle vivant. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG | Rodin, L’Homme qui marche, Paris, 1907 | enchaîné 10]Avec L'Homme qui marche, il va plus loin : une figure sans tête ni bras, issue d'une étude pour un saint Jean-Baptiste, assume le fragment comme œuvre achevée. Le bronze garde la trace des doigts et du modelage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG/1280px-La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG | Maillol, La Méditerranée, Paris, 1902-1905 | enchaîné 10]Face à ce tourment, Aristide Maillol retrouve le calme. Venu tard à la sculpture après la peinture et la tapisserie, il sculpte de 1902 à 1905 La Méditerranée, que lui commande le comte Harry Kessler : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Museum_of_Modern_Art_-_panoramio.jpg/1280px-Museum_of_Modern_Art_-_panoramio.jpg | Maillol, La Méditerranée, Paris, 1902-1905 | enchaîné 10]une femme assise, nue, sans geste ni histoire, aux volumes pleins et fermés, aux surfaces lisses. Le sujet ne raconte rien ; seule compte la forme. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG/1280px-Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG | Bourdelle, Héraklès archer, Paris, 1909 | enchaîné 10]Antoine Bourdelle, ancien praticien de Rodin, donne à la ronde-bosse une architecture. Son Héraklès archer, fondu en 1909 et montré au Salon de 1910, dépasse deux mètres cinquante : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1f/Hercules_boogschutter_-_Emile-Antoine_Bourdelle_-_Middelheimmuseum_-_4.jpg/1280px-Hercules_boogschutter_-_Emile-Antoine_Bourdelle_-_Middelheimmuseum_-_4.jpg | Bourdelle, Héraklès archer, Paris, 1909 | enchaîné 10]il bande son arc, le pied calé sur un rocher, tout le corps ramassé comme un ressort. Chaque muscle obéit à une géométrie : la statue n'est plus un récit, c'est une structure tendue dans l'espace. En six siècles, la ronde-bosse s'est détachée de la niche, puis du récit.
+[image: https://mnemart.fr/assets/schemas/schema-relief-ronde-bosse.png |  | noir 10]La ronde-bosse est une sculpture taillée en plein volume, que l'on contourne et que l'on regarde sous tous les angles, à la différence du relief, qui reste attaché à un fond. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Eglise_Saint-Ayoul_Provins_statues-colonnes.jpg/960px-Eglise_Saint-Ayoul_Provins_statues-colonnes.jpg | Portail central de l'église Saint-Ayoul, Provins, 1150-1160 | enchaîné 10]Au Moyen-âge, la statue sert d'abord l'architecture : les statues-colonnes des portails sont encore engagées dans la pierre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Amiens%2C_cathedral_Notre-Dame%2C_the_kings_galery-1.JPG/1280px-Amiens%2C_cathedral_Notre-Dame%2C_the_kings_galery-1.JPG | Galerie des Rois, Cathédrale d'Amiens, 1230-1240 | enchaîné 10]Au XIIIe siècle, sur les façades des édifices comme la Cathédrale d'Amiens, les corps se détachent peu à peu du mur, se creusent d'un hanchement, les visages s'individualisent. Mais les figures demeurent dans leur niche. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG | Ghiberti, Saint Jean-Baptiste, Florence, 1412-1416 | noir 5]Vers 1412, à Florence, la corporation des marchands de draps commande à Lorenzo Ghiberti un *Saint Jean-Baptiste* de bronze pour une niche d'Orsanmichele. [image: https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG | Ghiberti, Saint Jean-Baptiste, Florence, 1412-1416 | enchaîné 10]C'est l'une des premières grandes statues de bronze de la Renaissance. Le drapé aux plis amples reste gothique, et la figure demeure prisonnière de sa niche. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]Vers 1440, Donatello fond pour les Médicis un *David* de bronze d'environ un mètre soixante. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Bronze_David_by_Donatello-Bargello-3.jpg/500px-Bronze_David_by_Donatello-Bargello-3.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]Il est nu, coiffé d'un chapeau et chaussé de bottes ; la plume du casque de Goliath remonte le long de sa cuisse. Dressée seule au milieu de la cour du palais des Médicis, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/David%2C_Donatello%2C_ca._1440%2C_Bargello_Florenz-02.jpg/960px-David%2C_Donatello%2C_ca._1440%2C_Bargello_Florenz-02.jpg | Donatello, David, Florence, vers 1440 | enchaîné 10]c'est la première statue de nu masculin en bronze, libre dans l'espace, depuis l'Antiquité. Le poids repose sur une jambe : le contrapposto antique est retrouvé. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg | Rossellino, Buste de Matteo Palmieri, Florence, 1468 | enchaîné 10]Autre résurrection à l'antique : le buste-portrait. En 1468, Antonio Rossellino taille dans le marbre le buste de l'humaniste Matteo Palmieri [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/af/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._02.jpg/960px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._02.jpg | Rossellino, Buste de Matteo Palmieri, Florence, 1468 | enchaîné 10]: rides, chairs fatiguées, regard concentré. Le sculpteur ne flatte plus, il observe, puis polit le marbre pour qu'il rende la peau. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 10]En 1501, Michel-Ange, vingt-six ans, reçoit un énorme bloc de marbre de Carrare, déjà entamé puis abandonné, qui traîne depuis un quart de siècle dans la cour [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/%27David%27_by_Michelangelo_JBU16.JPG/960px-%27David%27_by_Michelangelo_JBU16.JPG | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]de la cathédrale. Les Florentins l'appellent « le Géant ». Il en tire un *David* de cinq mètres dix-sept, saisi avant le combat : le front plissé, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/%27David%27_by_Michelangelo_FI_Acca_JBS_040.jpg/960px-%27David%27_by_Michelangelo_FI_Acca_JBS_040.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]la main gonflée de veines. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4b/David_michelange.jpg/1280px-David_michelange.jpg | Michel-Ange, David, Florence, 1501-1504 | enchaîné 3]Il faut quatre jours à plus de quarante hommes pour le rouler jusqu'à la place de la Seigneurie, et des opposants lui jettent des pierres. [image: https://upload.wikimedia.org/wikipedia/commons/4/48/Firenze.Loggia.Perseus01.JPG | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 3]Quatre décennies plus tard, Benvenuto Cellini coule pour le duc Cosme Ier un *Persée* de bronze, selon la technique de la cire perdue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Florenz_2014_-_David_und_Perseus.jpg/960px-Florenz_2014_-_David_und_Perseus.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]Au moment de la coulée, le métal commence à figer ; Cellini raconte dans ses *Mémoires* qu'il jette dans le fourneau environ deux cents plats d'étain pour sauver la fonte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/%22Das_pulsierende_Herzst%C3%BCck_des_mittelalterlichen_Florenz%22._05.jpg/1280px-%22Das_pulsierende_Herzst%C3%BCck_des_mittelalterlichen_Florenz%22._05.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]Inauguré en 1554, le héros brandit la tête de Méduse dans une torsion maniériste [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Italie%2C_Florence%2C_Piazza_della_Signorina%2C_Loggia_dei_Lanzi%2C_Pers%C3%A9e_tenant_la_t%C3%AAte_de_la_Gorgone_par_Benvenuto_Cellini_%281545-1554%29_dont_voici_le_portrait_%2850131085132%29.jpg/960px-thumbnail.jpg | Cellini, Persée avec la tête de Méduse, Florence, 1545-1554 | enchaîné 10]; derrière son casque, Cellini s'est lui-même représenté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg/500px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]Vers 1580, le Flamand Jean Bologne, sculpteur des Médicis à Florence, fond son *Mercure volant*. Le dieu ne touche le sol [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Giambologna%2C_mercurio_volante%2C_ante_1580%2C_10.jpg/960px-Giambologna%2C_mercurio_volante%2C_ante_1580%2C_10.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]que par la pointe d'un pied, porté par un souffle de vent, un bras tendu vers le ciel : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-02.jpg/960px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-02.jpg | Jean Bologne, Mercure volant, Florence, vers 1580 | enchaîné 10]seul le bronze, plus résistant que le marbre, permet un tel équilibre. Le corps s'enroule en spirale, la *figura serpentinata*, et oblige le spectateur à tourner autour. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Bernini%27s_David_02.jpg/960px-Bernini%27s_David_02.jpg | Bernin, David, Rome, 1623-1624 | enchaîné 10]En 1623, à Rome, Le Bernin, vingt-cinq ans, sculpte pour le cardinal Borghèse un *David* de marbre. Michel-Ange montrait l'attente ; Le Bernin montre l'action : le corps se tord, la fronde est tendue, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Museo_borghese%2C_sala_del_sole%2C_g.l._bernini%2C_david%2C_1623-24%2C_18_autoritratto.JPG/960px-Museo_borghese%2C_sala_del_sole%2C_g.l._bernini%2C_david%2C_1623-24%2C_18_autoritratto.JPG | Bernin, David, Rome, 1623-1624 | enchaîné 3]le héros mord sa lèvre. Selon son biographe, l'œuvre fut achevée en sept mois, et le futur pape Urbain VIII tenait le miroir où Le Bernin étudiait son propre visage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/2/2b/Louvre_statue_DSC00917.jpg/960px-Louvre_statue_DSC00917.jpg | Puget, Milon de Crotone, Paris, 1671-1682 | enchaîné 10]Le baroque français a son sculpteur : Pierre Puget, né à Marseille, formé en Italie. Pour les jardins de Versailles, il taille de 1671 à 1682 *Milon de Crotone* : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Milo_of_Croton_by_Pierre_Puget_%28Louvre_MR_2075%29_20141107_134427.jpg/1280px-Milo_of_Croton_by_Pierre_Puget_%28Louvre_MR_2075%29_20141107_134427.jpg | Puget, Milon de Crotone, Paris, 1671-1682 | enchaîné 10]l'athlète vieilli, la main prise dans le tronc qu'il voulait fendre, est dévoré par un lion. La légende parlait de loups ; Puget préfère le lion, plus puissant. Le marbre devient muscle, cri, torsion : c'est la défaite de l'orgueil humain. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG/1280px-Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG | Houdon, Voltaire assis, Paris, 1778 | enchaîné 10]Au siècle des Lumières, la ronde-bosse se fait portrait. En 1778, Voltaire, de retour à Paris après vingt-huit ans d'absence, pose pour Houdon, quelques semaines avant sa mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Voltaire-1781.jpg/960px-Voltaire-1781.jpg | Houdon, Voltaire assis, Paris, 1778 | enchaîné 10]Le sculpteur le montre assis, drapé à l'antique, décharné, un fin sourire aux lèvres. Il creuse la pupille et l'iris du marbre pour accrocher la lumière : le regard semble vivant. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/Apollo_of_the_Belvedere.jpg/960px-Apollo_of_the_Belvedere.jpg | L'Apollon du Belvedere | enchaîné 10]Lorsque Napoléon emporte à Paris l'*Apollon du Belvédère*, Canova taille un *Persée* de marbre pour combler la niche [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Persus-with-the-head-of-med.jpg/960px-Persus-with-the-head-of-med.jpg | Canova, Persée tenant la tête de Méduse, Rome, 1801 | enchaîné 5]vide du Vatican ; il est révélé en 1801. Plus de torsion : le héros, serein, tient la tête de Méduse à bout de bras, dans un calme idéal néo-classique inspiré de l'Antiquité. Canova modèle d'abord le plâtre, fait dégrossir le marbre par ses praticiens, puis polit lui-même la surface jusqu'à la douceur de la peau. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG/1280px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_204.JPG | Barye, Lion au serpent, Paris, 1832 | enchaîné 10]Au XIXe siècle, le romantisme sort la ronde-bosse des palais et des mythes pour aller vers un réalisme puissant. Antoine-Louis Barye, ancien apprenti orfèvre qui dessine les fauves au Jardin des plantes, modèle en 1832 *Le Lion au serpent*, fondu en bronze en 1835. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Lion_et_serpent_-_Antoine-Louis_Barye.jpg/1280px-Lion_et_serpent_-_Antoine-Louis_Barye.jpg | Barye, Lion au serpent, Paris, 1832 | enchaîné 10]Le sujet n'est plus un dieu, mais la force brute de la nature. Louis-Philippe achète le bronze, qui reste aux Tuileries de 1836 à 1911. [image: https://upload.wikimedia.org/wikipedia/commons/e/ee/Edgar_degas%2C_little_dancer_aged_14%2C_1879-81.JPG | Degas, La Petite Danseuse de quatorze ans, Washington, 1878-1881 | enchaîné 10]En 1881, à l'exposition des Impressionnistes, Edgar Degas présente une danseuse de cire de quatorze ans, Marie van Goethem, élève de l'Opéra. Sur une armature métallique, il modèle de la cire colorée, puis l'habille d'un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Bailarina%2C_Degas.jpg/960px-Bailarina%2C_Degas.jpg | Degas, La Petite Danseuse de quatorze ans, Washington, 1878-1881 | enchaîné 10]vrai tutu, de vrais rubans et de vrais cheveux. Le public est choqué ; Huysmans y voit pourtant la première tentative vraiment moderne de sculpture. Degas n'exposera plus jamais de sculpture ; les bronzes ne seront fondus qu'après sa mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Rodin_The_bronze_age.jpg/500px-Rodin_The_bronze_age.jpg | Rodin, L'Age d'Airain, 1875 | enchaîné 10]Auguste Rodin fait vibrer la matière. Dès 1877, son *Âge d'airain* est si naturel qu'on l'accuse d'avoir moulé un modèle vivant. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG/1280px-L72_-_Mus%C3%A9e_Rodin_-_L%27Homme_qui_marche.JPG | Rodin, L’Homme qui marche, Paris, 1907 | enchaîné 10]Avec *L'Homme qui marche*, il va plus loin : une figure sans tête ni bras, issue d'une étude pour un saint Jean-Baptiste, assume le fragment comme œuvre achevée. Le bronze garde la trace des doigts et du modelage. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG/1280px-La_M%C3%A9diterran%C3%A9e_Statue_Maillol_Mus%C3%A9e_d%27Orsay.JPG | Maillol, La Méditerranée, Paris, 1902-1905 | enchaîné 10]Face à ce tourment, Aristide Maillol retrouve le calme. Venu tard à la sculpture après la peinture et la tapisserie, il sculpte de 1902 à 1905 *La Méditerranée*, que lui commande le comte Harry Kessler : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Museum_of_Modern_Art_-_panoramio.jpg/1280px-Museum_of_Modern_Art_-_panoramio.jpg | Maillol, La Méditerranée, Paris, 1902-1905 | enchaîné 10]une femme assise, nue, sans geste ni histoire, aux volumes pleins et fermés, aux surfaces lisses. Le sujet ne raconte rien ; seule compte la forme. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/65/Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG/1280px-Herakles-Archer_by_Antoine_Bourdelle%2C_c._1909%2C_bronze_-_Chazen_Museum_of_Art_-_DSC02262.JPG | Bourdelle, Héraklès archer, Paris, 1909 | enchaîné 10]Antoine Bourdelle, ancien praticien de Rodin, donne à la ronde-bosse une architecture. Son *Héraklès archer*, fondu en 1909 et montré au Salon de 1910, dépasse deux mètres cinquante : [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1f/Hercules_boogschutter_-_Emile-Antoine_Bourdelle_-_Middelheimmuseum_-_4.jpg/1280px-Hercules_boogschutter_-_Emile-Antoine_Bourdelle_-_Middelheimmuseum_-_4.jpg | Bourdelle, Héraklès archer, Paris, 1909 | enchaîné 10]il bande son arc, le pied calé sur un rocher, tout le corps ramassé comme un ressort. Chaque muscle obéit à une géométrie : la statue n'est plus un récit, c'est une structure tendue dans l'espace. En six siècles, la ronde-bosse s'est détachée de la niche, puis du récit pour aller vers la forme.
 [sortie: noir]</v>
       </c>
       <c r="D6" t="str">
-        <v>26/10/2026 16:53:15</v>
+        <v>26/10/2026 19:31:00</v>
       </c>
       <c r="E6" t="str">
         <v>Terminé</v>
